--- a/workspaces/nasdaq_hourly_24hrs/volatility/bb_width_20.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/volatility/bb_width_20.xlsx
@@ -625,76 +625,76 @@
         <v>90</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-3.648190416598418</v>
+        <v>-3.615188156351927</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-5.085789334096667</v>
+        <v>-5.052391450112772</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-5.414543902440066</v>
+        <v>-5.379464142817248</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-8.334988539768105</v>
+        <v>-8.299081890581562</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-12.01395152817341</v>
+        <v>-11.94875515918951</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-17.35703399298072</v>
+        <v>-17.29204467217955</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-28.07884857617958</v>
+        <v>-28.01298907115252</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-32.78687158161169</v>
+        <v>-32.72066872238082</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-30.54275471246308</v>
+        <v>-30.47653673357903</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-30.21622644234186</v>
+        <v>-30.14905884713623</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-28.8450148046786</v>
+        <v>-28.77810761950358</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-29.13175039375987</v>
+        <v>-29.06446978261883</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-30.26096451071512</v>
+        <v>-30.19233286668162</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-27.16778134155024</v>
+        <v>-27.09882801497997</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-27.83333790004769</v>
+        <v>-27.76356887392557</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-27.248270461441</v>
+        <v>-27.17913861874349</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-25.17305997597314</v>
+        <v>-25.10371423131443</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-21.95860777326739</v>
+        <v>-21.88908038694863</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-20.64028632959229</v>
+        <v>-20.57095731618815</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-21.56974943766474</v>
+        <v>-21.50058941447536</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-25.4495477296878</v>
+        <v>-25.37970797787514</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-22.20225926106146</v>
+        <v>-22.13227570580099</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-20.8238502887901</v>
+        <v>-20.75413551559645</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-17.57309941520442</v>
+        <v>-17.5032450674974</v>
       </c>
     </row>
     <row r="7">
@@ -707,76 +707,76 @@
         <v>184</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3.366590457675102</v>
+        <v>3.399633952695972</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1.956023990577783</v>
+        <v>1.989459115312364</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-3.252391794276953</v>
+        <v>-3.217321186196699</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-6.122752595743577</v>
+        <v>-6.086858507094988</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-3.245763001983818</v>
+        <v>-3.180546398890563</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-5.221886587285894</v>
+        <v>-5.156858723110979</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-7.611911347207837</v>
+        <v>-7.545968417417157</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-7.890630027493664</v>
+        <v>-7.824324027467853</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-6.229059861026798</v>
+        <v>-6.162746802137015</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-5.378618607047997</v>
+        <v>-5.311359207069373</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-4.024643707052427</v>
+        <v>-3.957650191808028</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-2.13856084786066</v>
+        <v>-2.071189875934834</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-2.717870879738541</v>
+        <v>-2.64915525873699</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-1.314736619714481</v>
+        <v>-1.245712118146677</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-2.514339091008132</v>
+        <v>-2.444508675788981</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-3.548087223773656</v>
+        <v>-3.478905902966005</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-6.394631232494802</v>
+        <v>-6.325255936144281</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-7.586927046057923</v>
+        <v>-7.517384277263417</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-6.288826029772849</v>
+        <v>-6.219483775128772</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-7.73273027902939</v>
+        <v>-7.663560788941346</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-8.821179553039848</v>
+        <v>-8.75133000242505</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-8.9005151278255</v>
+        <v>-8.830527425537532</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-9.715776589937548</v>
+        <v>-9.646060577499028</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-11.42575642003572</v>
+        <v>-11.35590207232832</v>
       </c>
     </row>
     <row r="8">
@@ -786,79 +786,79 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-1.248193673769315</v>
+        <v>-1.021252457049904</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1.001775958645986</v>
+        <v>1.238857245176604</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2.895402924550645</v>
+        <v>2.776297498889797</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2.926663610247402</v>
+        <v>2.811100736777334</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1.45737288435874</v>
+        <v>1.737487885927969</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2022046378438063</v>
+        <v>0.07090220451986085</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>5.313674717117678</v>
+        <v>5.611282590941528</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>5.039537597728746</v>
+        <v>5.337586087045445</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>5.082329272883925</v>
+        <v>5.009314252908936</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>5.053300352407391</v>
+        <v>4.983935630780316</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>5.327897935192759</v>
+        <v>5.258213203901605</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>7.642389343479834</v>
+        <v>7.582709910162706</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>7.63636517871668</v>
+        <v>7.582129306859336</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>6.676788891429148</v>
+        <v>6.620040815871334</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>6.022227156031825</v>
+        <v>5.966239232958763</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>6.617565910947171</v>
+        <v>6.560889692025413</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>6.486046319010441</v>
+        <v>6.429524414443435</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>5.641026089354625</v>
+        <v>5.581855720107043</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>3.260469288668425</v>
+        <v>3.191347969004333</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>1.22071167469278</v>
+        <v>1.143054064250535</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>3.648858396264458</v>
+        <v>3.582919724032642</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>3.573442084387189</v>
+        <v>3.880459318970942</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>3.105490464562187</v>
+        <v>3.036545616484275</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>3.401704384877846</v>
+        <v>3.33423420281769</v>
       </c>
     </row>
     <row r="9">
@@ -871,76 +871,76 @@
         <v>296</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.9623162192572394</v>
+        <v>-1.264361292987267</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.04399177761862205</v>
+        <v>-0.2577486704689846</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-2.053357394700932</v>
+        <v>-2.01826593384579</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.08009963819762334</v>
+        <v>-0.0441389254313691</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.229307799351318</v>
+        <v>-0.04107061427824732</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.4173517420674031</v>
+        <v>0.1466778678236977</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1.9984575141726</v>
+        <v>1.728619874679907</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>2.731044139004169</v>
+        <v>2.461455001922772</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>4.788106390173787</v>
+        <v>4.85445237977509</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>5.699669470027118</v>
+        <v>5.766962294374117</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>5.638493424616463</v>
+        <v>5.705511878967471</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>5.361394205674614</v>
+        <v>5.428780262726839</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>7.272028002512847</v>
+        <v>7.34077054255166</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>7.726997087241323</v>
+        <v>7.796043169321592</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>8.420332193039307</v>
+        <v>8.490187499892194</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>5.312363689458572</v>
+        <v>5.381551636172219</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>5.854687547517017</v>
+        <v>5.924077675349139</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>7.100012539326286</v>
+        <v>7.16957586166447</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>7.655478698840206</v>
+        <v>7.724836677332455</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>7.845224511718754</v>
+        <v>7.914407908550643</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>8.992185535548096</v>
+        <v>9.062049542673641</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>7.90633176001446</v>
+        <v>7.63873137540768</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>8.183487679631291</v>
+        <v>8.253208255246633</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>8.447921605816425</v>
+        <v>8.517775953523618</v>
       </c>
     </row>
     <row r="10">
@@ -953,322 +953,322 @@
         <v>276</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.5873382716589646</v>
+        <v>0.6210033032596911</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-1.548279617216352</v>
+        <v>-1.514231012546468</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.2245475009532498</v>
+        <v>0.2603653091365175</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>2.223375083182454</v>
+        <v>2.05829256120245</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2.416485825922464</v>
+        <v>2.075683998841924</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2.447770952811013</v>
+        <v>1.900762825855914</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.879722917855908</v>
+        <v>1.119701015483244</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3.969220458705458</v>
+        <v>3.20542994862123</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>3.498236589505368</v>
+        <v>2.737367399571568</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>3.809796095572082</v>
+        <v>3.250572784160738</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>3.72402488784099</v>
+        <v>3.375089382248049</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>2.365473844009188</v>
+        <v>2.224254412621463</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.329433776185262</v>
+        <v>2.398071691842617</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.831092621947086</v>
+        <v>2.900045685408116</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>3.259137581544387</v>
+        <v>3.328907291392184</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>4.938142609954362</v>
+        <v>5.007282721755075</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>5.168118459419802</v>
+        <v>5.237465043469129</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>3.619798576309144</v>
+        <v>3.689310492701161</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.9449799895721256</v>
+        <v>1.014279625495696</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>2.21739922156722</v>
+        <v>2.286539884210349</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>2.398827634932211</v>
+        <v>2.468657872361348</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>2.323534365712867</v>
+        <v>2.393508851793214</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>1.512320756340834</v>
+        <v>1.582029684390243</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.01271294177472981</v>
+        <v>0.05714140593254768</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ 0.02192</t>
+          <t>X ≈ 0.02191</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.3428134851348261</v>
+        <v>-0.1262295783673011</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.68508940458527</v>
+        <v>1.892880156401141</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.603756332677207</v>
+        <v>2.804079147442074</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-2.056269913728293</v>
+        <v>-1.840577416177275</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2.424637924352737</v>
+        <v>-2.18074161985966</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.6608390734213856</v>
+        <v>-0.4225731592745561</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-3.014986781800722</v>
+        <v>-2.774674794321072</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-4.083924030015318</v>
+        <v>-3.84228717544265</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-7.98528448713769</v>
+        <v>-7.735636666396211</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-12.08335333006942</v>
+        <v>-12.05564169510183</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-13.15841242826239</v>
+        <v>-13.3541260924903</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-13.60314224203691</v>
+        <v>-14.02757596412236</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-14.33315352062485</v>
+        <v>-14.76611962737275</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-13.77170138378239</v>
+        <v>-13.96780479061817</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-12.45898187809194</v>
+        <v>-12.42494700907939</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-12.26651495617822</v>
+        <v>-11.98981993182151</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-11.61499397414632</v>
+        <v>-11.3410845805742</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-12.51660918870314</v>
+        <v>-12.23927632562945</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-13.09802194020798</v>
+        <v>-12.81763469286764</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-12.5218878658855</v>
+        <v>-12.24309576850185</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-11.88282291477895</v>
+        <v>-11.6079070987622</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-13.15446490875913</v>
+        <v>-12.874578438946</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-14.47338201928939</v>
+        <v>-14.18735901584482</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-14.55722639933158</v>
+        <v>-14.27092183517426</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ 0.02454</t>
+          <t>X ≈ 0.02453</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2.271009677493566</v>
+        <v>2.561443603909694</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>4.553550304058881</v>
+        <v>4.117991386939423</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.437192932547603</v>
+        <v>1.153529642360894</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>4.83153074594707</v>
+        <v>4.596354401003204</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>3.340773058618261</v>
+        <v>3.49857076347331</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.780019867747647</v>
+        <v>2.928771117574748</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>6.115284862286117</v>
+        <v>6.534796984275481</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>7.330158360196521</v>
+        <v>7.76963374845198</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>7.744128661954321</v>
+        <v>8.188100548217434</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>9.581685970900473</v>
+        <v>10.0600268909173</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>9.482688202158641</v>
+        <v>9.576707472359992</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>6.95863715488872</v>
+        <v>7.021546105482301</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>5.30637899403316</v>
+        <v>5.129463068472525</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>6.060767275766388</v>
+        <v>5.667045687126603</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>4.282566943988066</v>
+        <v>3.86684910468631</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>4.130444323527087</v>
+        <v>3.705566878418978</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>4.372347236182776</v>
+        <v>4.18132997041333</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>4.26860768111473</v>
+        <v>4.308733642534349</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>5.467173273648932</v>
+        <v>5.284113451261668</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>6.781133224866949</v>
+        <v>6.611168668477575</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>4.739553960517689</v>
+        <v>4.551116966049712</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>5.040671555963421</v>
+        <v>4.855739133138194</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>6.068315483693475</v>
+        <v>6.12799323358368</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>6.370091896407608</v>
+        <v>6.434228527770962</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ 0.02716</t>
+          <t>X ≈ 0.02715</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.455119181418453</v>
+        <v>1.155989109295504</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>4.240263291895594</v>
+        <v>4.913645919494378</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>7.438832354654899</v>
+        <v>7.537270566946042</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>3.084107296875558</v>
+        <v>3.238697858784739</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.627061926010029</v>
+        <v>0.3295253235840434</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>4.445959334214407</v>
+        <v>4.101169676318406</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2.108605461101696</v>
+        <v>1.783660932354081</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.825962393632636</v>
+        <v>1.500811760383904</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>4.978056041995806</v>
+        <v>4.612549289969536</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>6.785466158809037</v>
+        <v>6.385808297746522</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>2.38884852347536</v>
+        <v>2.560017173390911</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>2.099533565124389</v>
+        <v>2.269673451900253</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>6.138555507290071</v>
+        <v>6.240020184475277</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>4.362932010073095</v>
+        <v>4.484975565997608</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>5.044169083319623</v>
+        <v>4.835562914786529</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>3.361959604189735</v>
+        <v>2.872180834873276</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>3.747043322701977</v>
+        <v>3.247266748297626</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>2.919319301246702</v>
+        <v>2.110506762021352</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>4.173604130283394</v>
+        <v>3.660729346528491</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>3.122610010442095</v>
+        <v>2.627348754169155</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>2.581011659390533</v>
+        <v>2.079917320939629</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>3.545887103778156</v>
+        <v>3.346585577955935</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>3.821459081359933</v>
+        <v>3.621360712530979</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>3.746345029239762</v>
+        <v>3.86427630002396</v>
       </c>
     </row>
     <row r="14">
@@ -1278,1719 +1278,1719 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.545396773711929</v>
+        <v>2.317759067837208</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>6.368719440861057</v>
+        <v>6.166283109030147</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>4.330861288945776</v>
+        <v>4.130397142622741</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.614330711132894</v>
+        <v>3.417153302639953</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.651880832786887</v>
+        <v>2.479895206698089</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>5.213883977080556</v>
+        <v>5.065785209231649</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>5.032527890207284</v>
+        <v>4.888678587249288</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.5989345297184414</v>
+        <v>0.4172662427083154</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.733019304235818</v>
+        <v>-1.336861694345281</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-3.102079619312967</v>
+        <v>-2.71214406556291</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-3.422749737603851</v>
+        <v>-3.04005508525178</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.923403127508216</v>
+        <v>-1.526357636372836</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-4.831613869904359</v>
+        <v>-4.452659455470396</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-2.085644509963899</v>
+        <v>-1.679726355869079</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-6.307713380987913</v>
+        <v>-5.935436424669113</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-4.525918381878135</v>
+        <v>-4.143840745637178</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-1.332639088030824</v>
+        <v>-1.284537973227074</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.2491151163172987</v>
+        <v>-0.1949421532703681</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-1.812796311188187</v>
+        <v>-1.776646057965323</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.4388220471779078</v>
+        <v>-0.3921954575782038</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>0.2051704570989585</v>
+        <v>0.6307781285983651</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-2.249464736808406</v>
+        <v>-1.840277413649055</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-5.546766906232264</v>
+        <v>-5.158617072424498</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-4.438178780284041</v>
+        <v>-4.03684453522861</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 0.03241</t>
+          <t>X ≈ 0.0324</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-4.325998277385764</v>
+        <v>-3.968940582542189</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-4.968390251645104</v>
+        <v>-4.301366455868077</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.02806727568336953</v>
+        <v>0.6495758850603366</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.325205160883975</v>
+        <v>-0.7076765817113895</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-4.900405943891641</v>
+        <v>-4.89818956890231</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.50055254905611</v>
+        <v>-1.147216138500276</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2.872749928176518</v>
+        <v>3.209040305814426</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.953964036417254</v>
+        <v>2.289803220035857</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.218963633744785</v>
+        <v>-1.514863444203357</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.919259058548938</v>
+        <v>-4.210856043316774</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.8582797877672448</v>
+        <v>0.5503830860246381</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.5809408376483418</v>
+        <v>0.2716336825766419</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>6.534343102550359</v>
+        <v>6.199753667002575</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>4.382765663147218</v>
+        <v>4.055597867479058</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>3.728347161310658</v>
+        <v>3.3974545698985</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>3.680167473223996</v>
+        <v>3.350815850815849</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>5.474288746465646</v>
+        <v>5.13997563691531</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>4.084831515932287</v>
+        <v>3.753083651042836</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>3.016480864426008</v>
+        <v>2.686923749915884</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>1.274056154544532</v>
+        <v>0.9506926368070623</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>2.018192302988155</v>
+        <v>1.69019775089216</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>1.942641911173084</v>
+        <v>1.614351789483209</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>0.9278815550907353</v>
+        <v>0.6067752199139065</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>1.495000943218258</v>
+        <v>1.171968607716266</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ 0.03503</t>
+          <t>X ≈ 0.03502</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>165</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.871739325245017</v>
+        <v>-1.838186098478481</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-4.015312920599577</v>
+        <v>-4.587898901030485</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-7.876063115822646</v>
+        <v>-8.456775838963978</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-3.759527401924558</v>
+        <v>-4.335175617765984</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.5056469384916582</v>
+        <v>-0.7048116952271002</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.52338353868835</v>
+        <v>-1.72996672125079</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-6.526482178268282</v>
+        <v>-6.744339647565518</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-6.203894043316687</v>
+        <v>-6.416490486257999</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-7.977053624434895</v>
+        <v>-8.193185122525037</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-8.754289383146094</v>
+        <v>-8.966100798561598</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-7.27189012011187</v>
+        <v>-7.479919944278457</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-8.761378106542125</v>
+        <v>-8.9707905598476</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-10.49250497525144</v>
+        <v>-10.70001323276433</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-9.504775529461881</v>
+        <v>-9.708970897089706</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-6.542725563458212</v>
+        <v>-6.730750558306624</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-7.156228640208226</v>
+        <v>-7.348484848484844</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-7.288752942999416</v>
+        <v>-7.482401985462317</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-1.957294812233854</v>
+        <v>-2.132697234738046</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-1.743264171112287</v>
+        <v>-1.91680585381372</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.9522003775324421</v>
+        <v>-1.123899437785091</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>0.08867446014038194</v>
+        <v>-0.4543243936298396</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-2.408132597415047</v>
+        <v>-2.954412779281498</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>2.100411062958372</v>
+        <v>1.562486175624855</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.4013822434875038</v>
+        <v>-0.9375885018408354</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 0.03765</t>
+          <t>X ≈ 0.03764</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.054271989547573</v>
+        <v>-2.056336243444669</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-9.46640539607985</v>
+        <v>-9.429590676724132</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-7.042099598983555</v>
+        <v>-7.042499130684604</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.6813050255027875</v>
+        <v>-0.3573662110247753</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>2.817431450655668</v>
+        <v>3.15299716258194</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.2141112939914507</v>
+        <v>0.134835143550923</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.3015889479710552</v>
+        <v>0.6449377417119706</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.312616392989341</v>
+        <v>1.648777579010144</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>5.215091569633536</v>
+        <v>5.536418607078687</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>5.731515393747848</v>
+        <v>6.045554213093553</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>6.005874660863185</v>
+        <v>6.319613855255476</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>6.372756805263606</v>
+        <v>6.681890092833058</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.679935715252611</v>
+        <v>2.994625461874371</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.5284379205808918</v>
+        <v>0.8504696623508536</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>2.445285140882923</v>
+        <v>2.756428928872793</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>4.969809029794867</v>
+        <v>5.273892773892783</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>5.476612800919924</v>
+        <v>5.781001277940945</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>3.442504117707571</v>
+        <v>3.753083651042914</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>6.87598034959948</v>
+        <v>7.174103237095359</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>8.991810840163623</v>
+        <v>9.284025970140391</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>9.735145372141666</v>
+        <v>10.02353108422565</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>10.31304526082349</v>
+        <v>10.58871076384211</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>9.30674277460222</v>
+        <v>9.581134194272821</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>9.236936427089226</v>
+        <v>9.505301941049545</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 0.04027</t>
+          <t>X ≈ 0.04026</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.429326379066055</v>
+        <v>-2.828837808241893</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.463455944006284</v>
+        <v>1.036380890138993</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.675291763376521</v>
+        <v>-1.632130355770705</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.54122757954206</v>
+        <v>-1.504748240759618</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.465605577943073</v>
+        <v>1.520805824508088</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.8122436422538257</v>
+        <v>0.8674358761517311</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.03537881110984387</v>
+        <v>0.09548719226143731</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.094365580677874</v>
+        <v>-1.023060386945431</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.6348680802202225</v>
+        <v>0.6990990638768011</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.9914899765150764</v>
+        <v>-0.9141527466134818</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.7171307093997399</v>
+        <v>-0.6400931044515588</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.1563645140267127</v>
+        <v>-0.07850637344576228</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.4001973648783377</v>
+        <v>0.479003828605677</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.510876391576431</v>
+        <v>-1.42274731674847</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.4847558341314695</v>
+        <v>-0.4002183454213721</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.1109706653381934</v>
+        <v>0.1941685765215198</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-3.399224670410064</v>
+        <v>-3.301093098271124</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.9699658932988484</v>
+        <v>-0.8849253987310135</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-1.60103377754627</v>
+        <v>-1.509370152260367</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-1.41199063238102</v>
+        <v>-1.322524342292489</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-1.955191041378974</v>
+        <v>-1.865070510258519</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>1.871873574004582</v>
+        <v>1.42042806614765</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.392724535628858</v>
+        <v>-0.8261056247315537</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>2.069085142234115</v>
+        <v>1.619070525406521</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 0.0429</t>
+          <t>X ≈ 0.04288</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>4.108260672011475</v>
+        <v>4.112371519565059</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-6.63759354849747</v>
+        <v>-6.561830808333504</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.014205946517222</v>
+        <v>-1.965367098743812</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-3.591442850985942</v>
+        <v>-3.540390083703834</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-3.097065630161872</v>
+        <v>-3.014111590733826</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-3.772395462073789</v>
+        <v>-3.689214370153685</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.946388503089182</v>
+        <v>-1.874956157492313</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.238322680063163</v>
+        <v>1.295108259823529</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>3.882508421551968</v>
+        <v>3.922802338290005</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>3.097283254499828</v>
+        <v>3.149886662253515</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.635263875495127</v>
+        <v>1.699808373380961</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.349525947521997</v>
+        <v>1.421058969932965</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.81821294193216</v>
+        <v>2.884103799628612</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>4.332285630660792</v>
+        <v>4.387162854216463</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>1.931280867362126</v>
+        <v>2.004881625601421</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>5.131858032520377</v>
+        <v>5.185475444096141</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>5.868801100502196</v>
+        <v>5.913627272635949</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>4.028388184643831</v>
+        <v>4.08464863778029</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>5.977093408267926</v>
+        <v>6.024677949739051</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>7.903363289079095</v>
+        <v>7.935661690741597</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>8.228352203141135</v>
+        <v>8.255184488292819</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>6.412221915950902</v>
+        <v>6.455200595849185</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>8.967766012271291</v>
+        <v>8.453813239365715</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>6.291634884312224</v>
+        <v>5.791774089590724</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.04552</t>
+          <t>X ≈ 0.0455</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>96</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-4.706759835437815</v>
+        <v>-5.24201878273162</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-4.001031286539124</v>
+        <v>-3.975623911781781</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-6.478093399658526</v>
+        <v>-6.455309627479494</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-8.232790776394708</v>
+        <v>-8.209930313588842</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-6.516252434332706</v>
+        <v>-6.462387452802787</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-5.290840568665182</v>
+        <v>-5.233754600038743</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-5.023097838385326</v>
+        <v>-4.964036617262423</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-5.299881276648946</v>
+        <v>-5.242248062015442</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-4.218937154128973</v>
+        <v>-4.15909421343413</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.909783632975802</v>
+        <v>-2.848676556137285</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-3.674557222148557</v>
+        <v>-3.616283580642033</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-6.031031234572517</v>
+        <v>-5.978366317423358</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-5.073419124764477</v>
+        <v>-5.018195050946204</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-6.334794395714383</v>
+        <v>-6.280940594059402</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-5.951640766372059</v>
+        <v>-5.897417224973296</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-3.278315004174324</v>
+        <v>-3.219696969696969</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-2.373866244453318</v>
+        <v>-2.311947440007778</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.3991079419265589</v>
+        <v>-0.3334548104956809</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>1.8970521408366</v>
+        <v>1.965769903762038</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>1.042896671704817</v>
+        <v>1.110949047063393</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.4994010614977213</v>
+        <v>0.5684028790974267</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>1.464940471816469</v>
+        <v>1.534223584354933</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>4.859771018045386</v>
+        <v>4.933698296836994</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>2.704678362573098</v>
+        <v>2.774532710280376</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.04814</t>
+          <t>X ≈ 0.04813</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2.687818892756709</v>
+        <v>2.697181055582199</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>5.201790499647515</v>
+        <v>5.179305665683003</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3.738102828738405</v>
+        <v>3.741286616652182</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>4.460876679724308</v>
+        <v>4.436783301434623</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.206098862229446</v>
+        <v>-0.1243592837886993</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-2.860085635150092</v>
+        <v>-2.754294506142031</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-6.495425114752059</v>
+        <v>-6.343144598483086</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.075685517200426</v>
+        <v>-0.9875532263349101</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.828303895370247</v>
+        <v>1.870835364030654</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>2.456387461146718</v>
+        <v>2.506370392219516</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>4.151322421225764</v>
+        <v>4.188880738606791</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>8.133955596642096</v>
+        <v>8.135483447834773</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>6.990807661737144</v>
+        <v>7.01232138097874</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>6.769450850702789</v>
+        <v>6.79124250453215</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>6.091862895247594</v>
+        <v>6.133099206951591</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>3.845771558941379</v>
+        <v>3.910584720443794</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.8678612336624099</v>
+        <v>0.9597661750156945</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.765543062769666</v>
+        <v>0.8549254711945125</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>5.267380511415759</v>
+        <v>5.296168964794909</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>2.60794243070368</v>
+        <v>2.666113366312302</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>2.067407266908106</v>
+        <v>2.123567198346031</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-2.307588300461582</v>
+        <v>-2.177630875739041</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-2.032813133979452</v>
+        <v>-1.903156163256988</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>1.633249791144529</v>
+        <v>0.8379129919705122</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.05076</t>
+          <t>X ≈ 0.05075</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-3.674121405750796</v>
+        <v>-4.48830474055061</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2.657369746271542</v>
+        <v>1.956579478048781</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.884335948851977</v>
+        <v>3.908390937492221</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-4.496124031007746</v>
+        <v>-3.584224098899575</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-4.86139381603175</v>
+        <v>-3.920014571446849</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.340895869691671</v>
+        <v>-0.3432178768749452</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>9.552904664920952</v>
+        <v>10.74924021889576</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>5.941016686069162</v>
+        <v>7.081198265668206</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.649199417758368</v>
+        <v>3.732854939108243</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.2086973403223169</v>
+        <v>1.265024008834459</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.850276725895775</v>
+        <v>-1.850746857478192</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.2039627039628016</v>
+        <v>1.260334247548485</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.412804818808901</v>
+        <v>3.527002689166892</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.80855199222546</v>
+        <v>-1.778821949991602</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-1.80081656459609</v>
+        <v>-0.7420499933348808</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-1.205756514974709</v>
+        <v>-0.1476630713917899</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.3268164575429822</v>
+        <v>1.413335045867932</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-3.111500291885584</v>
+        <v>-2.081336166427825</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-1.228710462287097</v>
+        <v>-0.1705295312662187</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-1.041666666666764</v>
+        <v>0.01631627870172281</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-3.251533742331191</v>
+        <v>-2.221145143501403</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-1.660822131307135</v>
+        <v>-0.6020758506732236</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>0.2806197018416654</v>
+        <v>1.367314116046117</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>0.2046783625730981</v>
+        <v>1.291481862822749</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.05338</t>
+          <t>X ≈ 0.05337</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>49</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.6128969159548774</v>
+        <v>1.461193702894555</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>3.133560222462016</v>
+        <v>5.208049557605918</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>5.775492411437106</v>
+        <v>5.810846835105593</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-3.101566207878562</v>
+        <v>-3.065372490459595</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.426019666371992</v>
+        <v>-1.360346636476265</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.8019612731654604</v>
+        <v>0.8674358761518022</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>6.151544120703278</v>
+        <v>6.217936171853225</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.79135682212349</v>
+        <v>1.858092074038922</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.248759765915111</v>
+        <v>-2.182053397107609</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>3.099853802907255</v>
+        <v>3.167479906447745</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.333396743492088</v>
+        <v>1.400723222079058</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-5.068146139574651</v>
+        <v>-5.000475160960775</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-12.31508633765375</v>
+        <v>-12.24608620740879</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-4.373177842565603</v>
+        <v>-4.30389977773288</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.9504764285416698</v>
+        <v>-0.8804104222522042</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-6.477865358512013</v>
+        <v>-6.40847247990105</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-10.69359170572228</v>
+        <v>-10.62402226993975</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-4.676126142225726</v>
+        <v>-4.606413994169031</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-10.58245195888568</v>
+        <v>-10.51297159283654</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-12.43622448979592</v>
+        <v>-12.36694210939919</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-17.0610575518551</v>
+        <v>-16.99112093042638</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-13.05537995443648</v>
+        <v>-12.98533423877432</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-10.73978846142368</v>
+        <v>-10.67004319976166</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-12.85654612722282</v>
+        <v>-12.78669177951549</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.056</t>
+          <t>X ≈ 0.05599</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-2.693729248888054</v>
+        <v>-3.640847113431967</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-8.911257704708845</v>
+        <v>-9.744854681012555</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-8.390173855069499</v>
+        <v>-9.259796806966619</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-7.143182854537109</v>
+        <v>-8.049673903332433</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-3.586884012110225</v>
+        <v>-4.53931052972586</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-3.399719399103496</v>
+        <v>-4.352344343628538</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-8.094154158608454</v>
+        <v>-8.970446873672678</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.490355862950537</v>
+        <v>-3.479427549194988</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.448839797927903</v>
+        <v>-3.437940367280284</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.659677732479132</v>
+        <v>1.558374725913993</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>10.77717425449643</v>
+        <v>9.524742060383609</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>12.45886466474697</v>
+        <v>11.16906958001253</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>13.29515775998542</v>
+        <v>11.96898443623335</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>7.191448007774476</v>
+        <v>5.978674790555928</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>10.45408539618823</v>
+        <v>9.166685339129266</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>13.00992975953503</v>
+        <v>11.68414918414913</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>12.87583606538622</v>
+        <v>11.55023204717172</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>8.849284021839907</v>
+        <v>7.59923749719664</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>11.02619149849716</v>
+        <v>9.738205801197871</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>13.17401960784314</v>
+        <v>11.84812853424289</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>8.7092505713942</v>
+        <v>7.459428520122962</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>12.55486414320257</v>
+        <v>11.22973640486776</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>3.025717741057193</v>
+        <v>1.888826501965191</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>2.949776401788725</v>
+        <v>1.812994248741809</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.05863</t>
+          <t>X ≈ 0.05861</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>32</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>5.700878594249204</v>
+        <v>5.734152886568033</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.8842969203951228</v>
+        <v>-0.8506239117817813</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-2.323997384481174</v>
+        <v>-2.288642960812687</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-6.162790697674502</v>
+        <v>-6.126596980255599</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-3.403060482698464</v>
+        <v>-3.337387452802787</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-6.340895869691678</v>
+        <v>-6.275421266705408</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-10.23876200174562</v>
+        <v>-10.17236995059567</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-13.64231664726435</v>
+        <v>-13.57558139534892</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-10.47580058224172</v>
+        <v>-10.40909421343422</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-14.37463599301106</v>
+        <v>-14.30700988947062</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-17.22527672589572</v>
+        <v>-17.1579502473087</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-14.37937062937063</v>
+        <v>-14.31169965075669</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-18.62886184785769</v>
+        <v>-18.55986171761273</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-12.60021865889195</v>
+        <v>-12.53094059405922</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-13.25914989792934</v>
+        <v>-13.18908389163987</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-6.41408984830796</v>
+        <v>-6.344696969696884</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.2981835424569681</v>
+        <v>-0.228614106674442</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-3.528166958552248</v>
+        <v>-3.458454810495624</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-3.312043795620433</v>
+        <v>-3.242563429571298</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-6.25</v>
+        <v>-6.180717619603271</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.5432004089979543</v>
+        <v>-0.4732637875693015</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-3.744155464640563</v>
+        <v>-3.674109748978402</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-3.469380298158349</v>
+        <v>-3.399635036496264</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-3.545321637426817</v>
+        <v>-3.475467289719539</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.06125</t>
+          <t>X ≈ 0.06123</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>38</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.042542458382442</v>
+        <v>-1.009268166063613</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>11.78017676381541</v>
+        <v>11.81384977242875</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>12.97205524709761</v>
+        <v>13.0074096707661</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>9.62668298653626</v>
+        <v>9.662876703955163</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>11.89299214888048</v>
+        <v>11.95866517877616</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>14.71173570925569</v>
+        <v>14.77721031224196</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.7809748403594057</v>
+        <v>0.8473668915093526</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.129158752527353</v>
+        <v>-2.062423500611921</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.087642687504719</v>
+        <v>-2.020936318697217</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>5.033258743831041</v>
+        <v>5.100884847371482</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>13.20235485305165</v>
+        <v>13.26968133163867</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>12.92326094957674</v>
+        <v>12.99093192819068</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>19.69350657319479</v>
+        <v>19.76250670343975</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>8.94583397268682</v>
+        <v>9.015112037519543</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>18.81321852312305</v>
+        <v>18.88328452941251</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>19.40827857274459</v>
+        <v>19.47767145135566</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>19.27418487859575</v>
+        <v>19.34375431437827</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>21.80078040986888</v>
+        <v>21.8704925579255</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>16.75374567806384</v>
+        <v>16.82322604411298</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>19.57236842105263</v>
+        <v>19.64165080144936</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>16.39758906468627</v>
+        <v>16.46752568611492</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>16.32163400904366</v>
+        <v>16.39167972470582</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>13.96483022815729</v>
+        <v>14.03457548981937</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>11.25730994152038</v>
+        <v>11.32716428922766</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.06387</t>
+          <t>X ≈ 0.06385</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>39</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.736135004505726</v>
+        <v>2.769409296824556</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.400959489861286</v>
+        <v>2.434632498474627</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3.525361589877747</v>
+        <v>3.560716013546234</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.2474657125819135</v>
+        <v>0.2836594300008173</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.446298491660478</v>
+        <v>2.511971521556156</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-7.622947151742892</v>
+        <v>-7.557472548756621</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-13.52401841200204</v>
+        <v>-13.4576263608521</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-13.80257305752068</v>
+        <v>-13.73583780560524</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-16.32515955660061</v>
+        <v>-16.25845318779311</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-11.97078983916491</v>
+        <v>-11.90316373562447</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-14.26053313615213</v>
+        <v>-14.19320665756511</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-11.97552447552447</v>
+        <v>-11.90785349691054</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-18.22822082221675</v>
+        <v>-18.15922069197179</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-10.75726994094348</v>
+        <v>-10.68799187611076</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-11.41620117998064</v>
+        <v>-11.34613517369117</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-8.257038566256767</v>
+        <v>-8.187645687645691</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-10.95523482450832</v>
+        <v>-10.8856653887258</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-5.932013112398472</v>
+        <v>-5.862300964341848</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-8.279992513569219</v>
+        <v>-8.210512147520085</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-5.528846153846153</v>
+        <v>-5.459563773449425</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-3.507943998741545</v>
+        <v>-3.438007377312893</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-6.148001618486717</v>
+        <v>-6.077955902824556</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-3.309123887902103</v>
+        <v>-3.239378626240018</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.8209626630678599</v>
+        <v>-0.7511083153605824</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.06649</t>
+          <t>X ≈ 0.06648</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>32</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>5.700878594249161</v>
+        <v>5.73415288656799</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>11.61570307960488</v>
+        <v>11.64937608821822</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>7.051002615518698</v>
+        <v>7.086357039187185</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-3.037790697674417</v>
+        <v>-3.001596980255513</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-3.403060482698422</v>
+        <v>-3.337387452802744</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-12.59089586969168</v>
+        <v>-12.52542126670541</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-10.23876200174571</v>
+        <v>-10.17236995059576</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-13.64231664726427</v>
+        <v>-13.57558139534883</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-10.47580058224163</v>
+        <v>-10.40909421343413</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-11.24963599301106</v>
+        <v>-11.18200988947062</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-7.850276725895725</v>
+        <v>-7.782950247308698</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-5.004370629370626</v>
+        <v>-4.936699650756694</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-3.00386184785777</v>
+        <v>-2.934861717612812</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>3.024781341107875</v>
+        <v>3.094059405940598</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-3.884149897929426</v>
+        <v>-3.81408389163996</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-9.539089848308045</v>
+        <v>-9.469696969696969</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.2981835424570107</v>
+        <v>-0.2286141066744847</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-3.528166958552291</v>
+        <v>-3.458454810495667</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>2.937956204379567</v>
+        <v>3.007436570428702</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>0</v>
+        <v>0.06928238039672863</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>5.706799591002046</v>
+        <v>5.776736212430698</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>8.755844535359394</v>
+        <v>8.825890251021555</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>5.905619701841651</v>
+        <v>5.975364963503736</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>8.954678362573141</v>
+        <v>9.024532710280418</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.06912</t>
+          <t>X ≈ 0.0691</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>27</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.881434149804761</v>
+        <v>1.91470844212359</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-2.157445068543275</v>
+        <v>-2.123772059929934</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-7.300849236333114</v>
+        <v>-7.265494812664627</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>10.5038759689923</v>
+        <v>10.5400696864112</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>6.434902480264498</v>
+        <v>6.500575510160175</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>6.622067093271284</v>
+        <v>6.687541696257554</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>13.25660836862466</v>
+        <v>13.32300041977461</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>12.9780537231061</v>
+        <v>13.04478897502153</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>9.315866084425025</v>
+        <v>9.382572453232527</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>1.134623266248191</v>
+        <v>1.202249369788632</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>5.112686237067237</v>
+        <v>5.180012715654264</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>4.833592333592335</v>
+        <v>4.901263312206268</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>14.82021222621631</v>
+        <v>14.88921235646126</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>3.487744304070787</v>
+        <v>3.55702236890351</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>6.532516768737231</v>
+        <v>6.602582775026697</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>7.127576818358612</v>
+        <v>7.196969696969688</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.4139242831976588</v>
+        <v>-0.3443548474151328</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>3.184796004410771</v>
+        <v>3.254508152467395</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.3027845363611803</v>
+        <v>-0.2333041703120458</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.1157407407407476</v>
+        <v>-0.04645836034401896</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-4.362644853442397</v>
+        <v>-4.292708232013744</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-4.43859990908495</v>
+        <v>-4.368554193422789</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.4601210388991817</v>
+        <v>-0.3903757772370966</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>6.871345029239713</v>
+        <v>6.94119937694699</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.07174</t>
+          <t>X ≈ 0.07172</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>24</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-7.840788072417467</v>
+        <v>-7.807513780098638</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-12.34263025372849</v>
+        <v>-12.30895724511515</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-9.615664051147931</v>
+        <v>-9.580309627479444</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.99612403100781</v>
+        <v>-1.959930313588906</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-6.528060482698464</v>
+        <v>-6.462387452802787</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-2.17422920302495</v>
+        <v>-2.108754600038679</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1.219571331587687</v>
+        <v>1.285963382737634</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.9410166860690694</v>
+        <v>1.007751937984501</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>13.48253275109177</v>
+        <v>13.54923911989927</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>4.375364006988995</v>
+        <v>4.442990110529436</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.4830566074376108</v>
+        <v>0.5503830860246381</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-3.962703962703962</v>
+        <v>-3.89503298409003</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>3.24613815214223</v>
+        <v>3.315138282387188</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-5.308551992225397</v>
+        <v>-5.239273927392674</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-1.80081656459609</v>
+        <v>-1.730750558306624</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-9.539089848308045</v>
+        <v>-9.469696969696969</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-9.673183542456911</v>
+        <v>-9.603614106674385</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-13.94483362521886</v>
+        <v>-13.87512147716223</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-13.72871046228704</v>
+        <v>-13.65923009623791</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-13.54166666666667</v>
+        <v>-13.47238428626994</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-14.08486707566463</v>
+        <v>-14.01493045423597</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-14.16082213130723</v>
+        <v>-14.09077641564507</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-5.55271363149177</v>
+        <v>-5.482968369829685</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>2.704678362573098</v>
+        <v>2.774532710280376</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.07436</t>
+          <t>X ≈ 0.07434</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>11.03176094719038</v>
+        <v>8.859152886568033</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-6.950473390983312</v>
+        <v>-3.975623911781739</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>3.37453202728345</v>
+        <v>7.086357039187227</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2.660738714090293</v>
+        <v>0.1234030197444866</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-3.586884012110275</v>
+        <v>-6.462387452802787</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-9.282072340280038</v>
+        <v>-6.27542126670545</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-10.05493847233407</v>
+        <v>-7.047369950595801</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>1.431212764500444</v>
+        <v>5.174418604651166</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-16.17432999400642</v>
+        <v>-13.53409421343422</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-5.183459522422993</v>
+        <v>-1.807009889470621</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-16.67380613766043</v>
+        <v>-14.0329502473087</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-5.18819415878248</v>
+        <v>-1.811699650756694</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-12.19503831844592</v>
+        <v>-15.43486171761281</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>5.230663694048964</v>
+        <v>3.094059405940513</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>4.571732455011748</v>
+        <v>2.43591610836004</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>5.166792504633044</v>
+        <v>3.030303030302946</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.8496541306924286</v>
+        <v>-3.353614106674527</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.9546375467875379</v>
+        <v>-3.458454810495624</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-6.620867325032364</v>
+        <v>-9.492563429571383</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-6.433823529411761</v>
+        <v>-9.305717619603271</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-6.977023938409637</v>
+        <v>-9.848263787569216</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-7.052978994052417</v>
+        <v>-9.924109748978488</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-12.66055676874659</v>
+        <v>-15.89963503649635</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-12.73649810801506</v>
+        <v>-15.97546728971962</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.07698</t>
+          <t>X ≈ 0.07696</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.1720324404029938</v>
+        <v>3.502010029425129</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>15.2214723103741</v>
+        <v>10.31009037393251</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>13.78177184628797</v>
+        <v>8.872071324901519</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>13.06797853309475</v>
+        <v>15.30197444831586</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>20.39501644037851</v>
+        <v>22.10904111862578</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>20.5821810533853</v>
+        <v>15.15315016186597</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>27.50162261363896</v>
+        <v>21.52405862083277</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>27.22306796812029</v>
+        <v>21.24584717607969</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>19.5722763408353</v>
+        <v>14.1444772151373</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>34.18305631468134</v>
+        <v>27.65727582481499</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>34.45741558179664</v>
+        <v>27.93133546697707</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>34.17832167832178</v>
+        <v>27.65258606352901</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>25.36152276752679</v>
+        <v>26.52942399667295</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>25.1401659564926</v>
+        <v>26.30834512022642</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>24.48123471745519</v>
+        <v>25.65020182264575</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>25.07629476707668</v>
+        <v>26.24458874458885</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>17.24989338062007</v>
+        <v>18.96781446475413</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>9.452602272216865</v>
+        <v>11.72011661807571</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-5.715889949466479</v>
+        <v>-2.349706286714159</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-13.22115384615385</v>
+        <v>-9.305717619603271</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-13.76435425515191</v>
+        <v>-9.848263787569401</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-13.8403093107943</v>
+        <v>-9.924109748978303</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-5.873226452004587</v>
+        <v>-2.506777893639111</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-13.64147548358086</v>
+        <v>-9.725467289719624</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.07961</t>
+          <t>X ≈ 0.07958</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>7</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>3.468735737106442</v>
+        <v>3.502010029425271</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>3.133560222462016</v>
+        <v>3.167233231075357</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-12.5918545273385</v>
+        <v>-12.55650010367002</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-13.30564784053146</v>
+        <v>-13.26945412311255</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.6147966601586745</v>
+        <v>0.6804696900543519</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.8019612731654604</v>
+        <v>0.8674358761517311</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-14.25661914460285</v>
+        <v>-14.1902270934529</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-14.53517379012131</v>
+        <v>-14.46843853820587</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-28.77937201081306</v>
+        <v>-28.71266564200556</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-15.2674931358681</v>
+        <v>-15.19986703232766</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>13.57829470267561</v>
+        <v>13.64562118126263</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.9865134865134877</v>
+        <v>-0.918842507899555</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-2.11100470500083</v>
+        <v>-2.042004574755872</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-16.61807580174927</v>
+        <v>-16.54879773691655</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>11.2944215306421</v>
+        <v>11.36448753693157</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>11.88948158026339</v>
+        <v>11.95887445887446</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>11.75538788611456</v>
+        <v>11.82495732189709</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-2.635309815695109</v>
+        <v>-2.565597667638485</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-2.419186652763294</v>
+        <v>-2.349706286714159</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-16.51785714285715</v>
+        <v>-16.44857476246042</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-31.34677183756938</v>
+        <v>-31.27683521614073</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-17.13701260749771</v>
+        <v>-17.06696689183555</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-2.576523155301494</v>
+        <v>-2.506777893639409</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>11.63324979114453</v>
+        <v>11.70310413885181</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.08223</t>
+          <t>X ≈ 0.0822</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>7</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>3.468735737106343</v>
+        <v>3.502010029425172</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>3.133560222462016</v>
+        <v>3.167233231075357</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-12.5918545273383</v>
+        <v>-12.55650010366981</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-13.30564784053156</v>
+        <v>-13.26945412311266</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-13.67091762555561</v>
+        <v>-13.60524459565993</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.8019612731655599</v>
+        <v>0.8674358761518306</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.029095141111533</v>
+        <v>0.09548719226147995</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.2494595044071275</v>
+        <v>-0.1827242524916954</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>14.0777708463298</v>
+        <v>14.1444772151373</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.9817788501540221</v>
+        <v>-0.9141527466135813</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.7074195830385861</v>
+        <v>-0.6400931044515588</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>27.58491508491508</v>
+        <v>27.65258606352901</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>26.46042386642794</v>
+        <v>26.5294239966729</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>26.23906705539358</v>
+        <v>26.30834512022631</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>11.294421530642</v>
+        <v>11.36448753693147</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-2.396232705450807</v>
+        <v>-2.326839826839731</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-2.530326399599929</v>
+        <v>-2.460756963817403</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-2.635309815695109</v>
+        <v>-2.565597667638485</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>11.8665276329509</v>
+        <v>11.93600799900003</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>12.05357142857133</v>
+        <v>12.12285380896806</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>25.79608530528775</v>
+        <v>25.86602192671641</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>11.43441596393087</v>
+        <v>11.50446167959303</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>25.99490541612727</v>
+        <v>26.06465067778936</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>25.91896407685881</v>
+        <v>25.98881842456608</v>
       </c>
     </row>
   </sheetData>
@@ -3184,79 +3184,79 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3332</v>
+        <v>3336</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.006951619584526725</v>
+        <v>0.006071612379287217</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.01574780232401451</v>
+        <v>0.01484660638379864</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.09558253211024947</v>
+        <v>-0.09639541836416043</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.2260365210634347</v>
+        <v>-0.2267161697668385</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.126986176521207</v>
+        <v>-0.1285573484808822</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.2513436308857067</v>
+        <v>-0.2527617556738022</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.2311104639732378</v>
+        <v>-0.2325772276610749</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.1641207093909074</v>
+        <v>-0.1656768607426216</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.01400372011868711</v>
+        <v>0.01223524046022817</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.03435982288852557</v>
+        <v>0.03254234933535116</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.1766291037006837</v>
+        <v>0.1746490360594706</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.2438351122561713</v>
+        <v>0.2417651043209688</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.3931617836109709</v>
+        <v>0.3908777505676468</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.4589524961048852</v>
+        <v>0.4565818207642707</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.476445732121455</v>
+        <v>0.4740327002882907</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>0.5507305109733878</v>
+        <v>0.548245614035082</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.6143276884504871</v>
+        <v>0.6117613046327648</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0.6172794165226421</v>
+        <v>0.6147049740645159</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.6716990872084594</v>
+        <v>0.6690648254421703</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.6969424460431668</v>
+        <v>0.6942823803967286</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>0.7114847484233309</v>
+        <v>0.7087892223138965</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>0.6837089624740145</v>
+        <v>0.6810430371210572</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>0.7066623061019897</v>
+        <v>0.7039759913729995</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>0.7088800432453652</v>
+        <v>0.7061873865393693</v>
       </c>
     </row>
     <row r="7">
@@ -3266,79 +3266,79 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3242</v>
+        <v>3246</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.1084207075723356</v>
+        <v>0.1064762270391171</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.1573697462715415</v>
+        <v>0.1553430404825988</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.0520752480654707</v>
+        <v>0.05008523018814515</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.000926810488650176</v>
+        <v>-0.002898266232236324</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.203003608071235</v>
+        <v>0.1991745686367281</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.2235213082224305</v>
+        <v>0.219676772510276</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.5419606125531615</v>
+        <v>0.5376744870383234</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.7415077849027014</v>
+        <v>0.7369569247002161</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.8622789387899843</v>
+        <v>0.857580119592555</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.8741355057604352</v>
+        <v>0.8693704786275447</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.9822885582824625</v>
+        <v>0.9774056900954093</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>1.059320212669945</v>
+        <v>1.054322448690826</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>1.244139996593503</v>
+        <v>1.238841076369383</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>1.225888352177982</v>
+        <v>1.220595032476226</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>1.262343488720838</v>
+        <v>1.256960655211039</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>1.322448613230421</v>
+        <v>1.317027062263691</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>1.330202114668296</v>
+        <v>1.32475970211744</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>1.244000529132485</v>
+        <v>1.238654660599082</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>1.263333475706943</v>
+        <v>1.257974866337655</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>1.315080098582868</v>
+        <v>1.309666995781342</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>1.437731794391873</v>
+        <v>1.432130179805277</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>1.319038123522198</v>
+        <v>1.313574980085633</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>1.304363149266791</v>
+        <v>1.298932872342576</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>1.216399522351004</v>
+        <v>1.211069986928557</v>
       </c>
     </row>
     <row r="8">
@@ -3348,79 +3348,79 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3058</v>
+        <v>3062</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.08762351545543368</v>
+        <v>-0.0914143743720004</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.04914463804643532</v>
+        <v>0.04512835799772574</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.2509051812868535</v>
+        <v>0.2464283982530731</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.3674237272768437</v>
+        <v>0.3626956868437787</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.4105160528881484</v>
+        <v>0.4022668802059783</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.5511717505944134</v>
+        <v>0.5427605514764124</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1.032579461668924</v>
+        <v>1.023432257913498</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.260903912267295</v>
+        <v>1.251416655333429</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.288965119027488</v>
+        <v>1.279441698168071</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>1.250364006988939</v>
+        <v>1.240779447330425</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1.283555901912813</v>
+        <v>1.273960321796991</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>1.251736862486048</v>
+        <v>1.242138995957689</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>1.482534372409418</v>
+        <v>1.472476388472444</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>1.37875787305051</v>
+        <v>1.368798989273934</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>1.489586652445539</v>
+        <v>1.479387290385439</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>1.61550897752366</v>
+        <v>1.605221597078284</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>1.795005690821988</v>
+        <v>1.784460184625658</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>1.775357845625301</v>
+        <v>1.764817679726015</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>1.717747258901284</v>
+        <v>1.707306149822244</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>1.859487263226647</v>
+        <v>1.848881206228434</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>2.055010959835762</v>
+        <v>2.044069001990245</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>1.933949110522839</v>
+        <v>1.92314873666129</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>1.967445461893867</v>
+        <v>1.95663332785233</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>1.977078624181992</v>
+        <v>1.966237478405787</v>
       </c>
     </row>
     <row r="9">
@@ -3430,79 +3430,79 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2789</v>
+        <v>2794</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.02431387163185406</v>
+        <v>-0.002224465224657024</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.04273697731436954</v>
+        <v>-0.06937391178178132</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.004157526830020686</v>
+        <v>0.003763788743178509</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.1205841688261202</v>
+        <v>0.1278450950820798</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.3095463549083703</v>
+        <v>0.2741927107236961</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.6238351598772596</v>
+        <v>0.5880211230527692</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.6196663660376203</v>
+        <v>0.5833664421470388</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.8964534062116698</v>
+        <v>0.8594719854340767</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.9230938542776244</v>
+        <v>0.9216729634971585</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.883569501102393</v>
+        <v>0.8817365492758142</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.8934777352034899</v>
+        <v>0.8917914698270408</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.6353562538853552</v>
+        <v>0.6339525231563528</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.8889952949993685</v>
+        <v>0.8864395301590235</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.8677609766920114</v>
+        <v>0.8651007754127775</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>1.052411931949059</v>
+        <v>1.049009222880194</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>1.133058882474934</v>
+        <v>1.129874764778407</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>1.342553224352756</v>
+        <v>1.338906421708273</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>1.402512826778704</v>
+        <v>1.398688046647237</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>1.568951193642278</v>
+        <v>1.564957113479792</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>1.921097386322948</v>
+        <v>1.916584024428182</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>1.901283831689732</v>
+        <v>1.89646270510142</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>1.775819454743164</v>
+        <v>1.735403841865661</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>1.857680633741204</v>
+        <v>1.853048326652129</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>1.839672984301323</v>
+        <v>1.835019467617528</v>
       </c>
     </row>
     <row r="10">
@@ -3512,325 +3512,325 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2493</v>
+        <v>2498</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.1414588804177228</v>
+        <v>0.1473321804990135</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.0530344949478021</v>
+        <v>-0.04705248321035782</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.239148995789229</v>
+        <v>0.2433637878970316</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.1444118490824451</v>
+        <v>0.1482243064799889</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.319073275263321</v>
+        <v>0.3115497740545834</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.6483514421362813</v>
+        <v>0.6403180019750323</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.4559591137921473</v>
+        <v>0.447659870477807</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.6786279521777416</v>
+        <v>0.6696453349614302</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.4641914432767109</v>
+        <v>0.4556590694946436</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.3117421481935665</v>
+        <v>0.3028627219943516</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.3300903930188781</v>
+        <v>0.3213906527311323</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.07422218500062883</v>
+        <v>0.06579038908394352</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.1311221777013358</v>
+        <v>0.1216348945832806</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.05334706224251562</v>
+        <v>0.04382017149083595</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>0.1776007015909613</v>
+        <v>0.167268322161398</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.6368397798406917</v>
+        <v>0.6260731819391054</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.8068164575430359</v>
+        <v>0.7955874901319433</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.7260347221200192</v>
+        <v>0.7148678732104443</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.8462828657086234</v>
+        <v>0.8350434421825952</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>1.217711253504206</v>
+        <v>1.205873107814789</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>1.059363693566155</v>
+        <v>1.047377955733374</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>1.047928703696108</v>
+        <v>1.035890251021598</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>1.106602059499949</v>
+        <v>1.094662682591284</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>1.055059429560664</v>
+        <v>1.043147602193905</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; 0.02061</t>
+          <t>X &gt; 0.0206</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2217</v>
+        <v>2222</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.08595021466102537</v>
+        <v>0.08849634346843516</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.1331123944279824</v>
+        <v>0.1351893143129388</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.2409667732248337</v>
+        <v>0.2412519877790871</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.114403600900232</v>
+        <v>-0.0890298961768039</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.05796102267788683</v>
+        <v>0.09242239059765467</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.4243371052187186</v>
+        <v>0.4837550985586887</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.27871111653387</v>
+        <v>0.364184012682351</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.2689736753163814</v>
+        <v>0.3546693883502243</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.08647540342145277</v>
+        <v>0.1722425532474645</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.1237395340240539</v>
+        <v>-0.06327948194710586</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.09242919226343815</v>
+        <v>-0.05791666020615338</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.2110215939287201</v>
+        <v>-0.2023176534436644</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.1425512553981605</v>
+        <v>-0.1611268318089643</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.2924615865975611</v>
+        <v>-0.3109585152063588</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.2060277056562896</v>
+        <v>-0.2254465093002054</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.1013595898942015</v>
+        <v>0.08187253702948283</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.2638668172552627</v>
+        <v>0.2438511243708774</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.3657826590815816</v>
+        <v>0.3454051535977385</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.8339958083399637</v>
+        <v>0.8127800818790831</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>1.093257541647908</v>
+        <v>1.071640870962767</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>0.8926104018128598</v>
+        <v>0.8708373360262058</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>0.8891252924572299</v>
+        <v>0.8672571574964181</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>1.056093101300533</v>
+        <v>1.034125647264332</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>1.187989142906886</v>
+        <v>1.165621819191266</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; 0.02323</t>
+          <t>X &gt; 0.02322</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1965</v>
+        <v>1969</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.1409367044058456</v>
+        <v>0.1160868250450946</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.06591977176013586</v>
+        <v>-0.09065922964252593</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.06204746035378861</v>
+        <v>-0.08804982603236056</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.134629636164739</v>
+        <v>0.1360292823707425</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.3763401242818105</v>
+        <v>0.3845049170809958</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.5635047372885964</v>
+        <v>0.6002106847607251</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.7011090149462547</v>
+        <v>0.7675010660962016</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.8272078848551061</v>
+        <v>0.8939431367705382</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.12163239701988</v>
+        <v>1.188338765827382</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1.410012464247416</v>
+        <v>1.477638567787857</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.583208352505892</v>
+        <v>1.650534831092919</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.506441206744697</v>
+        <v>1.574112185358629</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>1.677312241211062</v>
+        <v>1.71549235421319</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.436173746171164</v>
+        <v>1.443831788338173</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>1.365343516457607</v>
+        <v>1.3420870744703</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>1.687468691985927</v>
+        <v>1.632983859842732</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>1.787262705007535</v>
+        <v>1.732418281989524</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>2.017875659408176</v>
+        <v>1.962431265453745</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>2.620697321130841</v>
+        <v>2.564174159081176</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>2.839321990858302</v>
+        <v>2.782472953128611</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>2.530986582871968</v>
+        <v>2.47425142541244</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>2.690135333529241</v>
+        <v>2.632967876592375</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>3.047659376307486</v>
+        <v>2.989958872133094</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>3.20722289183518</v>
+        <v>3.149088322266159</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; 0.02585</t>
+          <t>X &gt; 0.02584</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1699</v>
+        <v>1706</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.1925532372311949</v>
+        <v>-0.2608937334785821</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.7891564051726405</v>
+        <v>-0.73947230828324</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.2967725601252909</v>
+        <v>-0.2794539293075218</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.6007298077446777</v>
+        <v>-0.5515823859764737</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.08777945225349981</v>
+        <v>-0.09556502289625257</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.2164811794886461</v>
+        <v>0.241235659068991</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.146548886991603</v>
+        <v>-0.1215955496606327</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.1909114950394368</v>
+        <v>-0.1660255800361554</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.08479660745392437</v>
+        <v>0.1092430162561158</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.1306333278320366</v>
+        <v>0.1545622905410653</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.3464445855796825</v>
+        <v>0.4286219327029883</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.6528307757815952</v>
+        <v>0.7343260651988857</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.109135810221851</v>
+        <v>1.189188545391275</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.7121349710844598</v>
+        <v>0.7927736081615251</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.9086151870149237</v>
+        <v>0.9528652609024135</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>1.304989870332051</v>
+        <v>1.313470768467845</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>1.382534932616352</v>
+        <v>1.354889692273538</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>1.665495013278736</v>
+        <v>1.600721110018689</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>2.175045406257503</v>
+        <v>2.144863471013494</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>2.222181444509687</v>
+        <v>2.192234399121126</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>2.185207346583709</v>
+        <v>2.154078132805402</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>2.322129073866201</v>
+        <v>2.290301498824753</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>2.574737348900385</v>
+        <v>2.506193903163869</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>2.712035631554855</v>
+        <v>2.642645254242858</v>
       </c>
     </row>
     <row r="14">
@@ -3840,79 +3840,79 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1507</v>
+        <v>1511</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.4024756688043354</v>
+        <v>-0.4437475748690147</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.42993184103004</v>
+        <v>-1.46902760571318</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.282330717814595</v>
+        <v>-1.288230419558644</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.070198105081822</v>
+        <v>-1.040731722659743</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.1788541334921163</v>
+        <v>-0.1504244653606222</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.3223773511731522</v>
+        <v>-0.2569027481868815</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.4338678218515284</v>
+        <v>-0.3674757707015814</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.4478722028198234</v>
+        <v>-0.3811369509043914</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.5386312700723153</v>
+        <v>-0.4719249012648135</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.7172285856036567</v>
+        <v>-0.6496024820632158</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.08623121061221894</v>
+        <v>0.1535576891992463</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.4685129685129681</v>
+        <v>0.5361839471269008</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.4683603743644511</v>
+        <v>0.5373605046094099</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.2470035633300967</v>
+        <v>0.3162816281628196</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.3817231179435865</v>
+        <v>0.4517891242330521</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>1.042920733702537</v>
+        <v>1.112313612313613</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>1.081283697781288</v>
+        <v>1.110671607611266</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>1.505750976590036</v>
+        <v>1.534931432890623</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>1.920418150110869</v>
+        <v>1.949235512227645</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>2.107461945731302</v>
+        <v>2.136081322195672</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>2.134779723452375</v>
+        <v>2.163648853066036</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>2.166215642052613</v>
+        <v>2.153984228519946</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>2.415898216430421</v>
+        <v>2.362277604138988</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>2.580258986328907</v>
+        <v>2.484989361504731</v>
       </c>
     </row>
     <row r="15">
@@ -3922,1719 +3922,1719 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1339</v>
+        <v>1344</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.7723356914650878</v>
+        <v>-0.7868812127648042</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.408403398429371</v>
+        <v>-2.417760410298101</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.986599767206499</v>
+        <v>-1.961527147895175</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.657950787026614</v>
+        <v>-1.594650472083153</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.5340172958034515</v>
+        <v>-0.477257341278623</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.016994157107909</v>
+        <v>-0.9182784095625465</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.119718814850692</v>
+        <v>-1.02058423631005</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.5792116584332874</v>
+        <v>-0.4803433001107393</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.3887752657859309</v>
+        <v>-0.3644513562912692</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.4180090384317623</v>
+        <v>-0.3933194132801461</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.526491702994818</v>
+        <v>0.5503830860246381</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.7686189462064448</v>
+        <v>0.7924670159099705</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.133331003966511</v>
+        <v>1.157400187149094</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.5396733738703432</v>
+        <v>0.564297501178693</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>1.221025083455537</v>
+        <v>1.24543991788385</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>1.741624969264556</v>
+        <v>1.765422077922075</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>1.38415078367855</v>
+        <v>1.408290655230324</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>1.72592835045743</v>
+        <v>1.749878522837712</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>2.388812496263405</v>
+        <v>2.412198475190607</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>2.426935964259123</v>
+        <v>2.450234761349115</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>2.37688155821516</v>
+        <v>2.354117164811655</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>2.720236779953019</v>
+        <v>2.650295012926364</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>3.414948060050527</v>
+        <v>3.29679353493222</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>3.460839676986836</v>
+        <v>3.295366043613711</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 0.03372</t>
+          <t>X &gt; 0.03371</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1184</v>
+        <v>1188</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.3071180387474328</v>
+        <v>-0.3690350328950487</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-2.073269984368189</v>
+        <v>-2.170418202293959</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.250344185828055</v>
+        <v>-2.304399263333778</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.70151123639495</v>
+        <v>-1.711121791020858</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.03759608295809613</v>
+        <v>0.1032691128537735</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.9536904824862944</v>
+        <v>-0.8882158795000237</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.642381530365235</v>
+        <v>-1.575989479215288</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.9108351657827924</v>
+        <v>-0.8440999138673604</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.2800935115345595</v>
+        <v>-0.2133871427270577</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.04034717197210114</v>
+        <v>0.107973275512542</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.4830566074376108</v>
+        <v>0.5503830860246381</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.7931882931882939</v>
+        <v>0.8608592718022265</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.4262728322769078</v>
+        <v>0.4952729625218666</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.03656585289238734</v>
+        <v>0.1058439177251103</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.8927861290066019</v>
+        <v>0.9628521352960675</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>1.487846178627983</v>
+        <v>1.557239057239059</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.8487019794285544</v>
+        <v>0.9182714152110805</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>1.417119236733946</v>
+        <v>1.48683138479057</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>2.306643073066439</v>
+        <v>2.376123439115574</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>2.577861952861952</v>
+        <v>2.64714433325868</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>2.423838344161268</v>
+        <v>2.441298501992996</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>2.822033405511206</v>
+        <v>2.7863279614593</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>3.740535313655911</v>
+        <v>3.650028263166952</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>3.718191876086607</v>
+        <v>3.574196009943677</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 0.03634</t>
+          <t>X &gt; 0.03633</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1019</v>
+        <v>1023</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.05376915526156267</v>
+        <v>-0.1320751836074052</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.758807683604516</v>
+        <v>-1.780501960562269</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.339408343385365</v>
+        <v>-1.312080460812773</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.368270149729213</v>
+        <v>-1.287887302836161</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.1255598695520277</v>
+        <v>0.2336047270603672</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.8614438148971573</v>
+        <v>-0.7524496147015043</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.8515310819805393</v>
+        <v>-0.7423846133523497</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.0537647881644574</v>
+        <v>0.05467275909887093</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.9662248580714774</v>
+        <v>1.073677047562938</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.464405102879354</v>
+        <v>1.571533610040625</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.738764369994691</v>
+        <v>1.845593252202548</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>2.340296689611762</v>
+        <v>2.446609244648975</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.194279052337919</v>
+        <v>2.300964284342221</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.581532808818245</v>
+        <v>1.688878565275886</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>2.096769867236908</v>
+        <v>2.203755795554564</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>2.887524633100959</v>
+        <v>2.993646138807428</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>2.166346790224047</v>
+        <v>2.273218737900336</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>1.963516016007439</v>
+        <v>2.070626323424221</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>2.962418043909899</v>
+        <v>3.068531389588038</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>3.149461839530332</v>
+        <v>3.255377199556065</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>2.801956146775048</v>
+        <v>2.908334452899908</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>3.668919951618008</v>
+        <v>3.712253887385231</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>4.006109897919991</v>
+        <v>3.986728599867284</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>4.385247548049058</v>
+        <v>4.301903189263761</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 0.03896</t>
+          <t>X &gt; 0.03895</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.3051173485744698</v>
+        <v>0.2141586403079572</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.3760789273155396</v>
+        <v>-0.4041953403532119</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.3163560926704108</v>
+        <v>-0.2810016690019239</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.4915104208578</v>
+        <v>-1.455316703438896</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.3573569071506029</v>
+        <v>-0.2916838772549255</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.9775740703837172</v>
+        <v>-0.9120994673974465</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.058398679946393</v>
+        <v>-0.992006628796446</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.2988910417279342</v>
+        <v>-0.2321557898125022</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.2039860382889316</v>
+        <v>0.2706924070964334</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.6988934187536486</v>
+        <v>0.7665195222940895</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.9732526858689852</v>
+        <v>1.040579164456013</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.616880812382547</v>
+        <v>1.68455179099648</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>2.107153146375218</v>
+        <v>2.176153276620177</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.7704560815923</v>
+        <v>1.839734146425023</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>2.034246872543477</v>
+        <v>2.104312878832943</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>2.513966668416295</v>
+        <v>2.583359547027371</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>1.572491198027457</v>
+        <v>1.642060633809983</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>1.698188289429289</v>
+        <v>1.767900437485913</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>2.260332213606787</v>
+        <v>2.329812579655922</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>2.101355247981537</v>
+        <v>2.170637628378266</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>1.558154838983583</v>
+        <v>1.628091460412236</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>2.476976175082299</v>
+        <v>2.474967528991613</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>3.055186175830002</v>
+        <v>2.980122748970786</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>3.514863547758281</v>
+        <v>3.365651510741742</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 0.04158</t>
+          <t>X &gt; 0.04157</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.7376433001315519</v>
+        <v>0.6982717116681627</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.6670509310903086</v>
+        <v>-0.6333779224769671</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.1014038015935625</v>
+        <v>-0.0660493779250757</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.483646312647686</v>
+        <v>-1.447452595228782</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.6457075415219933</v>
+        <v>-0.5800345116263159</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.260681965948365</v>
+        <v>-1.195207362962094</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.231409060569234</v>
+        <v>-1.165017009419287</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.1730653103658781</v>
+        <v>-0.1063300584504461</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.1358304338011465</v>
+        <v>0.2025368026086483</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.9662730978980321</v>
+        <v>1.033899201438473</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.240632365013369</v>
+        <v>1.307958843600396</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.897367338543809</v>
+        <v>1.965038317157742</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.37715419492298</v>
+        <v>2.446154325167939</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.289487223460817</v>
+        <v>2.35876528829354</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>2.432695021856667</v>
+        <v>2.502761028146132</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>2.894065231905863</v>
+        <v>2.963458110516939</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>2.358902019040364</v>
+        <v>2.428471454822891</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>2.120228763372886</v>
+        <v>2.18994091142951</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>2.871111284593475</v>
+        <v>2.94059165064261</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>2.657085561497333</v>
+        <v>2.726367941894061</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>2.113885152499378</v>
+        <v>2.183821773928031</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>2.572689455145529</v>
+        <v>2.64273517080769</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>3.600566154318138</v>
+        <v>3.585659081150709</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>3.743552357211165</v>
+        <v>3.643516667499625</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.04421</t>
+          <t>X &gt; 0.04419</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.1233469486795826</v>
+        <v>0.07163313933264703</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.421082826440319</v>
+        <v>0.4547558350536605</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.2472051471643084</v>
+        <v>0.2825595708327953</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.099499558433905</v>
+        <v>-1.063305841015001</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.1989465586478332</v>
+        <v>-0.1332735287521558</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.8029211861473797</v>
+        <v>-0.737446583161109</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.101103773897606</v>
+        <v>-1.034711722747659</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.430291330808565</v>
+        <v>-0.3635560788931329</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.5470031138872002</v>
+        <v>-0.4802967450796984</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.5778956525585599</v>
+        <v>0.6455217560990008</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.168710615876428</v>
+        <v>1.236037094463455</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.997211649110383</v>
+        <v>2.064882627724316</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>2.296771063534628</v>
+        <v>2.365771193779587</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.917186404399018</v>
+        <v>1.986464469231741</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>2.524077950171844</v>
+        <v>2.594143956461309</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>2.486226607388154</v>
+        <v>2.55561948599923</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>1.719221520834175</v>
+        <v>1.788790956616701</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>1.77246595284015</v>
+        <v>1.842178100896774</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>2.305044811974504</v>
+        <v>2.374525178023639</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>1.700949367088612</v>
+        <v>1.77023174748534</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.9995211099893879</v>
+        <v>1.069457731418041</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>1.872933142954373</v>
+        <v>1.942978858616534</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>2.622391853740297</v>
+        <v>2.692137115402382</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>3.279163307105584</v>
+        <v>3.249216254584177</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.04683</t>
+          <t>X &gt; 0.04681</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.9900576987268224</v>
+        <v>1.023331991045652</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.214583676619803</v>
+        <v>1.248256685233144</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.45398769014561</v>
+        <v>1.489342113814097</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.1804928844151377</v>
+        <v>0.2166866018340414</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.9346260844657124</v>
+        <v>1.00029911436139</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.002387712397876385</v>
+        <v>0.06786231538414711</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.3973440912979456</v>
+        <v>-0.3309520401479986</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.4435042482581153</v>
+        <v>0.5102395001735474</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.1118859849225444</v>
+        <v>0.1785923537300462</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.203722215944161</v>
+        <v>1.271348319484602</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.037782975596812</v>
+        <v>2.10510945418384</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>3.437793549733847</v>
+        <v>3.50546452834778</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>3.619272480500435</v>
+        <v>3.688272610745393</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>3.39791566946608</v>
+        <v>3.467193734298803</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>4.044954579682518</v>
+        <v>4.115020585971983</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>3.52061164422927</v>
+        <v>3.590004522840346</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>2.453682129184827</v>
+        <v>2.523251564967353</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>2.162131548910438</v>
+        <v>2.231843696967061</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>2.378254711842253</v>
+        <v>2.447735077891387</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>1.819029850746269</v>
+        <v>1.888312231142997</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>1.089262277569205</v>
+        <v>1.159198898997857</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>1.946143042822122</v>
+        <v>2.016188758484283</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>2.220918209304251</v>
+        <v>2.290663470966336</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>3.382248456031043</v>
+        <v>3.33423420281769</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.04945</t>
+          <t>X &gt; 0.04944</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>465</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.7344807447868362</v>
+        <v>0.7677550371056654</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.6143589935833731</v>
+        <v>0.6480320021967145</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.110142400464973</v>
+        <v>1.14549682413346</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.4638659664916176</v>
+        <v>-0.4276722490727138</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.106348119452072</v>
+        <v>1.172021149347749</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.4332976786954177</v>
+        <v>0.4987722816816884</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.5206466004048309</v>
+        <v>0.5870386515547779</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.672199481767997</v>
+        <v>0.7389347336834291</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.1464995069728161</v>
+        <v>-0.0797931381653143</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.015148953225498</v>
+        <v>1.082775056765939</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.719615747222555</v>
+        <v>1.786942225809582</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.730844424392821</v>
+        <v>2.798515403006753</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>3.111729549991693</v>
+        <v>3.180729680236652</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.890372738957339</v>
+        <v>2.959650803790062</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>3.736817844006055</v>
+        <v>3.80688385029552</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>3.471662839864003</v>
+        <v>3.541055718475079</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>2.692407855392496</v>
+        <v>2.761977291175022</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>2.372370675856352</v>
+        <v>2.442082823912976</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>1.943332548465591</v>
+        <v>2.012812914514726</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>1.700268817204297</v>
+        <v>1.769551197601025</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.9420146447654929</v>
+        <v>1.011951266194146</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>2.586489696649764</v>
+        <v>2.656535412311925</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>2.861264863131893</v>
+        <v>2.931010124793978</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>3.645538577626859</v>
+        <v>3.715392925334136</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.05207</t>
+          <t>X &gt; 0.05206</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.387606989310932</v>
+        <v>1.531566679671478</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.3116907339258645</v>
+        <v>0.4578736251640265</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.847298911815038</v>
+        <v>0.7439925071675191</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.1335055986218805</v>
+        <v>0.03103848772477846</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.990458035820048</v>
+        <v>1.911996783650416</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.6961411673453597</v>
+        <v>0.6211304574325283</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.8174657054494077</v>
+        <v>-0.8897344826154665</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.1083660299803171</v>
+        <v>-0.1827242524916954</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.5606771254515124</v>
+        <v>-0.6338479080154116</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.134623266248191</v>
+        <v>1.056290603140219</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>2.396636854351193</v>
+        <v>2.315571920178989</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3.105197271863943</v>
+        <v>3.02204419160784</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3.215273954611362</v>
+        <v>3.130409218347772</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.734657884317748</v>
+        <v>3.648246598058826</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>4.557208126761928</v>
+        <v>4.467935812793534</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>4.164613855395665</v>
+        <v>4.077101059859679</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>3.04286584025909</v>
+        <v>2.957962248005359</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>3.184796004410714</v>
+        <v>3.099426962903387</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>2.413264846354878</v>
+        <v>2.330096668950866</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>2.106481481481481</v>
+        <v>2.024331641480472</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>1.563281072483527</v>
+        <v>1.481785473514442</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>3.21572107856931</v>
+        <v>3.130077443139825</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>3.243582664804528</v>
+        <v>3.158246736902662</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>4.155295646523719</v>
+        <v>4.06763615855624</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.05469</t>
+          <t>X &gt; 0.05468</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.662957245934592</v>
+        <v>1.541225715699689</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.07671265073220468</v>
+        <v>-0.1941113067397637</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.1689801436086285</v>
+        <v>0.048541913136809</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.5787823360334556</v>
+        <v>0.4560360729657731</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2.460703562245357</v>
+        <v>2.361141958961923</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.6815760404206799</v>
+        <v>0.5873238313338049</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.776683350060317</v>
+        <v>-1.865297121464103</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.369844737151908</v>
+        <v>-0.4628362973096216</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.328328672129274</v>
+        <v>-0.4213491153949178</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.8641280519327594</v>
+        <v>0.7665195222940895</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>2.542981701070566</v>
+        <v>2.441139388545643</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>4.23017993242712</v>
+        <v>4.123174298823137</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>5.352879725175946</v>
+        <v>5.240908590510436</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4.850624037737084</v>
+        <v>4.73971766924592</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>5.315288304317768</v>
+        <v>5.202022550937066</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>5.629449477534656</v>
+        <v>5.516297428062131</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>4.933558030576748</v>
+        <v>4.822156201448806</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>4.266776861672469</v>
+        <v>4.157091407991764</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>4.202001148199784</v>
+        <v>4.092870744098164</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>4.108146067415731</v>
+        <v>3.999604509248265</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>4.126743411226762</v>
+        <v>4.017282430918087</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>5.45528273760663</v>
+        <v>5.341996693598624</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>5.16826015127976</v>
+        <v>5.056247316444825</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>6.49681319403377</v>
+        <v>6.38097528731118</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.05732</t>
+          <t>X &gt; 0.0573</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>305</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.391452364741006</v>
+        <v>2.424726657059836</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.400539145178648</v>
+        <v>1.434212153791989</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.600182943387594</v>
+        <v>1.635537367056081</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.869996187571488</v>
+        <v>1.906189904990391</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.471939517301536</v>
+        <v>3.537612547197213</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.364022163095214</v>
+        <v>1.429496766081485</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.7203193787948905</v>
+        <v>-0.6539273276449435</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.01526746693640035</v>
+        <v>0.05146778497903171</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.0262485980862337</v>
+        <v>0.0929549668937355</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.5638885971528751</v>
+        <v>0.6315147006933159</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1.166116716727224</v>
+        <v>1.233443195314251</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>2.854235928006418</v>
+        <v>2.92190690662035</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4.024826676732395</v>
+        <v>4.093826806977354</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>4.45920757061608</v>
+        <v>4.528485635448803</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>4.456014036496803</v>
+        <v>4.526080042786269</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>4.39533638120016</v>
+        <v>4.464729259811236</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>3.605504982133198</v>
+        <v>3.675074417915724</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>3.500521566037918</v>
+        <v>3.570233714094542</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>3.060907024051694</v>
+        <v>3.130387390100829</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>2.592213114754095</v>
+        <v>2.661495495150824</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>3.360488115592211</v>
+        <v>3.430424737020864</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>4.268139617326646</v>
+        <v>4.338185332988807</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>5.526521341185834</v>
+        <v>5.596266602847919</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>7.089924264212449</v>
+        <v>7.159778611919727</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.05994</t>
+          <t>X &gt; 0.05992</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>273</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.003534271904883</v>
+        <v>2.036808564223712</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.668358757260556</v>
+        <v>1.702031765873897</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.060160124676244</v>
+        <v>2.095514548344731</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.811568276684561</v>
+        <v>2.847761994103465</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>4.277800323162339</v>
+        <v>4.343473353058016</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.267162738366935</v>
+        <v>2.332637341353205</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.3953955074117985</v>
+        <v>0.4617875585617455</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.582042327094712</v>
+        <v>1.648777579010144</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.257258025816981</v>
+        <v>1.323964394624483</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>2.314924446549377</v>
+        <v>2.382550550089817</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>3.32188444626545</v>
+        <v>3.389210924852478</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>4.874292374292374</v>
+        <v>4.941963352906306</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>6.680204086208157</v>
+        <v>6.749204216453116</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>6.458847275173802</v>
+        <v>6.528125340006525</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>6.532516768737231</v>
+        <v>6.602582775026697</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>5.662375353157152</v>
+        <v>5.731768231768228</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>4.063080193806762</v>
+        <v>4.132649629589288</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>4.324397144011854</v>
+        <v>4.394109292068478</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>3.807919574342932</v>
+        <v>3.877399940392067</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>3.628663003663</v>
+        <v>3.697945384059729</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>3.818063327265776</v>
+        <v>3.887999948694429</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>5.207309736824634</v>
+        <v>5.277355452486795</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>6.580986002207858</v>
+        <v>6.650731263869943</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>8.33654649444123</v>
+        <v>8.406400842148507</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.06256</t>
+          <t>X &gt; 0.06254</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>235</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.496091360206655</v>
+        <v>2.529365652525485</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.03325627109423834</v>
+        <v>0.06692927970757978</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.2956834665825738</v>
+        <v>0.3310378902510607</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.709549727857492</v>
+        <v>1.745743445276396</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3.046407602407918</v>
+        <v>3.112080632303595</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.2548488111593912</v>
+        <v>0.3203234141456619</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.3330465088926005</v>
+        <v>0.3994385600425474</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.182151437842116</v>
+        <v>2.248886689757548</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.798135587971132</v>
+        <v>1.864841956778633</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.875364006988939</v>
+        <v>1.942990110529379</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.724191359210657</v>
+        <v>1.791517837797684</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>3.572757030203839</v>
+        <v>3.640428008817771</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>4.575925386184785</v>
+        <v>4.644925516429744</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>6.056696234724889</v>
+        <v>6.125974299557612</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>4.546701165900366</v>
+        <v>4.616767172189832</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>3.439633555947275</v>
+        <v>3.509026434558351</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>1.603412202223879</v>
+        <v>1.672981638006405</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>1.498428786128599</v>
+        <v>1.568140934185223</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>1.714551949060414</v>
+        <v>1.784032315109549</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>1.050531914893618</v>
+        <v>1.119814295290347</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>1.783927250576511</v>
+        <v>1.853863872005164</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>3.410099854508374</v>
+        <v>3.480145570170535</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>5.387002680564969</v>
+        <v>5.456747942227054</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>7.864252830658209</v>
+        <v>7.934107178365487</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.06518</t>
+          <t>X &gt; 0.06516</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>196</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.448327573841034</v>
+        <v>2.481601866159863</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.4378683489665534</v>
+        <v>-0.4041953403532119</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.346956568154738</v>
+        <v>-0.3116021444862511</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2.00047460844803</v>
+        <v>2.036668325866934</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>3.16581706832195</v>
+        <v>3.231490098217627</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.822369436430769</v>
+        <v>1.88784403941704</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>3.090319630907359</v>
+        <v>3.156711682057306</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>5.362785393552059</v>
+        <v>5.429520645467491</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>5.404301458574693</v>
+        <v>5.471007827382195</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>4.630466047805264</v>
+        <v>4.698092151345705</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>4.9048253149206</v>
+        <v>4.972151793507628</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>6.666547737976316</v>
+        <v>6.734218716590249</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>9.113485090917742</v>
+        <v>9.1824852211627</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>9.402332361516038</v>
+        <v>9.471610426348761</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>7.722992959213435</v>
+        <v>7.793058965502901</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>5.767032600671548</v>
+        <v>5.836425479282624</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>4.102326661624666</v>
+        <v>4.171896097407192</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>2.976935082264077</v>
+        <v>3.046647230320701</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>3.70326232682855</v>
+        <v>3.772742692877685</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>2.359693877551017</v>
+        <v>2.428976257947745</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>2.836901631818371</v>
+        <v>2.906838253247024</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>5.31196698433903</v>
+        <v>5.382012700001191</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>7.117354395719126</v>
+        <v>7.187099657381211</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>9.592433464613912</v>
+        <v>9.662287812321189</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.06781</t>
+          <t>X &gt; 0.06779</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>164</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.813683472297988</v>
+        <v>1.846957764616818</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-2.789784725273172</v>
+        <v>-2.756111716659831</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-1.790460799115401</v>
+        <v>-1.755106375446914</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2.983550765740212</v>
+        <v>3.019744483159116</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>4.447549273399098</v>
+        <v>4.513222303294775</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>4.634713886405883</v>
+        <v>4.700188489392154</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>5.691116047034782</v>
+        <v>5.757508098184729</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>9.07109798688208</v>
+        <v>9.137833238797512</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>8.502857954343739</v>
+        <v>8.569564323151241</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>7.72902254357431</v>
+        <v>7.79664864711475</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>7.393625713128671</v>
+        <v>7.460952191715698</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>8.943800102336695</v>
+        <v>9.011471080950628</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>11.4778454692154</v>
+        <v>11.54684559946036</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>10.64673256062007</v>
+        <v>10.7160106254528</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>9.987801321582772</v>
+        <v>10.05786732787224</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>8.753593078521227</v>
+        <v>8.822985957132303</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>4.960962799006452</v>
+        <v>5.030532234788978</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>4.246223285350197</v>
+        <v>4.315935433406821</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>3.85259035072103</v>
+        <v>3.922070716770165</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>2.820121951219512</v>
+        <v>2.889404331616241</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>2.276921542221558</v>
+        <v>2.346858163650211</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>4.639990876822857</v>
+        <v>4.710036592485018</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>7.353790433548888</v>
+        <v>7.423535695210973</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>9.716873484524307</v>
+        <v>9.786727832231584</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.07043</t>
+          <t>X &gt; 0.07041</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>137</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1.800331148993727</v>
+        <v>1.833605441312557</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-2.914406409446215</v>
+        <v>-2.880733400832874</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.704471837036003</v>
+        <v>-0.6691174133675162</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1.501442878967914</v>
+        <v>1.537636596386818</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>4.055881123140956</v>
+        <v>4.121554153036634</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>4.243045736147742</v>
+        <v>4.308520339134013</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>4.200106611392982</v>
+        <v>4.266498662542929</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>8.301114009670044</v>
+        <v>8.367849261585476</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>8.342630074692678</v>
+        <v>8.40933644350018</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>9.028648678521783</v>
+        <v>9.096274782062224</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>7.843153931038586</v>
+        <v>7.910480409625613</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>9.753841049461485</v>
+        <v>9.821512028075418</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>10.81913085287216</v>
+        <v>10.88813098311712</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>12.05762805643635</v>
+        <v>12.12690612126907</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>10.66876981009977</v>
+        <v>10.73883581638923</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>9.074048837823348</v>
+        <v>9.143441716434424</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>6.020247114477343</v>
+        <v>6.089816550259869</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>4.455409683783515</v>
+        <v>4.525121831840138</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>4.67153284671533</v>
+        <v>4.741013212764464</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>3.398722627737229</v>
+        <v>3.468005008133957</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>3.585449226038541</v>
+        <v>3.655385847467194</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>6.429202199593014</v>
+        <v>6.499247915255175</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>8.893758387972959</v>
+        <v>8.963503649635044</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>10.27767106330302</v>
+        <v>10.3475254110103</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.07305</t>
+          <t>X &gt; 0.07303</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>113</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>3.848002488054512</v>
+        <v>3.881276780373341</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.911951787651752</v>
+        <v>-0.8782787790384106</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.188170757111664</v>
+        <v>1.22352518078015</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2.244288948343282</v>
+        <v>2.280482665762186</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>6.303797924381179</v>
+        <v>6.369470954276856</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>5.606006785175573</v>
+        <v>5.671481388161844</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>4.833140653121546</v>
+        <v>4.899532704271493</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>9.864320520877328</v>
+        <v>9.93105577279276</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>7.250969329262787</v>
+        <v>7.317675698070289</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>10.01695692734291</v>
+        <v>10.08458303088335</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>9.40636044224587</v>
+        <v>9.473686920832897</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>12.66708954762052</v>
+        <v>12.73476052623445</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>12.42755408134577</v>
+        <v>12.49655421159073</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>15.74602027916097</v>
+        <v>15.81529834399369</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>13.3171775356989</v>
+        <v>13.38724354198836</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>13.02728183310789</v>
+        <v>13.09667471171896</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>9.353365130109395</v>
+        <v>9.422934565891921</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>8.363425961801724</v>
+        <v>8.433138109858348</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>8.579549124733539</v>
+        <v>8.649029490782674</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>6.996681415929203</v>
+        <v>7.065963796325931</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>7.33843675914364</v>
+        <v>7.408373380572293</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>10.80230471235058</v>
+        <v>10.87235042801274</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>11.9620356310451</v>
+        <v>12.03178089270719</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>11.88609429177664</v>
+        <v>11.95594863948391</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.07567</t>
+          <t>X &gt; 0.07565</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.575878594249204</v>
+        <v>3.060183814403082</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.1573697462715415</v>
+        <v>-0.3673764891013676</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.8010026155187404</v>
+        <v>0.2564601319707336</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2.170542635658919</v>
+        <v>2.636289617682635</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>8.055272850634879</v>
+        <v>8.486066155444632</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>8.242437463641664</v>
+        <v>7.642104506490462</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>7.469571331587638</v>
+        <v>6.870155822600111</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>11.35768335273573</v>
+        <v>10.71565571805323</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>11.39919941775837</v>
+        <v>10.75714289996793</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>12.70869734032228</v>
+        <v>12.04608289403453</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>14.02472327410428</v>
+        <v>13.35107037124801</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>15.82896270396272</v>
+        <v>15.1341766379031</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>16.78780481880889</v>
+        <v>17.10379807620162</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>17.60811467444122</v>
+        <v>17.91364703480659</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>14.86585010207057</v>
+        <v>15.19364806712293</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>14.4192434850253</v>
+        <v>14.75710715401438</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>11.16014979087637</v>
+        <v>11.53040651188226</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>10.01349970811441</v>
+        <v>10.39463797300952</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>11.27128953771291</v>
+        <v>11.64145718898541</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>9.375</v>
+        <v>9.766447328850333</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>9.873466257668703</v>
+        <v>10.25482899593585</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>13.96417786869278</v>
+        <v>14.30269437473294</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>16.32228636850822</v>
+        <v>16.63902475731808</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>16.24634502923976</v>
+        <v>16.56319250409481</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.07829</t>
+          <t>X &gt; 0.07827</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>83</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>2.952384618345597</v>
+        <v>2.985658910664426</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-2.202068004732475</v>
+        <v>-2.168394996119133</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-1.232129914601742</v>
+        <v>-1.196775490933256</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.4637153264219762</v>
+        <v>0.49990904384088</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>6.122541926940094</v>
+        <v>6.188214956835772</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>6.30970653994688</v>
+        <v>6.375181142933151</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>4.332021130784412</v>
+        <v>4.398413181934359</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>8.872743593699596</v>
+        <v>8.939478845615028</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>10.11907893583066</v>
+        <v>10.18578530463816</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>9.345243525061228</v>
+        <v>9.412869628601669</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>10.82442206928499</v>
+        <v>10.89174854787202</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>12.95496672002696</v>
+        <v>13.02263769864089</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>15.44493333286511</v>
+        <v>15.51393346311007</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>16.4283957989392</v>
+        <v>16.49767386377192</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>13.35982600568503</v>
+        <v>13.42989201197449</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>12.75006677819798</v>
+        <v>12.81945965680906</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>10.20633452983219</v>
+        <v>10.27590396561472</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>10.10135111373691</v>
+        <v>10.17106326179353</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>13.93193210799402</v>
+        <v>14.00141247404316</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>12.91415662650603</v>
+        <v>12.98343900690276</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>13.5757754946165</v>
+        <v>13.64571211604515</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>18.31909754740763</v>
+        <v>18.38914326306979</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>19.79869199099819</v>
+        <v>19.86843725266027</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>20.92756992883816</v>
+        <v>20.99742427654544</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.08092</t>
+          <t>X &gt; 0.08089</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>76</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.904825962670252</v>
+        <v>2.938100254989081</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-2.69350744671091</v>
+        <v>-2.659834438097569</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.18583948974441</v>
+        <v>-0.1504850660759232</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1.73194614443085</v>
+        <v>1.768139861849754</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>6.629834254143638</v>
+        <v>6.695507284039316</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>6.816998867150424</v>
+        <v>6.882473470136695</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>6.044132735096397</v>
+        <v>6.110524786246344</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>11.02873598431468</v>
+        <v>11.09547123623011</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>13.70183099670574</v>
+        <v>13.76853736551324</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>11.61220611225209</v>
+        <v>11.67983221579253</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>10.57077590568322</v>
+        <v>10.63810238427025</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>14.23905042326095</v>
+        <v>14.30672140187488</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>17.06192762582645</v>
+        <v>17.13092775607141</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>19.47214976216051</v>
+        <v>19.54142782699323</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>13.55006062838635</v>
+        <v>13.62012663467582</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>12.82933120432353</v>
+        <v>12.89872408293461</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>10.06365856280618</v>
+        <v>10.13322799858871</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>11.27446462039512</v>
+        <v>11.34417676845175</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>15.43795620437957</v>
+        <v>15.5074365704287</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>15.625</v>
+        <v>15.69428238039673</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>17.71337853837047</v>
+        <v>17.78331515979912</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>21.58479190378049</v>
+        <v>21.65483761944265</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>21.85956707026262</v>
+        <v>21.92931233192471</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>21.78362573099415</v>
+        <v>21.85348007870143</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.08354</t>
+          <t>X &gt; 0.08351</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>69</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>2.847617724683985</v>
+        <v>2.880892017002814</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-3.284659239235701</v>
+        <v>-3.25098623062236</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>1.072741745953522</v>
+        <v>1.108096169622009</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>3.257499157398044</v>
+        <v>3.293692874816948</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>8.689330821649364</v>
+        <v>8.755003851545041</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>7.427220072337299</v>
+        <v>7.49269467532357</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>6.654353940283272</v>
+        <v>6.720745991433219</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>12.17290074404008</v>
+        <v>12.23963599595551</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>13.66369217138156</v>
+        <v>13.73039854018906</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>12.88985676061213</v>
+        <v>12.95748286415257</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>11.71494066540862</v>
+        <v>11.78226714399565</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>12.88512212425256</v>
+        <v>12.95279310286649</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>16.10845699272195</v>
+        <v>16.17745712296691</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>18.78565090632527</v>
+        <v>18.85492897115799</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>13.77889358033143</v>
+        <v>13.8489595866209</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>14.37395362995282</v>
+        <v>14.44334650856389</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>11.34130921116622</v>
+        <v>11.41087864694875</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>12.68560115738978</v>
+        <v>12.75531330544641</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>15.80027504495929</v>
+        <v>15.86975541100842</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>15.98731884057972</v>
+        <v>16.05660122097645</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>16.89339379390059</v>
+        <v>16.96333041532925</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>22.61454018753334</v>
+        <v>22.6845859031955</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>21.44003999169664</v>
+        <v>21.50978525335873</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>21.36409865242818</v>
+        <v>21.43395300013545</v>
       </c>
     </row>
   </sheetData>
@@ -5831,76 +5831,76 @@
         <v>69</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-7.297309811547898</v>
+        <v>-7.264035519229068</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-10.5310360508299</v>
+        <v>-10.49736304221656</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-6.173635065640674</v>
+        <v>-6.138280641972187</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-1.090326929558472</v>
+        <v>-1.054133212139568</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-5.803422801539043</v>
+        <v>-5.737749771643365</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.180843260743103</v>
+        <v>0.2463178637293737</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.5920228713109239</v>
+        <v>-0.525630820160977</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-3.769128241467158</v>
+        <v>-3.702392989551726</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-12.42326435035758</v>
+        <v>-12.35655798155008</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-13.19709976112701</v>
+        <v>-13.12947365758657</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-20.16911730560587</v>
+        <v>-20.10179082701884</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-23.34676193371845</v>
+        <v>-23.27909095510452</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-30.26835460148096</v>
+        <v>-30.199354471236</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-33.38826213715299</v>
+        <v>-33.31898407232028</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-34.04719337619029</v>
+        <v>-33.97712736990083</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-37.79995941352544</v>
+        <v>-37.73056653491436</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-40.83260383231204</v>
+        <v>-40.76303439652951</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-40.93758724840732</v>
+        <v>-40.86787510035069</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-43.62001481011319</v>
+        <v>-43.55053444406406</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-44.88224637681159</v>
+        <v>-44.81296399641487</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-45.42544678580955</v>
+        <v>-45.3555101643809</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-44.05212647913332</v>
+        <v>-43.98208076347116</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-45.22662667497003</v>
+        <v>-45.15688141330794</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-45.3025680142385</v>
+        <v>-45.23271366653122</v>
       </c>
     </row>
     <row r="7">
@@ -5913,76 +5913,76 @@
         <v>159</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-5.246448449775954</v>
+        <v>-5.213174157457125</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-7.468416417250467</v>
+        <v>-7.434743408637125</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-5.763462793286294</v>
+        <v>-5.728108369617807</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-5.219394471259321</v>
+        <v>-5.183200753840417</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-9.358249161943746</v>
+        <v>-9.292576132048069</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-9.800015366547022</v>
+        <v>-9.734540763560751</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-16.23325885709161</v>
+        <v>-16.16686680594167</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-20.28539840827056</v>
+        <v>-20.21866315635513</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-22.75960561368817</v>
+        <v>-22.69289924488067</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-22.90451020684754</v>
+        <v>-22.8368841033071</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-25.14587421017246</v>
+        <v>-25.07854773158543</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-26.68282974886748</v>
+        <v>-26.61515877025355</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-30.32304423779488</v>
+        <v>-30.25404410754992</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-29.91547023121917</v>
+        <v>-29.84619216638645</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-30.57440147025647</v>
+        <v>-30.50433546396701</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-31.86613387346528</v>
+        <v>-31.7967409948542</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-32.0002275676142</v>
+        <v>-31.93065813183167</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-30.21841853087929</v>
+        <v>-30.14870638282267</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-30.63122618555754</v>
+        <v>-30.56174581950841</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-31.70204402515723</v>
+        <v>-31.6327616447605</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-34.13203688698538</v>
+        <v>-34.06210026555672</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-31.69226867218773</v>
+        <v>-31.62222295652557</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-31.4174935057056</v>
+        <v>-31.34774824404352</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-29.60664239214388</v>
+        <v>-29.53678804443661</v>
       </c>
     </row>
     <row r="8">
@@ -5995,76 +5995,76 @@
         <v>343</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.6128969159548774</v>
+        <v>-0.5796226236360482</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-2.405798378121069</v>
+        <v>-2.372125369507728</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-4.428589221215951</v>
+        <v>-4.393234797547464</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-5.725472913417853</v>
+        <v>-5.689279195998949</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-6.0907426984419</v>
+        <v>-6.025069668546223</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-7.361304032956987</v>
+        <v>-7.295829429970716</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-11.63271243906349</v>
+        <v>-11.56632038791354</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-13.66053822160829</v>
+        <v>-13.59380296969286</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-13.91056734609003</v>
+        <v>-13.84386097728252</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-13.51822199884197</v>
+        <v>-13.45059589530153</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-13.82695311073537</v>
+        <v>-13.75962663214835</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-13.52295663520153</v>
+        <v>-13.4552856565876</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-15.5220834222018</v>
+        <v>-15.45308329195684</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-14.57725947521865</v>
+        <v>-14.50798141038593</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-15.52773590376033</v>
+        <v>-15.45766989747086</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-16.68194699116519</v>
+        <v>-16.61255411255411</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-18.27376663283598</v>
+        <v>-18.20419719705345</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-18.08720485942688</v>
+        <v>-18.01749271137026</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-17.57953650699069</v>
+        <v>-17.51005614094156</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-18.85021865889212</v>
+        <v>-18.7809362784954</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-20.55959982590758</v>
+        <v>-20.48966320447892</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-19.46937412353269</v>
+        <v>-19.39932840787053</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-19.77768933605931</v>
+        <v>-19.70794407439723</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-19.85363067532778</v>
+        <v>-19.7837763276205</v>
       </c>
     </row>
     <row r="9">
@@ -6074,79 +6074,79 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.8963436279730175</v>
+        <v>-0.7766899939556922</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.9047217569964303</v>
+        <v>-0.7841345500796564</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-1.200631371409365</v>
+        <v>-1.240156872433069</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-1.914424684602523</v>
+        <v>-1.953110891875809</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.769890548057944</v>
+        <v>-2.61623360664894</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-4.216712863155728</v>
+        <v>-4.065928631680862</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-4.172585531157466</v>
+        <v>-4.019546710006558</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-5.431532333538769</v>
+        <v>-5.279754881437213</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-5.553414961326595</v>
+        <v>-5.565599941748367</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-5.346858215233283</v>
+        <v>-5.356518891107285</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-5.39929633373886</v>
+        <v>-5.409791491171212</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-4.207802001919646</v>
+        <v>-4.215545804602847</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-5.33229322040679</v>
+        <v>-5.338707871458965</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-5.22685264582023</v>
+        <v>-5.232454505679698</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-6.049182577667992</v>
+        <v>-6.054263924373181</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-6.434514684909352</v>
+        <v>-6.441873729107769</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-7.385601843110557</v>
+        <v>-7.394121471649896</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-7.653983952016297</v>
+        <v>-7.662628296584003</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-8.418252945947238</v>
+        <v>-8.428733642337257</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-10.02859477124183</v>
+        <v>-10.04221516461146</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-9.918200408997954</v>
+        <v>-9.930096848125764</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-9.340560693398736</v>
+        <v>-9.187612203970218</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-9.719380298158434</v>
+        <v>-9.731468097052812</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-9.631922944616441</v>
+        <v>-9.643634229163155</v>
       </c>
     </row>
     <row r="10">
@@ -6156,325 +6156,325 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.9208174409930834</v>
+        <v>-0.9396343240163176</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.5952000040955667</v>
+        <v>-0.6128896229173932</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.484239675230164</v>
+        <v>-1.499640755741105</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-1.316975719700842</v>
+        <v>-1.330566109252203</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-1.792377663315207</v>
+        <v>-1.776610165040935</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-2.706534636211501</v>
+        <v>-2.692179811358109</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-2.157814865181827</v>
+        <v>-2.141085496351003</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-2.766765986471313</v>
+        <v>-2.750057690828434</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-2.174589128497139</v>
+        <v>-2.157302592706451</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-1.736970794773171</v>
+        <v>-1.717428853086943</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.793008003428767</v>
+        <v>-1.77412996064939</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.080912479590893</v>
+        <v>-1.060597114924278</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.214214270765261</v>
+        <v>-1.191476932607301</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.9950424474383723</v>
+        <v>-0.9715414760880634</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-1.323577210704755</v>
+        <v>-1.298924023944259</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-2.600763857118615</v>
+        <v>-2.578848017106012</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-3.06525402703847</v>
+        <v>-3.043525903807847</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-2.839840967362818</v>
+        <v>-2.817605857904667</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-3.174378597382542</v>
+        <v>-3.152982393187621</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-4.198788546255507</v>
+        <v>-4.178925998875592</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-3.750799527940679</v>
+        <v>-3.729189917668528</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-3.716622424992984</v>
+        <v>-3.69478229583617</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-3.882375892872098</v>
+        <v>-3.861321916319945</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-3.738052914959944</v>
+        <v>-3.716647003060316</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; 0.02061</t>
+          <t>X &lt; 0.0206</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.5648777082718013</v>
+        <v>-0.5710405532974008</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.8160196094707501</v>
+        <v>-0.8217130623284561</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.079249485321597</v>
+        <v>-1.082272060896877</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.4857511686584388</v>
+        <v>-0.5336617405582871</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.8041547587927411</v>
+        <v>-0.8694522131055606</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.496750966574581</v>
+        <v>-1.607633209514496</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.21156975891266</v>
+        <v>-1.37033042157978</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.189785001694645</v>
+        <v>-1.349150418917851</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.8474222038632533</v>
+        <v>-1.007767338960669</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.4388251822002474</v>
+        <v>-0.552794037868594</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.5023037529227565</v>
+        <v>-0.5677603738909696</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.2746408996409002</v>
+        <v>-0.2914293804864201</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.3856186046145282</v>
+        <v>-0.3513874995232129</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.1002186588921248</v>
+        <v>-0.06528125340005886</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.2523931411726679</v>
+        <v>-0.21623942841088</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.8397655239837221</v>
+        <v>-0.8052844591306112</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-1.142778137051565</v>
+        <v>-1.108263303631333</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-1.332221012606304</v>
+        <v>-1.297634861214135</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-2.214070822647464</v>
+        <v>-2.180644579190918</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-2.702702702702695</v>
+        <v>-2.670045599315863</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-2.316849057646607</v>
+        <v>-2.282752375904039</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-2.308344653829749</v>
+        <v>-2.274067483551519</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-2.624785703563838</v>
+        <v>-2.591308747400831</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-2.869645961751225</v>
+        <v>-2.836202708147347</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; 0.02323</t>
+          <t>X &lt; 0.02322</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1436</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.5253324784151516</v>
+        <v>-0.4920581860963225</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.3760789273155396</v>
+        <v>-0.3424059187021982</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.431696346418974</v>
+        <v>-0.3963419227504872</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.7611286478129173</v>
+        <v>-0.7632751809475522</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.088005042643026</v>
+        <v>-1.099065653494826</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.347830682451736</v>
+        <v>-1.396528533141399</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.527363667255763</v>
+        <v>-1.614843999038662</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.697872202819823</v>
+        <v>-1.785415190362684</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-2.10410148564678</v>
+        <v>-2.190539119879041</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.491812627225251</v>
+        <v>-2.578507809026796</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.735454178922865</v>
+        <v>-2.821118186239993</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.627977871710463</v>
+        <v>-2.714477428534465</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.847176611088962</v>
+        <v>-2.895772072025601</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.511430358056472</v>
+        <v>-2.521378702543409</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-2.404344884001844</v>
+        <v>-2.37445271557872</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-2.853853079505818</v>
+        <v>-2.784460200894742</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-2.987946773654741</v>
+        <v>-2.918377337872215</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-3.301843838775085</v>
+        <v>-3.232131690718461</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-4.130288920968624</v>
+        <v>-4.06080855491949</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-4.430710306406681</v>
+        <v>-4.361427926009952</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-3.998980353287649</v>
+        <v>-3.929043731858997</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-4.214211174946968</v>
+        <v>-4.144165459284807</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-4.70545272155676</v>
+        <v>-4.635707459894675</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-4.920669826841937</v>
+        <v>-4.85081547913466</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; 0.02585</t>
+          <t>X &lt; 0.02584</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1702</v>
+        <v>1699</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.08811557484700216</v>
+        <v>-0.01935178632916035</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.3930354411209152</v>
+        <v>0.346805994760274</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.1397791814474232</v>
+        <v>-0.1566336150183787</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.1127492906501573</v>
+        <v>0.06499180479121947</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.3948829126049986</v>
+        <v>-0.3876210976626027</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.700919247833113</v>
+        <v>-0.7263558461446564</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.3301362707515594</v>
+        <v>-0.3553769640381859</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.2828959333965102</v>
+        <v>-0.3080375356997109</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.5592314955905806</v>
+        <v>-0.5842697546863249</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.5968093966431667</v>
+        <v>-0.621412699775064</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.8162790705616132</v>
+        <v>-0.8995290405131513</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.120572975411683</v>
+        <v>-1.203551936805937</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.566068420627722</v>
+        <v>-1.648204826117215</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.166351953078859</v>
+        <v>-1.248663598754241</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-1.355523943730951</v>
+        <v>-1.402897749537786</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-1.758702296928128</v>
+        <v>-1.772869707652312</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-1.834076085028904</v>
+        <v>-1.814078539361098</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-2.115219219268624</v>
+        <v>-2.061395986966218</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-2.629023819122196</v>
+        <v>-2.610210488394827</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-2.676997649823733</v>
+        <v>-2.658658796073851</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-2.632653993016753</v>
+        <v>-2.612969669922236</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-2.76736345523986</v>
+        <v>-2.747639160743105</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-3.021377947982167</v>
+        <v>-2.969234801063742</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-3.156073693831132</v>
+        <v>-3.103925206141042</v>
       </c>
     </row>
     <row r="14">
@@ -6487,76 +6487,76 @@
         <v>1894</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.06737519288866167</v>
+        <v>0.1006494852074908</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.778772153388239</v>
+        <v>0.8124451620015805</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.6243010448381128</v>
+        <v>0.6303130831432711</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.4113318795911667</v>
+        <v>0.3883166775152915</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.2911632080653419</v>
+        <v>-0.313774161332347</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.1793856442066186</v>
+        <v>-0.2314652227493639</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.08333178138894226</v>
+        <v>-0.1363751861978528</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.0694820015949702</v>
+        <v>-0.1228574561136355</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.00214059422895474</v>
+        <v>-0.05138981091840833</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.1517696822385446</v>
+        <v>0.09715896212875208</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.4896037500807964</v>
+        <v>-0.5426564382845598</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.7911275993864137</v>
+        <v>-0.8438518817278222</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.7801776373314624</v>
+        <v>-0.834021381478351</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.6021275583128656</v>
+        <v>-0.6565974516526722</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.703169919004246</v>
+        <v>-0.7580902007882244</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-1.236506822477786</v>
+        <v>-1.289791656703805</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-1.265170890901885</v>
+        <v>-1.28782463299023</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-1.603061473320174</v>
+        <v>-1.625253125398203</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-1.936713980317002</v>
+        <v>-1.958316854228833</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-2.088833157338968</v>
+        <v>-2.110145663883713</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-2.10405046179627</v>
+        <v>-2.125543703225595</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-2.127207206984806</v>
+        <v>-2.118202575982615</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-2.327616834589264</v>
+        <v>-2.288157463936976</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-2.456356484311804</v>
+        <v>-2.386502136604527</v>
       </c>
     </row>
     <row r="15">
@@ -6566,1719 +6566,1719 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.2681862865568903</v>
+        <v>0.2793068067219551</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.231087694989498</v>
+        <v>1.243231307073444</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.9242589887751151</v>
+        <v>0.9115133643435485</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.6707030463101802</v>
+        <v>0.631459777801247</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.05237439699793356</v>
+        <v>-0.0891310795464122</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.2583334173988803</v>
+        <v>0.1940352027510599</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.332021130784419</v>
+        <v>0.267355747190571</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.01526746693640035</v>
+        <v>-0.07955347045716366</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.1390302011514208</v>
+        <v>-0.1549998011027256</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.1130529814280479</v>
+        <v>-0.1292990460971311</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.7281135197151372</v>
+        <v>-0.7434131209827513</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.8829938177764234</v>
+        <v>-0.8981685364296368</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.109830915039979</v>
+        <v>-1.125016157767256</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.7228008639211367</v>
+        <v>-0.7386301160294693</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-1.159790923570448</v>
+        <v>-1.175195002751067</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-1.504239896710757</v>
+        <v>-1.518996148044003</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-1.271246496452122</v>
+        <v>-1.286399406481024</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-1.493283237622009</v>
+        <v>-1.508164534733645</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-1.927530950249611</v>
+        <v>-1.941740583491914</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-1.955019398642101</v>
+        <v>-1.969155876261866</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-1.91626054478845</v>
+        <v>-1.902527353460769</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-2.137705416143952</v>
+        <v>-2.095704513883874</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-2.590379328226327</v>
+        <v>-2.520634066564241</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-2.617824062257171</v>
+        <v>-2.520227115047135</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 0.03372</t>
+          <t>X &lt; 0.03371</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2217</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.05158115530357321</v>
+        <v>-0.01830686298474404</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.8005464800522972</v>
+        <v>0.8544297554811848</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.8625514069242897</v>
+        <v>0.8922604381138868</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.5322384111477945</v>
+        <v>0.5370881718017273</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.3900676511572456</v>
+        <v>-0.4248203687240775</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.1360203113930325</v>
+        <v>0.1004176594690875</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.509556383904517</v>
+        <v>0.4727732902278845</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.1222638821211035</v>
+        <v>0.0859725679292751</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.2143553398717941</v>
+        <v>-0.2500440342226611</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.3787895628359408</v>
+        <v>-0.4146970252841555</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.6175723233800028</v>
+        <v>-0.6529054042593643</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.781056022629059</v>
+        <v>-0.8162981254089985</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.5758042939009371</v>
+        <v>-0.6121507660867778</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.3659069180014356</v>
+        <v>-0.4027973520297721</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.8182183047701059</v>
+        <v>-0.8547397766354692</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-1.141971433179719</v>
+        <v>-1.177562138236297</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.7993096685830992</v>
+        <v>-0.8356284951636539</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-1.103088094198931</v>
+        <v>-1.138954135731794</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-1.581881487234504</v>
+        <v>-1.616775850813426</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-1.729533152909333</v>
+        <v>-1.764069713254777</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-1.641249574536971</v>
+        <v>-1.650065589371096</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-1.85252262747322</v>
+        <v>-1.834880366373625</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-2.344549445655055</v>
+        <v>-2.300672006739809</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-2.33027878672776</v>
+        <v>-2.260424439020483</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 0.03634</t>
+          <t>X &lt; 0.03633</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2382</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.1770356438856808</v>
+        <v>-0.1437613515668517</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.4680042041363208</v>
+        <v>0.4789972372606783</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.2593359488520761</v>
+        <v>0.2483054155402726</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.2357086770650554</v>
+        <v>0.201462969786121</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.3979520590120558</v>
+        <v>-0.4440617551767971</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.02122344611975535</v>
+        <v>-0.02542126670540767</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.0231328229621468</v>
+        <v>-0.02361005063744415</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.3150723883916129</v>
+        <v>-0.3614446146982928</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.7509676666192391</v>
+        <v>-0.7968184520657573</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.9578996787611587</v>
+        <v>-1.003587518852918</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.077701475059605</v>
+        <v>-1.123242522882805</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.333051097793884</v>
+        <v>-1.378324546328955</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.26223004869459</v>
+        <v>-1.307720054428529</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.9988687216798979</v>
+        <v>-1.044736580681473</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-1.214551907979683</v>
+        <v>-1.260236129197466</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-1.558360899837162</v>
+        <v>-1.603588183086089</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-1.249042720998467</v>
+        <v>-1.294698242296043</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-1.161814757294387</v>
+        <v>-1.207617289557604</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-1.592245137902317</v>
+        <v>-1.637515251942474</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-1.674622324800666</v>
+        <v>-1.71979976545407</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-1.521894783473186</v>
+        <v>-1.567341355703476</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-1.891720536009167</v>
+        <v>-1.912364782535448</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-2.036760650803274</v>
+        <v>-2.033185183370044</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-2.196665046326984</v>
+        <v>-2.168792226747328</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 0.03896</t>
+          <t>X &lt; 0.03895</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2537</v>
+        <v>2538</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.2912508543233443</v>
+        <v>-0.2606204623964103</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.13605748377541</v>
+        <v>-0.1264640837239455</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.184809517553667</v>
+        <v>-0.1967613664399721</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.1802006883866625</v>
+        <v>0.1673826913629384</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.202169374198661</v>
+        <v>-0.2246088059510072</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.007066512753461041</v>
+        <v>-0.01564035903717809</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.0402952307121538</v>
+        <v>0.01720930576432522</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.2158460590289693</v>
+        <v>-0.2386589207991037</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.3872854782792956</v>
+        <v>-0.4098286435163843</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.5500677041570583</v>
+        <v>-0.572683870661848</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.6457223481964647</v>
+        <v>-0.6680933284533452</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.8630705508160261</v>
+        <v>-0.8852290625213968</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.02203473587349</v>
+        <v>-1.044414483403322</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.9060362689550203</v>
+        <v>-0.9287035453937804</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.9914051083108646</v>
+        <v>-1.014221308208469</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-1.15986089472819</v>
+        <v>-1.182187150372535</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.8380792528072263</v>
+        <v>-0.8609814937078397</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.8805291632766554</v>
+        <v>-0.9034233639547438</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-1.074450254856352</v>
+        <v>-1.096967676523718</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-1.021966115051221</v>
+        <v>-1.044505975228759</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.8326663136096926</v>
+        <v>-0.8557411586830312</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-1.145121172169141</v>
+        <v>-1.144582189923277</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-1.343345611520675</v>
+        <v>-1.319583835236017</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-1.498120218428078</v>
+        <v>-1.451235611232626</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 0.04158</t>
+          <t>X &lt; 0.04157</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2655</v>
+        <v>2657</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.3856311217448223</v>
+        <v>-0.3747030298186829</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.06537168675026095</v>
+        <v>-0.07491469192362388</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.2507924480564299</v>
+        <v>-0.260543632956157</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.1035766798040711</v>
+        <v>0.09305188040941204</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.1283598838960671</v>
+        <v>-0.1469913392003974</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.04248114266324166</v>
+        <v>0.02364415385533647</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.03979605068875713</v>
+        <v>0.02069287662936858</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.2548119638622452</v>
+        <v>-0.273579898902895</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.3418050799927599</v>
+        <v>-0.3604415188233503</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.56933040620941</v>
+        <v>-0.5878971975949199</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.6484762757831959</v>
+        <v>-0.6668453783948465</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.8310591847177236</v>
+        <v>-0.8492605349830029</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.9580660520619801</v>
+        <v>-0.976465915513856</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.9322220385391446</v>
+        <v>-0.9507474931970137</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.9681093269301826</v>
+        <v>-0.9868145743106354</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-1.102411907684221</v>
+        <v>-1.120728864631303</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.9513790311787744</v>
+        <v>-0.9699804730408133</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.8838457851787922</v>
+        <v>-0.9025967556702383</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-1.097032508938717</v>
+        <v>-1.115403399518712</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-1.03853029732781</v>
+        <v>-1.056938964962164</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.8820558306846991</v>
+        <v>-0.9008953665166786</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-1.01110461718293</v>
+        <v>-1.029788575604947</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-1.301301202113237</v>
+        <v>-1.297490566970389</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-1.339577757954217</v>
+        <v>-1.313724722914955</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.04421</t>
+          <t>X &lt; 0.04419</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2770</v>
+        <v>2773</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.1999093713668429</v>
+        <v>-0.1882531957217637</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.3367781099329221</v>
+        <v>-0.3441391175062876</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.3235493558074225</v>
+        <v>-0.331323705265163</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.04948843880026033</v>
+        <v>-0.05785369346710922</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.2511594783943067</v>
+        <v>-0.2661123811695489</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.1155639715933603</v>
+        <v>-0.1306702813954885</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.04269236786199571</v>
+        <v>-0.05812263876779866</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.1930347801188432</v>
+        <v>-0.2083350705012208</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.1668925362646121</v>
+        <v>-0.1822290771357089</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.4171261115881393</v>
+        <v>-0.4323238471311868</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.5533680271178625</v>
+        <v>-0.5683055954781153</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.7399423661559581</v>
+        <v>-0.7546978554245598</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.800624437785828</v>
+        <v>-0.8156088440495992</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.713074002540921</v>
+        <v>-0.7282546436461743</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.8468928784909835</v>
+        <v>-0.8620709513092635</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.8426548465075356</v>
+        <v>-0.8576869013762192</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.6674198536961669</v>
+        <v>-0.6827507973219227</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.6790678594531556</v>
+        <v>-0.6944209853786703</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.8021303132844508</v>
+        <v>-0.8172574540493329</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.6660205553552032</v>
+        <v>-0.6813027834491479</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.5026159934135421</v>
+        <v>-0.5182926060131052</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.7014813397758886</v>
+        <v>-0.7169025417711978</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.8746149551981404</v>
+        <v>-0.8897215541603671</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-1.022758460531591</v>
+        <v>-1.016487845074828</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.04683</t>
+          <t>X &lt; 0.04681</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2866</v>
+        <v>2869</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.3500216827591061</v>
+        <v>-0.3559231853545128</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.4588985830206838</v>
+        <v>-0.4647280280045365</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.5286924641763378</v>
+        <v>-0.5347502272487645</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.322236104953447</v>
+        <v>-0.3287430515604655</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.4600993176499202</v>
+        <v>-0.4720827436615167</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.2881730115577952</v>
+        <v>-0.3003606501484271</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.2088348678109355</v>
+        <v>-0.2213131245389306</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.3635072060980065</v>
+        <v>-0.3758413606867919</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.302189471130518</v>
+        <v>-0.3146073895783772</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.500460932226062</v>
+        <v>-0.5127851236017307</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.6577819378484691</v>
+        <v>-0.6698343555668487</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.9169966286754629</v>
+        <v>-0.9287596993509339</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.9437088575935206</v>
+        <v>-0.9556950509461473</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.901305615413861</v>
+        <v>-0.9134084648478762</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-1.017935562508413</v>
+        <v>-1.03003246703954</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.9244013693661799</v>
+        <v>-0.9365026700793138</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.7247155758831525</v>
+        <v>-0.7371328827523271</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.6698423329862493</v>
+        <v>-0.6823678539738864</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.7118695795925589</v>
+        <v>-0.7242962061892584</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.6088794004879716</v>
+        <v>-0.6214154963871223</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.469106964088617</v>
+        <v>-0.4819685229453441</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.6289653704654725</v>
+        <v>-0.6416297768432528</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.6823949527292612</v>
+        <v>-0.6949312037437423</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.8979036332398849</v>
+        <v>-0.8896359896150585</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.04945</t>
+          <t>X &lt; 0.04944</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.2777036970654336</v>
+        <v>-0.2827640894697652</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.3243746756351555</v>
+        <v>-0.3294389016534893</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.4270156462330306</v>
+        <v>-0.4322177666216263</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.2087988167542534</v>
+        <v>-0.214434818093352</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.4536103980960959</v>
+        <v>-0.4637392608460402</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.3490204465366347</v>
+        <v>-0.3592616994302276</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.3579204846444455</v>
+        <v>-0.368303329019831</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.3801215253130508</v>
+        <v>-0.3905340340497858</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.2515122054202195</v>
+        <v>-0.2620975975288857</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.4297207387737743</v>
+        <v>-0.4402190973243734</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.5427148405108539</v>
+        <v>-0.5530145886564739</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.7006053647844723</v>
+        <v>-0.7107511412715937</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.7536921837926229</v>
+        <v>-0.7639874377076907</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.7175811843503794</v>
+        <v>-0.7279744923644884</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.8472229030228036</v>
+        <v>-0.8575732100529834</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-0.8094702830906471</v>
+        <v>-0.8197648123021253</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-0.6857557476897256</v>
+        <v>-0.6962506862468913</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-0.6347271217065682</v>
+        <v>-0.645318354283809</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.5685041832436895</v>
+        <v>-0.5791508659040616</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.5314625850340136</v>
+        <v>-0.5421306630815295</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-0.4081629813014587</v>
+        <v>-0.4191098630025323</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.6680833067099954</v>
+        <v>-0.6786984641381579</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.7135920788870749</v>
+        <v>-0.7240995043644247</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.8375559698519695</v>
+        <v>-0.8479162693114688</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.05207</t>
+          <t>X &lt; 0.05206</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2996</v>
+        <v>2999</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.3452045458634174</v>
+        <v>-0.3648709387132385</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.2650954624759763</v>
+        <v>-0.2847930610701042</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.3611617862048249</v>
+        <v>-0.3474177952498607</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.2940904324224292</v>
+        <v>-0.2802902561746947</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.5413274810400921</v>
+        <v>-0.5313072672494386</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.3687658099703768</v>
+        <v>-0.358947948839976</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.16055921382668</v>
+        <v>-0.1508182264578224</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.2542024374369021</v>
+        <v>-0.2443210305063772</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.1937099146893217</v>
+        <v>-0.1838951424321422</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.4169947969977699</v>
+        <v>-0.4068273471539925</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.588728038624204</v>
+        <v>-0.5784349750643401</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.6825621187323208</v>
+        <v>-0.6721280798500189</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.6905096696070174</v>
+        <v>-0.6798783289084867</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.7593171286193368</v>
+        <v>-0.7485793444748197</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.8662630426881535</v>
+        <v>-0.8553072958952797</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.8173854541668959</v>
+        <v>-0.8065775816025251</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-0.6655245347979601</v>
+        <v>-0.6548449782645918</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-0.6842295834689622</v>
+        <v>-0.6735130467685053</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.5817039089159977</v>
+        <v>-0.5711253470147071</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.5416666666666643</v>
+        <v>-0.5311588450445015</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.465049358647839</v>
+        <v>-0.4545262792415201</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.6879513285498433</v>
+        <v>-0.6771920548764356</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.6936879391327366</v>
+        <v>-0.6829683698296805</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.8166834531812412</v>
+        <v>-0.8058274097596367</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.05469</t>
+          <t>X &lt; 0.05468</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3045</v>
+        <v>3048</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.3494799455161157</v>
+        <v>-0.3357347721750443</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.2107967573693728</v>
+        <v>-0.197122283117281</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.2630874040507365</v>
+        <v>-0.2490942478769611</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.3389734056678861</v>
+        <v>-0.3247716869047963</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.5554756263016003</v>
+        <v>-0.5445524348699493</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.3500372343668303</v>
+        <v>-0.3393482073446705</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.05954906902199042</v>
+        <v>-0.04900127196606974</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.2214574509232037</v>
+        <v>-0.2106988888214119</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.2266175757056885</v>
+        <v>-0.2158604556802928</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.3606608377315581</v>
+        <v>-0.3496290926058236</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.5579287860657658</v>
+        <v>-0.5467529261718127</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.7528577082060934</v>
+        <v>-0.7414382128482018</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.8768984970724318</v>
+        <v>-0.8651493933238257</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.8172808520181505</v>
+        <v>-0.8055481807173521</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.867614207032247</v>
+        <v>-0.8557096685454226</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.9082349514852552</v>
+        <v>-0.8963985403775894</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.8265256132302383</v>
+        <v>-0.8147434029101248</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.7483406720888013</v>
+        <v>-0.7366146009343879</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.7423716644728913</v>
+        <v>-0.7306898625880081</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.7328222367989454</v>
+        <v>-0.7211828882795501</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.7318487029612086</v>
+        <v>-0.7201090841933535</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.8868367905348862</v>
+        <v>-0.8749294211095489</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.8552962535097137</v>
+        <v>-0.843469080445189</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-1.01042836977502</v>
+        <v>-0.998433168984711</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.05732</t>
+          <t>X &lt; 0.0573</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3096</v>
+        <v>3100</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.387811691098662</v>
+        <v>-0.3907670621991812</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.3531070550968565</v>
+        <v>-0.3561492160739022</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.39606186956307</v>
+        <v>-0.3992245051895793</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.4503388363136906</v>
+        <v>-0.4535200571785865</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.6051070316551304</v>
+        <v>-0.6111530828124074</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.3999838594155136</v>
+        <v>-0.4062743776739808</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.1911792841099853</v>
+        <v>-0.1978351414844326</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.2586405547192854</v>
+        <v>-0.2652476341164842</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.2630474482011351</v>
+        <v>-0.2696479855047613</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.3111311698599337</v>
+        <v>-0.3177677571649085</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.3719878870407811</v>
+        <v>-0.3785172245011168</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.5360630360630267</v>
+        <v>-0.5424194451011601</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.6442706022832567</v>
+        <v>-0.6506283521354703</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.685778864944929</v>
+        <v>-0.6921142274999141</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.68165392369432</v>
+        <v>-0.6880787452906532</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.6795537658338162</v>
+        <v>-0.6859131859131864</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.6013176062661856</v>
+        <v>-0.6077982070928485</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.5905460688036968</v>
+        <v>-0.5970575149386335</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.5488222541821912</v>
+        <v>-0.5553653619384491</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.5040322580645125</v>
+        <v>-0.510614526819765</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.5764772725023164</v>
+        <v>-0.58303658808493</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.6655563684494723</v>
+        <v>-0.6720143266702081</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.7913854644483962</v>
+        <v>-0.7976518052806156</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.9451924384604951</v>
+        <v>-0.9512737413325283</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.05994</t>
+          <t>X &lt; 0.05992</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3128</v>
+        <v>3132</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.325977959225888</v>
+        <v>-0.3286442608170717</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.3585032696014707</v>
+        <v>-0.3611660804564778</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.4156534657769129</v>
+        <v>-0.4184003347423655</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.5084069619692002</v>
+        <v>-0.5111147467529804</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.6335577817134066</v>
+        <v>-0.6388393728281727</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.460412716481251</v>
+        <v>-0.4658974571815975</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.2934122402194745</v>
+        <v>-0.2991959270962354</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.394861176526355</v>
+        <v>-0.4005496291480739</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.3670271173991324</v>
+        <v>-0.3727500761605427</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.4543622819989608</v>
+        <v>-0.4600613834312099</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.5436864680160696</v>
+        <v>-0.5492459547808792</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.6771413300075722</v>
+        <v>-0.682564790705797</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.8276114496417719</v>
+        <v>-0.8329686218444436</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.807277294966056</v>
+        <v>-0.8126878887761393</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.8099548070782987</v>
+        <v>-0.8154369639099386</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.738069440144784</v>
+        <v>-0.7435823200154417</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.5982234148652665</v>
+        <v>-0.603932679468322</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.6205409215388471</v>
+        <v>-0.6262368372642726</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.5770453915348881</v>
+        <v>-0.5827770094246603</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.5627394636015381</v>
+        <v>-0.5684727216440848</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.5761371704160325</v>
+        <v>-0.5819161001689821</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-0.6970308640015901</v>
+        <v>-0.7026675026478344</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-0.8187730754035627</v>
+        <v>-0.8242280783093037</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.9717922256621918</v>
+        <v>-0.9770637137298408</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.06256</t>
+          <t>X &lt; 0.06254</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3166</v>
+        <v>3170</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.3345165139351778</v>
+        <v>-0.3367443887216695</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.2138138589145697</v>
+        <v>-0.2162254155411745</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.2560259379798424</v>
+        <v>-0.2585191751656382</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.3875239054584654</v>
+        <v>-0.3899198642680517</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.4841044387424205</v>
+        <v>-0.4887279984283737</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.2793380807469532</v>
+        <v>-0.2842042027154434</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.2805857529238338</v>
+        <v>-0.2855249553023853</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.4155724612177565</v>
+        <v>-0.4203711003080244</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.3875814687553003</v>
+        <v>-0.3924144646115195</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.3887869364072927</v>
+        <v>-0.3936933065560524</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.3793739262732032</v>
+        <v>-0.3842697572050255</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.5145185211264547</v>
+        <v>-0.5192735036793863</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.582158983520344</v>
+        <v>-0.5869365368520434</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.6905838981868371</v>
+        <v>-0.6952487701600276</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.5750947798191888</v>
+        <v>-0.5799693902244201</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.496871826883968</v>
+        <v>-0.5017926273432849</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.3602305011711167</v>
+        <v>-0.3653390043766791</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.3519374503555213</v>
+        <v>-0.3570694200674112</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.3693600996254816</v>
+        <v>-0.3744531933508313</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.3213722397476317</v>
+        <v>-0.3265115704539383</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.3726024285624803</v>
+        <v>-0.3777311685967177</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.4928928383779336</v>
+        <v>-0.4978802407816758</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.6413885078205723</v>
+        <v>-0.6461660992525751</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.8250120985766145</v>
+        <v>-0.829568236091859</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.06518</t>
+          <t>X &lt; 0.06516</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3205</v>
+        <v>3209</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.2974175643629451</v>
+        <v>-0.2992629550161254</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.1822129414673341</v>
+        <v>-0.1842280591045906</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.2103117056219901</v>
+        <v>-0.2124045707198974</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.379844961240309</v>
+        <v>-0.3817843447646538</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.4486560161972264</v>
+        <v>-0.4524741938188939</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.3681996239578922</v>
+        <v>-0.3721054935414756</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.4408880104359554</v>
+        <v>-0.4447661068263855</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.5776628130512833</v>
+        <v>-0.5813953488372121</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.5806142468379036</v>
+        <v>-0.5843423523919498</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.5291094319672638</v>
+        <v>-0.5329639695202602</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.5476042585246859</v>
+        <v>-0.5514170381218619</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.6534613971667085</v>
+        <v>-0.6571668969535338</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.7961504050717068</v>
+        <v>-0.7997685499109508</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.8126992187677118</v>
+        <v>-0.8163164871939088</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.7066452308479043</v>
+        <v>-0.7104480930072725</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.5910661944020319</v>
+        <v>-0.5949689622366066</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.4888747006138772</v>
+        <v>-0.4929175892615092</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.4197116486799359</v>
+        <v>-0.4238513890337217</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.4654705868976876</v>
+        <v>-0.4695391607474022</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.3846603303209761</v>
+        <v>-0.3888175262325859</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.4107191122398532</v>
+        <v>-0.414888943235546</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.5616640396327668</v>
+        <v>-0.5656544391060905</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.673840684933225</v>
+        <v>-0.6776724196739252</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.8249628230743298</v>
+        <v>-0.8286146876629061</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.06781</t>
+          <t>X &lt; 0.06779</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3237</v>
+        <v>3241</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.238538583664905</v>
+        <v>-0.2401118193143148</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.06636964208889395</v>
+        <v>-0.06817677724301774</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.1389912457458351</v>
+        <v>-0.140804211579173</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.4059592576989743</v>
+        <v>-0.4074924111049469</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.4776919323299182</v>
+        <v>-0.4807923607782456</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.4883613074796926</v>
+        <v>-0.4914384498904383</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.5372407970745314</v>
+        <v>-0.5403104048621827</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.7061807726869489</v>
+        <v>-0.7090631270037306</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.6779838540743484</v>
+        <v>-0.6809001102400316</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.6346329170344376</v>
+        <v>-0.6376550507609409</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.6195074951264985</v>
+        <v>-0.6225323001667107</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.6963143043475455</v>
+        <v>-0.6992649750727082</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.8179012567247597</v>
+        <v>-0.8207780767764064</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.7748798846389704</v>
+        <v>-0.7778261677290459</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.7379699841894407</v>
+        <v>-0.7410069685630347</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.6793055647949515</v>
+        <v>-0.6823777945661575</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.486993653431071</v>
+        <v>-0.4903136140636022</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.4503840415001434</v>
+        <v>-0.4537581674404976</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.4318772317709616</v>
+        <v>-0.4352621356711097</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.3808623881518045</v>
+        <v>-0.3843000541179151</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.3502991744300559</v>
+        <v>-0.3538124928713984</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.4696108521058306</v>
+        <v>-0.4729842478991557</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.6088182228032792</v>
+        <v>-0.6120039445777721</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.7282842571365151</v>
+        <v>-0.7313296778714289</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.07043</t>
+          <t>X &lt; 0.07041</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3264</v>
+        <v>3268</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.2211247522673787</v>
+        <v>-0.222433257461141</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.08355133305488494</v>
+        <v>-0.08504640418300369</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.1978558319698394</v>
+        <v>-0.1992920942879977</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.316262074044694</v>
+        <v>-0.3175945471654842</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.4208414756926828</v>
+        <v>-0.4234461689573337</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.429866009850123</v>
+        <v>-0.4324510901990166</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.4237284753817931</v>
+        <v>-0.4263653843857185</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.59353615945939</v>
+        <v>-0.5959833441917084</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.5956923175267832</v>
+        <v>-0.5981362481584753</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.6200600320592642</v>
+        <v>-0.622518725546179</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.5722785568386612</v>
+        <v>-0.5747820059188768</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.6507381507381496</v>
+        <v>-0.6531630653908422</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.6889763516745617</v>
+        <v>-0.6914185947094893</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.7397269056850462</v>
+        <v>-0.742121191984964</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.6779934665209382</v>
+        <v>-0.6805013466292777</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.6148844693349389</v>
+        <v>-0.6174381174381125</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.48639051280243</v>
+        <v>-0.4891102898805499</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.4203687934146387</v>
+        <v>-0.4231768630307471</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.4308110027173981</v>
+        <v>-0.433596121291437</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.3786719706242323</v>
+        <v>-0.3815122406301654</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.3834590560747841</v>
+        <v>-0.3863255423843484</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.502422457904494</v>
+        <v>-0.5051495043300775</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.6075885676837061</v>
+        <v>-0.6101734274415946</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.6654196766425855</v>
+        <v>-0.66793974993994</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.07305</t>
+          <t>X &lt; 0.07303</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3288</v>
+        <v>3292</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.2763563800787878</v>
+        <v>-0.2773478675797776</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.1724389143528242</v>
+        <v>-0.1735720107558336</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.2661626912204511</v>
+        <v>-0.2672499635293377</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.3284497061387484</v>
+        <v>-0.3294955309801466</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.4651635973038424</v>
+        <v>-0.4672198297281795</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.4425292635210738</v>
+        <v>-0.444605556735624</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.4117952846503954</v>
+        <v>-0.4139459554310605</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.5823892864894518</v>
+        <v>-0.5843480217091681</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.4933982207520842</v>
+        <v>-0.4954640350246891</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.5837516804732061</v>
+        <v>-0.5857455216545304</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.5646057171105028</v>
+        <v>-0.5666113668245814</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.6748251748251661</v>
+        <v>-0.6767117572942283</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.6603486620438872</v>
+        <v>-0.6623064648123318</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.7729748747805374</v>
+        <v>-0.7748079471787221</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.686166883067429</v>
+        <v>-0.6881372088165705</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.6798665473371699</v>
+        <v>-0.6818181818181799</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.5533049385115945</v>
+        <v>-0.5554176835159126</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.5189076992929955</v>
+        <v>-0.521068515771546</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.5277285815299422</v>
+        <v>-0.5298700719734839</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.4746354799514023</v>
+        <v>-0.4768341244576391</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.4833781665184631</v>
+        <v>-0.485593074367479</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.6020582002028689</v>
+        <v>-0.6041340355600653</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.6436733963645764</v>
+        <v>-0.6456872685036359</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.6408204208818944</v>
+        <v>-0.6428427453696841</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.07567</t>
+          <t>X &lt; 0.07565</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3305</v>
+        <v>3308</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.2185925595969493</v>
+        <v>-0.2334619438132322</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.2070726943656638</v>
+        <v>-0.191840127998006</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.2475542094962933</v>
+        <v>-0.2319067036784972</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.3131666375240485</v>
+        <v>-0.3273181341016667</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.4811290747562254</v>
+        <v>-0.4960514143296919</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.4877511209706356</v>
+        <v>-0.472655181317549</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.4611430974711723</v>
+        <v>-0.4458661911972612</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.5720817782489149</v>
+        <v>-0.5566283267567798</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.5736921485066944</v>
+        <v>-0.558244078014333</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.6073114976811453</v>
+        <v>-0.5916275896512317</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.6471423075714355</v>
+        <v>-0.6314898438157712</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.6979567011222088</v>
+        <v>-0.6821815784675351</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.7194830782558483</v>
+        <v>-0.7335209523220598</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.7421869846839755</v>
+        <v>-0.7561515645235346</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.6591951604520574</v>
+        <v>-0.6730679133463227</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.6498655802730298</v>
+        <v>-0.6639068611324319</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.5548260545342671</v>
+        <v>-0.5689233072777569</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.5211449108325255</v>
+        <v>-0.5352502238933354</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.559022647584186</v>
+        <v>-0.5731550383850603</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.5052508310667818</v>
+        <v>-0.5194857355453024</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.5167493811865853</v>
+        <v>-0.5308370282820718</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.6352198734703123</v>
+        <v>-0.6491852776793081</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.7054662025746481</v>
+        <v>-0.71944464665048</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.7030372198777357</v>
+        <v>-0.7170029608199897</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.07829</t>
+          <t>X &lt; 0.07827</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3318</v>
+        <v>3322</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.2170726179627067</v>
+        <v>-0.2178276814439286</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.1470214712933284</v>
+        <v>-0.1478727156095374</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.1929326944543064</v>
+        <v>-0.1937805617699979</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.2610531302687846</v>
+        <v>-0.2618453345343923</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.3998015675051789</v>
+        <v>-0.4013278897976988</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.4056440711305314</v>
+        <v>-0.4071577936515141</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.3521428113409044</v>
+        <v>-0.3537491060315148</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.463702370119691</v>
+        <v>-0.4651859489737546</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.4951150136847744</v>
+        <v>-0.4965605005183349</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.4715747685212648</v>
+        <v>-0.4730770357535974</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.5101386292280523</v>
+        <v>-0.5115859294676213</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.5618030618030616</v>
+        <v>-0.5631993508166815</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.6176347526339754</v>
+        <v>-0.6190051319542391</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.6410840435075116</v>
+        <v>-0.6424351918985352</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.5609608387169231</v>
+        <v>-0.562432735830896</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.5493123377848903</v>
+        <v>-0.5507780507780495</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.4852136176449307</v>
+        <v>-0.4867621991947146</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.4821380776858248</v>
+        <v>-0.4836951951110109</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.5791969704624478</v>
+        <v>-0.5806307574943474</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.5550120409391965</v>
+        <v>-0.5564692732412766</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.5686069130629932</v>
+        <v>-0.5700682988474952</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.6869265489779153</v>
+        <v>-0.6882493398327867</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.7257075051484918</v>
+        <v>-0.7269747897313792</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.7537303173545737</v>
+        <v>-0.7549675907431066</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.08092</t>
+          <t>X &lt; 0.08089</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3325</v>
+        <v>3329</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.2093663280925</v>
+        <v>-0.2100595239331611</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.1401603802098847</v>
+        <v>-0.1409476957268723</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2188718614687062</v>
+        <v>-0.2196131100664971</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.2883512357910121</v>
+        <v>-0.2890335284788605</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.3976777075788505</v>
+        <v>-0.3990660669007582</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.4031154329582023</v>
+        <v>-0.404492076385722</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.381266490076051</v>
+        <v>-0.3826957126997641</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.4931846508560085</v>
+        <v>-0.4944902144818712</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.5543933966128947</v>
+        <v>-0.5556253139125999</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.5025934653081521</v>
+        <v>-0.503913867933079</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.4805942813181261</v>
+        <v>-0.4819328924313808</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.5626939736918786</v>
+        <v>-0.5639444876318862</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.620768322677911</v>
+        <v>-0.6219874661158045</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.6746189587422009</v>
+        <v>-0.6757818639006672</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.5360695140062148</v>
+        <v>-0.5374212193811232</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.5231882581490268</v>
+        <v>-0.5245366460529723</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.4594980682672869</v>
+        <v>-0.4609282553554976</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.4866629057152636</v>
+        <v>-0.4880650053981697</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.5830648166414534</v>
+        <v>-0.5843450732425666</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.5885776509462346</v>
+        <v>-0.5898460324445551</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.6333446397671807</v>
+        <v>-0.6345783133796203</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.7215374904896734</v>
+        <v>-0.7226687402723115</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.7296027876352795</v>
+        <v>-0.7307161175774297</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.7276524644945681</v>
+        <v>-0.728771585303889</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.08354</t>
+          <t>X &lt; 0.08351</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3332</v>
+        <v>3336</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.2016921956166655</v>
+        <v>-0.2023237433813634</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.1333279281470681</v>
+        <v>-0.1340515472791068</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.2447027229840941</v>
+        <v>-0.2453379265559903</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.3155353277460122</v>
+        <v>-0.3161083032590852</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.4254045590935718</v>
+        <v>-0.4266199416254395</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.4005973622289929</v>
+        <v>-0.4018374861448848</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.3804087619726388</v>
+        <v>-0.3816974185349196</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.4926750702033331</v>
+        <v>-0.4938391519120771</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.5237913202159348</v>
+        <v>-0.5249178481700341</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.5035959451927638</v>
+        <v>-0.5047710835004722</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.481068953100511</v>
+        <v>-0.4822634751379056</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.5037725432462281</v>
+        <v>-0.5049493520709163</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.5640622666432975</v>
+        <v>-0.5652023211383579</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.6182467857622669</v>
+        <v>-0.6193297153983224</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.5112824929608522</v>
+        <v>-0.5125143849135085</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.5271138004038534</v>
+        <v>-0.5283094098883581</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.4638394274524771</v>
+        <v>-0.4651157519032765</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.4911687560357763</v>
+        <v>-0.4924165100767084</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.5569493994562151</v>
+        <v>-0.5581126663267568</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.5620503597122308</v>
+        <v>-0.5632026495433919</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.5778705739154901</v>
+        <v>-0.5790214994590883</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.6960150927149513</v>
+        <v>-0.697027663897515</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.6734757076993887</v>
+        <v>-0.6745076765922491</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.6716721776429893</v>
+        <v>-0.6727094959546349</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/nasdaq_hourly_24hrs/volatility/bb_width_20.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/volatility/bb_width_20.xlsx
@@ -618,83 +618,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ 0.008807</t>
+          <t>X ≈ 0.008809</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-3.615188156351927</v>
+        <v>-4.646195010556994</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-5.052391450112772</v>
+        <v>-6.020014221097874</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-5.379464142817248</v>
+        <v>-6.139996593446803</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-8.299081890581562</v>
+        <v>-8.990037864216866</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-11.94875515918951</v>
+        <v>-12.65557820722584</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-17.29204467217955</v>
+        <v>-18.15493032599072</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-28.01298907115252</v>
+        <v>-29.12584771867552</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-32.72066872238082</v>
+        <v>-33.96111783267177</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-30.47653673357903</v>
+        <v>-29.31817891549278</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-30.14905884713623</v>
+        <v>-28.98821658297811</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-28.77810761950358</v>
+        <v>-27.59341484139835</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-29.06446978261883</v>
+        <v>-27.87716226459639</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-30.19233286668162</v>
+        <v>-28.99636945463208</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-27.09882801497997</v>
+        <v>-25.85389624156647</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-27.76356887392557</v>
+        <v>-26.54216669268952</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-27.17913861874349</v>
+        <v>-27.1239877307683</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-25.10371423131443</v>
+        <v>-24.96831286501368</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-21.88908038694863</v>
+        <v>-21.70604452399672</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-20.57095731618815</v>
+        <v>-20.36395455678593</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-21.50058941447536</v>
+        <v>-21.29117853393701</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-25.37970797787514</v>
+        <v>-24.13548394069709</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-22.13227570580099</v>
+        <v>-21.94701221958461</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-20.75413551559645</v>
+        <v>-20.57441498389292</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-17.5032450674974</v>
+        <v>-17.33407575318274</v>
       </c>
     </row>
     <row r="7">
@@ -704,2293 +704,2293 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3.399633952695972</v>
+        <v>3.339677511304039</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1.989459115312364</v>
+        <v>1.451741642229209</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-3.217321186196699</v>
+        <v>-3.635983742163702</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-6.086858507094988</v>
+        <v>-6.421536580808585</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-3.180546398890563</v>
+        <v>-3.401669340852358</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-5.156858723110979</v>
+        <v>-4.894775811523353</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-7.545968417417157</v>
+        <v>-6.784571200490838</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-7.824324027467853</v>
+        <v>-7.089295936998475</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-6.162746802137015</v>
+        <v>-5.314390934477366</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-5.311359207069373</v>
+        <v>-3.908854071856524</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-3.957650191808028</v>
+        <v>-2.538428101171007</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-2.071189875934834</v>
+        <v>-0.6133238639847889</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-2.64915525873699</v>
+        <v>-1.173589116397231</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-1.245712118146677</v>
+        <v>0.2302778414347415</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-2.444508675788981</v>
+        <v>-1.000991272647312</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-3.478905902966005</v>
+        <v>-2.094907201527263</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-6.325255936144281</v>
+        <v>-6.058553779478395</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-7.517384277263417</v>
+        <v>-7.848124026555638</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-6.219483775128772</v>
+        <v>-5.430469721195571</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-7.663560788941346</v>
+        <v>-7.425535678015322</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-8.75133000242505</v>
+        <v>-9.099096391041243</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-8.830527425537532</v>
+        <v>-8.625682811150639</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-9.646060577499028</v>
+        <v>-8.937724746074302</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-11.35590207232832</v>
+        <v>-10.76074576825054</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ 0.01405</t>
+          <t>X ≈ 0.01404</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-1.021252457049904</v>
+        <v>-1.455652209027704</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1.238857245176604</v>
+        <v>0.9229041275372225</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2.776297498889797</v>
+        <v>2.675854405812139</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2.811100736777334</v>
+        <v>3.213685671987797</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1.737487885927969</v>
+        <v>2.566266798636391</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.07090220451986085</v>
+        <v>0.8485397267475321</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>5.611282590941528</v>
+        <v>6.437473626048501</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>5.337586087045445</v>
+        <v>6.137431975432335</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>5.009314252908936</v>
+        <v>5.89127346196917</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>4.983935630780316</v>
+        <v>5.851389561967849</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>5.258213203901605</v>
+        <v>6.499906019136724</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>7.582709910162706</v>
+        <v>8.856637039077626</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>7.582129306859336</v>
+        <v>8.877388360193045</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>6.620040815871334</v>
+        <v>7.880286849583918</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>5.966239232958763</v>
+        <v>7.202978809603231</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>6.560889692025413</v>
+        <v>7.765089801435764</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>6.429524414443435</v>
+        <v>7.287547296528835</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>5.581855720107043</v>
+        <v>6.403640295564728</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>3.191347969004333</v>
+        <v>3.982379215657573</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>1.143054064250535</v>
+        <v>1.55973073015975</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>3.582919724032642</v>
+        <v>4.385591331496094</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>3.880459318970942</v>
+        <v>4.688152689624211</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>3.036545616484275</v>
+        <v>4.178157719695818</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>3.33423420281769</v>
+        <v>4.016696116457055</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ 0.01667</t>
+          <t>X ≈ 0.01665</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-1.264361292987267</v>
+        <v>-0.6545031971936197</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.2577486704689846</v>
+        <v>-0.2259950124125254</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-2.01826593384579</v>
+        <v>-1.133790305951266</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.0441389254313691</v>
+        <v>0.969546497746542</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.04107061427824732</v>
+        <v>1.033459015077135</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.1466778678236977</v>
+        <v>1.527853867861758</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1.728619874679907</v>
+        <v>3.09498020542442</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>2.461455001922772</v>
+        <v>3.805259691686224</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>4.85445237977509</v>
+        <v>6.292941192739242</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>5.766962294374117</v>
+        <v>7.188560570085187</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>5.705511878967471</v>
+        <v>7.124684567666506</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>5.428780262726839</v>
+        <v>6.850811727537447</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>7.34077054255166</v>
+        <v>8.782028875765569</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>7.796043169321592</v>
+        <v>9.213223807913444</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>8.490187499892194</v>
+        <v>9.550854820496092</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>5.381551636172219</v>
+        <v>6.734918850511761</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>5.924077675349139</v>
+        <v>7.310199968377937</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>7.16957586166447</v>
+        <v>8.532774806783365</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>7.724836677332455</v>
+        <v>9.088247104098187</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>7.914407908550643</v>
+        <v>9.305898408404559</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>9.062049542673641</v>
+        <v>10.43487332884789</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>7.63873137540768</v>
+        <v>9.007981530136426</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>8.253208255246633</v>
+        <v>9.593201261747701</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>8.517775953523618</v>
+        <v>9.773012074244072</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ 0.01929</t>
+          <t>X ≈ 0.01927</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.6210033032596911</v>
+        <v>0.3562496410079419</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-1.514231012546468</v>
+        <v>-0.9406218198392367</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.2603653091365175</v>
+        <v>0.6280682293044464</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>2.05829256120245</v>
+        <v>2.500509732383932</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2.075683998841924</v>
+        <v>2.58071729441172</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.900762825855914</v>
+        <v>2.03552716042433</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.119701015483244</v>
+        <v>1.245080320255049</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3.20542994862123</v>
+        <v>3.056961809796739</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2.737367399571568</v>
+        <v>2.127025397415125</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>3.250572784160738</v>
+        <v>2.392795398132208</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>3.375089382248049</v>
+        <v>2.311994793239975</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>2.224254412621463</v>
+        <v>1.331228989027778</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.398071691842617</v>
+        <v>1.28144779203182</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.900045685408116</v>
+        <v>1.740811473987598</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>3.328907291392184</v>
+        <v>2.475748233768641</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>5.007282721755075</v>
+        <v>3.74441744668944</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>5.237465043469129</v>
+        <v>3.996325882053817</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>3.689310492701161</v>
+        <v>2.096653659301843</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>1.014279625495696</v>
+        <v>-0.5190281056401247</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>2.286539884210349</v>
+        <v>0.7570849563517541</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>2.468657872361348</v>
+        <v>0.8982668685620609</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>2.393508851793214</v>
+        <v>0.8229432651549971</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>1.582029684390243</v>
+        <v>0.3574554795137459</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>0.05714140593254768</v>
+        <v>-0.8688920007649443</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ 0.02191</t>
+          <t>X ≈ 0.02189</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.1262295783673011</v>
+        <v>-1.019405811331588</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.892880156401141</v>
+        <v>1.793724626704453</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.804079147442074</v>
+        <v>3.227368284283223</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1.840577416177275</v>
+        <v>-0.8014848821680403</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2.18074161985966</v>
+        <v>-1.073865911608756</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.4225731592745561</v>
+        <v>0.6144554124782218</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-2.774674794321072</v>
+        <v>-1.706769961333237</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-3.84228717544265</v>
+        <v>-2.776019042187443</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-7.735636666396211</v>
+        <v>-6.100291037440897</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-12.05564169510183</v>
+        <v>-10.34619418726275</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-13.3541260924903</v>
+        <v>-11.23140459457942</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-14.02757596412236</v>
+        <v>-11.89639176215065</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-14.76611962737275</v>
+        <v>-12.6264408431719</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-13.96780479061817</v>
+        <v>-12.11180387810382</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-12.42494700907939</v>
+        <v>-10.8744050813029</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-11.98981993182151</v>
+        <v>-10.70385439322683</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-11.3410845805742</v>
+        <v>-10.04273449035174</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-12.23927632562945</v>
+        <v>-10.94990286349741</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-12.81763469286764</v>
+        <v>-11.51079372565749</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-12.24309576850185</v>
+        <v>-10.91718782966802</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-11.6079070987622</v>
+        <v>-10.7191385352937</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-12.874578438946</v>
+        <v>-11.95747612237949</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-14.18735901584482</v>
+        <v>-13.6500251579761</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-14.27092183517426</v>
+        <v>-13.43358435269133</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ 0.02453</t>
+          <t>X ≈ 0.0245</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2.561443603909694</v>
+        <v>3.454735922900618</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>4.117991386939423</v>
+        <v>5.056671070448814</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.153529642360894</v>
+        <v>2.32149944223557</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>4.596354401003204</v>
+        <v>5.626224929046806</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>3.49857076347331</v>
+        <v>4.818592875472206</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.928771117574748</v>
+        <v>4.074390605277976</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>6.534796984275481</v>
+        <v>7.352951513436764</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>7.76963374845198</v>
+        <v>8.534007887773555</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>8.188100548217434</v>
+        <v>9.037396771081639</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>10.0600268909173</v>
+        <v>10.84246792256079</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>9.576707472359992</v>
+        <v>10.00821440850811</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>7.021546105482301</v>
+        <v>7.883396823007516</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>5.129463068472525</v>
+        <v>6.404059820189339</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>5.667045687126603</v>
+        <v>6.901150183379976</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>3.86684910468631</v>
+        <v>5.108591490096039</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>3.705566878418978</v>
+        <v>4.928760742914264</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>4.18132997041333</v>
+        <v>5.198501784600573</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>4.308733642534349</v>
+        <v>5.067184993351134</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>5.284113451261668</v>
+        <v>6.027255088143093</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>6.611168668477575</v>
+        <v>6.61622325191243</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>4.551116966049712</v>
+        <v>5.304482279973527</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>4.855739133138194</v>
+        <v>4.857422543079643</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>6.12799323358368</v>
+        <v>6.221111810414889</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>6.434228527770962</v>
+        <v>6.292111492407493</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ 0.02715</t>
+          <t>X ≈ 0.02712</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.155989109295504</v>
+        <v>0.6952345892341967</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>4.913645919494378</v>
+        <v>5.242646178900401</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>7.537270566946042</v>
+        <v>6.265395960662417</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>3.238697858784739</v>
+        <v>3.159572139997742</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.3295253235840434</v>
+        <v>-0.6348555007188494</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>4.101169676318406</v>
+        <v>3.543401442943463</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.783660932354081</v>
+        <v>1.521316511375638</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.500811760383904</v>
+        <v>2.225084050317378</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>4.612549289969536</v>
+        <v>5.878624738219052</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>6.385808297746522</v>
+        <v>7.103544379310577</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>2.560017173390911</v>
+        <v>3.852809558734791</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>2.269673451900253</v>
+        <v>2.570925271435996</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>6.240020184475277</v>
+        <v>6.505185747761821</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>4.484975565997608</v>
+        <v>4.745793580037457</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>4.835562914786529</v>
+        <v>5.07653769172348</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>2.872180834873276</v>
+        <v>3.618243836720445</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>3.247266748297626</v>
+        <v>3.515534280548103</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>2.110506762021352</v>
+        <v>2.370268374118815</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>3.660729346528491</v>
+        <v>3.090582048988544</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>2.627348754169155</v>
+        <v>1.785125442078886</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>2.079917320939629</v>
+        <v>1.214777559905855</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>3.346585577955935</v>
+        <v>2.660583609633186</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>3.621360712530979</v>
+        <v>2.203928492606487</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>3.86427630002396</v>
+        <v>2.041789498317023</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ 0.02978</t>
+          <t>X ≈ 0.02974</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.317759067837208</v>
+        <v>2.193178525716945</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>6.166283109030147</v>
+        <v>6.520333214089781</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>4.130397142622741</v>
+        <v>5.843923842557643</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.417153302639953</v>
+        <v>4.109946836393725</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.479895206698089</v>
+        <v>3.267276452754778</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>5.065785209231649</v>
+        <v>5.710887827196686</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>4.888678587249288</v>
+        <v>4.918451930263409</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.4172662427083154</v>
+        <v>0.0384351626618411</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.336861694345281</v>
+        <v>-1.552627783060466</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.71214406556291</v>
+        <v>-2.347381098144005</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-3.04005508525178</v>
+        <v>-3.222747724484009</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.526357636372836</v>
+        <v>-1.203840248909714</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-4.452659455470396</v>
+        <v>-4.043363462303262</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.679726355869079</v>
+        <v>-0.8443510711368205</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-5.935436424669113</v>
+        <v>-4.405766262333884</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-4.143840745637178</v>
+        <v>-3.272317561327021</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-1.284537973227074</v>
+        <v>-0.4983259449106825</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.1949421532703681</v>
+        <v>-0.05808505559113541</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-1.776646057965323</v>
+        <v>-1.000816636156109</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.3921954575782038</v>
+        <v>0.3660696858538088</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>0.6307781285983651</v>
+        <v>1.527476984906649</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-1.840277413649055</v>
+        <v>-1.657557581533709</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-5.158617072424498</v>
+        <v>-3.726061824579041</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-4.03684453522861</v>
+        <v>-3.310166136787508</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 0.0324</t>
+          <t>X ≈ 0.03235</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.968940582542189</v>
+        <v>-3.529564626184268</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-4.301366455868077</v>
+        <v>-5.042505384630005</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.6495758850603366</v>
+        <v>0.01021316059447486</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.7076765817113895</v>
+        <v>-0.5785969601840435</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-4.89818956890231</v>
+        <v>-5.258894271723662</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.147216138500276</v>
+        <v>-1.954785393130614</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>3.209040305814426</v>
+        <v>2.923865004107782</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2.289803220035857</v>
+        <v>2.343910454173134</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.514863444203357</v>
+        <v>-1.94062731358806</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-4.210856043316774</v>
+        <v>-3.361460271549774</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.5503830860246381</v>
+        <v>1.967982545526034</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.2716336825766419</v>
+        <v>1.697300035719245</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>6.199753667002575</v>
+        <v>6.920824215890484</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>4.055597867479058</v>
+        <v>4.776730189365232</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>3.3974545698985</v>
+        <v>4.105717603990591</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>3.350815850815849</v>
+        <v>4.670259752080128</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>5.13997563691531</v>
+        <v>6.473141514313447</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>3.753083651042836</v>
+        <v>4.440321138081984</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>2.686923749915884</v>
+        <v>3.38612172675802</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.9506926368070623</v>
+        <v>1.692081230096534</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>1.69019775089216</v>
+        <v>1.760633547615711</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>1.614351789483209</v>
+        <v>1.048528350501186</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>0.6067752199139065</v>
+        <v>0.0182774854610912</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>1.171968607716266</v>
+        <v>0.4930811663307963</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ 0.03502</t>
+          <t>X ≈ 0.03497</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.838186098478481</v>
+        <v>-1.737668536989901</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-4.587898901030485</v>
+        <v>-3.791158147950121</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-8.456775838963978</v>
+        <v>-8.667016849807347</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-4.335175617765984</v>
+        <v>-4.434240766786793</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.7048116952271002</v>
+        <v>-0.489689480813766</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.72996672125079</v>
+        <v>-1.537519437860382</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-6.744339647565518</v>
+        <v>-6.555835381088968</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-6.416490486257999</v>
+        <v>-6.258936453861288</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-8.193185122525037</v>
+        <v>-7.605260378678778</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-8.966100798561598</v>
+        <v>-9.008167621257712</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-7.479919944278457</v>
+        <v>-8.743480022643695</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-8.9707905598476</v>
+        <v>-9.632113252948983</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-10.70001323276433</v>
+        <v>-11.96691907854319</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-9.708970897089706</v>
+        <v>-11.01395006645175</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-6.730750558306624</v>
+        <v>-7.460517268521102</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-7.348484848484844</v>
+        <v>-8.121880310556087</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-7.482401985462317</v>
+        <v>-7.625499712793292</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-2.132697234738046</v>
+        <v>-1.684956320298255</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-1.91680585381372</v>
+        <v>-2.086877069572822</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-1.123899437785091</v>
+        <v>-0.6585974105514936</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.4543243936298396</v>
+        <v>-0.2395218042562846</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-2.954412779281498</v>
+        <v>-2.753708716455471</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>1.562486175624855</v>
+        <v>1.148462354188766</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.9375885018408354</v>
+        <v>-1.452701030344528</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 0.03764</t>
+          <t>X ≈ 0.03759</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>156</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.056336243444669</v>
+        <v>-1.599340262363469</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-9.429590676724132</v>
+        <v>-10.09418305932726</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-7.042499130684604</v>
+        <v>-6.265276616987329</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.3573662110247753</v>
+        <v>0.1096335786018869</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>3.15299716258194</v>
+        <v>3.653924800545816</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.134835143550923</v>
+        <v>1.263100672870031</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.6449377417119706</v>
+        <v>1.109426190224504</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.648777579010144</v>
+        <v>1.450679245649376</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>5.536418607078687</v>
+        <v>5.386542594260646</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>6.045554213093553</v>
+        <v>5.87768551964372</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>6.319613855255476</v>
+        <v>6.792051595232238</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>6.681890092833058</v>
+        <v>6.529599656617606</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.994625461874371</v>
+        <v>3.522253276588529</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.8504696623508536</v>
+        <v>1.36468008157113</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>2.756428928872793</v>
+        <v>2.60189742097635</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>5.273892773892783</v>
+        <v>5.080226730977358</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>5.781001277940945</v>
+        <v>5.616301018425425</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>3.753083651042914</v>
+        <v>4.209091075716231</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>7.174103237095359</v>
+        <v>8.909271508603567</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>9.284025970140391</v>
+        <v>10.41235046447899</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>10.02353108422565</v>
+        <v>11.1269572451496</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>10.58871076384211</v>
+        <v>12.3338460052456</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>9.581134194272821</v>
+        <v>11.29542920847262</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>9.505301941049545</v>
+        <v>10.49226457315752</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 0.04026</t>
+          <t>X ≈ 0.0402</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.828837808241893</v>
+        <v>-2.249088028219305</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.036380890138993</v>
+        <v>0.9069178442397146</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.632130355770705</v>
+        <v>-3.747152106835323</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.504748240759618</v>
+        <v>-2.641895868235295</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.520805824508088</v>
+        <v>0.4920692767663439</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.8674358761517311</v>
+        <v>0.6444365366015958</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.09548719226143731</v>
+        <v>-0.9984599507435519</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.023060386945431</v>
+        <v>-1.298306676193363</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.6990990638768011</v>
+        <v>-0.3185043170298769</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.9141527466134818</v>
+        <v>-1.962004171917563</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.6400931044515588</v>
+        <v>-0.838527154982458</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.07850637344576228</v>
+        <v>-0.2612725898429744</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.479003828605677</v>
+        <v>0.3321089248935181</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.42274731674847</v>
+        <v>-1.630281892669174</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.4002183454213721</v>
+        <v>-0.6044752432419216</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.1941685765215198</v>
+        <v>-0.04619113004504527</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-3.301093098271124</v>
+        <v>-3.587736544771843</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.8849253987310135</v>
+        <v>-1.148010557981223</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-1.509370152260367</v>
+        <v>-1.802844606720022</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-1.322524342292489</v>
+        <v>-0.1977291111177735</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-1.865070510258519</v>
+        <v>0.09689535301874486</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>1.42042806614765</v>
+        <v>2.607939727615225</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.8261056247315537</v>
+        <v>0.265367316341937</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>1.619070525406521</v>
+        <v>2.689435218604139</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 0.04288</t>
+          <t>X ≈ 0.04281</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>4.112371519565059</v>
+        <v>2.087744340396483</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-6.561830808333504</v>
+        <v>-5.878503062309285</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.965367098743812</v>
+        <v>-1.971722116181894</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-3.540390083703834</v>
+        <v>-4.296546182223111</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-3.014111590733826</v>
+        <v>-3.699928296425902</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-3.689214370153685</v>
+        <v>-8.698504646166853</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.874956157492313</v>
+        <v>-6.054591657146879</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.295108259823529</v>
+        <v>-1.202013780723192</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>3.922802338290005</v>
+        <v>1.49671083250373</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>3.149886662253515</v>
+        <v>-0.1324483525026281</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.699808373380961</v>
+        <v>-3.29632866623524</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.421058969932965</v>
+        <v>-3.567322690616599</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.884103799628612</v>
+        <v>-0.3646954201867203</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>4.387162854216463</v>
+        <v>1.112769276095911</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>2.004881625601421</v>
+        <v>-0.4279524446915062</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>5.185475444096141</v>
+        <v>2.726935360468886</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>5.913627272635949</v>
+        <v>3.48945323253448</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>4.08464863778029</v>
+        <v>1.622789599448808</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>6.024677949739051</v>
+        <v>4.445255658216055</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>7.935661690741597</v>
+        <v>6.398972538057592</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>8.255184488292819</v>
+        <v>7.570658471459566</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>6.455200595849185</v>
+        <v>6.625930732112884</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>8.453813239365715</v>
+        <v>9.478260869565226</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>5.791774089590724</v>
+        <v>7.576991440493096</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.0455</t>
+          <t>X ≈ 0.04543</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-5.24201878273162</v>
+        <v>-4.062010611795927</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-3.975623911781781</v>
+        <v>-4.30958204096558</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-6.455309627479494</v>
+        <v>-6.564758260515028</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-8.209930313588842</v>
+        <v>-8.145990422720573</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-6.462387452802787</v>
+        <v>-7.431886302689662</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-5.233754600038743</v>
+        <v>-3.290502457450984</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-4.964036617262423</v>
+        <v>-5.083569697142813</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-5.242248062015442</v>
+        <v>-5.391819327483056</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-4.15909421343413</v>
+        <v>-5.262225824333164</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.848676556137285</v>
+        <v>-3.507607717070726</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-3.616283580642033</v>
+        <v>-4.237085050431958</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-5.978366317423358</v>
+        <v>-6.519552598643017</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-5.018195050946204</v>
+        <v>-6.649247232011312</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-6.280940594059402</v>
+        <v>-5.910140903441707</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-5.897417224973296</v>
+        <v>-5.607335443991147</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-3.219696969696969</v>
+        <v>-3.045049364201027</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-2.311947440007778</v>
+        <v>-2.14623348572659</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.3334548104956809</v>
+        <v>-0.271662881295029</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>1.965769903762038</v>
+        <v>1.573055394711446</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>1.110949047063393</v>
+        <v>1.787641839770487</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.5684028790974267</v>
+        <v>1.220197338389639</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>1.534223584354933</v>
+        <v>2.155135826535414</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>4.933698296836994</v>
+        <v>5.42907334211683</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>2.774532710280376</v>
+        <v>3.246732327625345</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.04813</t>
+          <t>X ≈ 0.04805</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2.697181055582199</v>
+        <v>4.473931643790017</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>5.179305665683003</v>
+        <v>5.46039657839907</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3.741286616652182</v>
+        <v>2.977425282772245</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>4.436783301434623</v>
+        <v>-0.08108531552107934</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.1243592837886993</v>
+        <v>-2.816837466715555</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-2.754294506142031</v>
+        <v>-6.357474124609347</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-6.343144598483086</v>
+        <v>-7.150736325029783</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.9875532263349101</v>
+        <v>-4.990913227812477</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.870835364030654</v>
+        <v>-2.400970495220953</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>2.506370392219516</v>
+        <v>-1.96101059650281</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>4.188880738606791</v>
+        <v>0.7748140350725805</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>8.135483447834773</v>
+        <v>4.203903616093307</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>7.01232138097874</v>
+        <v>3.086429574221782</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>6.79124250453215</v>
+        <v>1.596433696186004</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>6.133099206951591</v>
+        <v>0.9002280898162667</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>3.910584720443794</v>
+        <v>0.216740370323528</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.9597661750156945</v>
+        <v>-2.38381410256406</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.8549254711945125</v>
+        <v>0.7525325615050633</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>5.296168964794909</v>
+        <v>4.71699478865083</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>2.666113366312302</v>
+        <v>1.181581233709899</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>2.123567198346031</v>
+        <v>0.6141367323290154</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-2.177630875739041</v>
+        <v>-1.961025789626269</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-1.903156163256988</v>
+        <v>-1.717391304347892</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.8379129919705122</v>
+        <v>3.120469701362715</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.05075</t>
+          <t>X ≈ 0.05067</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-4.48830474055061</v>
+        <v>-3.635543491713314</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.956579478048781</v>
+        <v>1.223545615453887</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>3.908390937492221</v>
+        <v>1.634898735138258</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-3.584224098899575</v>
+        <v>-4.043916053820489</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-3.920014571446849</v>
+        <v>-6.059854826377951</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.3432178768749452</v>
+        <v>-2.477910013625241</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>10.74924021889576</v>
+        <v>8.630922110541064</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>7.081198265668206</v>
+        <v>6.613496063755065</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>3.732854939108243</v>
+        <v>3.353580472125586</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.265024008834459</v>
+        <v>-0.8907114207490068</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.850746857478192</v>
+        <v>-3.035250372615906</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.260334247548485</v>
+        <v>0.08141045889477283</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>3.527002689166892</v>
+        <v>2.367328119082295</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.778821949991602</v>
+        <v>-1.315957072582655</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.7420499933348808</v>
+        <v>-0.3130271911037994</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-0.1476630713917899</v>
+        <v>0.2500636907936311</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>1.413335045867932</v>
+        <v>2.954382183908045</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-2.081336166427825</v>
+        <v>-0.6267777833225736</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.1705295312662187</v>
+        <v>1.311822374857684</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.01631627870172281</v>
+        <v>1.526408819916618</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-2.221145143501403</v>
+        <v>-0.7651736124984012</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.6020758506732236</v>
+        <v>0.8838017965807978</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>1.367314116046117</v>
+        <v>2.851574212893603</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>1.291481862822749</v>
+        <v>2.689435218604096</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.05337</t>
+          <t>X ≈ 0.05328</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.461193702894555</v>
+        <v>-1.028063621314537</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>5.208049557605918</v>
+        <v>4.774573232302004</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>5.810846835105593</v>
+        <v>5.349976217789127</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-3.065372490459595</v>
+        <v>-7.193882291698742</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.360346636476265</v>
+        <v>-5.687887033739841</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.8674358761518022</v>
+        <v>-3.385322359780517</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>6.217936171853225</v>
+        <v>1.892411161967289</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.858092074038922</v>
+        <v>-4.485324815421855</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.182053397107609</v>
+        <v>-8.308852216417399</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>3.167479906447745</v>
+        <v>-1.371894002898976</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.400723222079058</v>
+        <v>-3.1967463669354</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-5.000475160960775</v>
+        <v>-8.373441708126151</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-12.24608620740879</v>
+        <v>-14.35869166784151</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-4.30389977773288</v>
+        <v>-7.393520040205594</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.8804104222522042</v>
+        <v>-2.856320665918155</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-6.40847247990105</v>
+        <v>-7.010702921608328</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-10.62402226993975</v>
+        <v>-11.11458333333334</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-4.606413994169031</v>
+        <v>-5.247467438494823</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-10.51297159283654</v>
+        <v>-11.03300521134905</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-12.36694210939919</v>
+        <v>-12.81841876629018</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-16.99112093042638</v>
+        <v>-17.38586326767086</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-12.98533423877432</v>
+        <v>-13.4610257896262</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-10.67004319976166</v>
+        <v>-11.21739130434776</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-12.78669177951549</v>
+        <v>-13.37953029863723</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.05599</t>
+          <t>X ≈ 0.0559</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-3.640847113431967</v>
+        <v>-6.603851217906517</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-9.744854681012555</v>
+        <v>-8.890574380140997</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-9.259796806966619</v>
+        <v>-8.104452155501967</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-8.049673903332433</v>
+        <v>-6.65603802777958</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-4.53931052972586</v>
+        <v>-4.890779841348298</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-4.352344343628538</v>
+        <v>-4.733846235350214</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-8.970446873672678</v>
+        <v>-9.61056090064416</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-3.479427549194988</v>
+        <v>-3.793032364460942</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-3.437940367280284</v>
+        <v>-1.62428712824623</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.558374725913993</v>
+        <v>3.702110356126276</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>9.524742060383609</v>
+        <v>12.13761067685306</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>11.16906958001253</v>
+        <v>13.90184504891243</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>11.96898443623335</v>
+        <v>14.82776925799222</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>5.978674790555928</v>
+        <v>8.457086216967262</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>9.166685339129266</v>
+        <v>11.85656448814338</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>11.68414918414913</v>
+        <v>14.45868483349372</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>11.55023204717172</v>
+        <v>14.35480442176871</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>7.59923749719664</v>
+        <v>10.14028766354582</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>9.738205801197871</v>
+        <v>10.35474989069159</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>11.84812853424289</v>
+        <v>12.61015266228125</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>7.459428520122962</v>
+        <v>7.961075507839226</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>11.22973640486776</v>
+        <v>11.96754563894518</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>1.888826501965191</v>
+        <v>2.007098491570545</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>1.812994248741809</v>
+        <v>1.844959497281032</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.05861</t>
+          <t>X ≈ 0.05851</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>5.734152886568033</v>
+        <v>10.97350230414747</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.8506239117817813</v>
+        <v>-5.401436789620917</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-2.288642960812687</v>
+        <v>-3.430324439899685</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-6.126596980255599</v>
+        <v>-7.248533090320819</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-3.337387452802787</v>
+        <v>-1.072478327194254</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-6.275421266705408</v>
+        <v>-0.91554472119617</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-10.17236995059567</v>
+        <v>-4.936433185041793</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-13.57558139534892</v>
+        <v>-8.467160080063309</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-10.40909421343422</v>
+        <v>-8.3392311703792</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-14.30700988947062</v>
+        <v>-12.36108911721145</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-17.1579502473087</v>
+        <v>-15.31466055422001</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-14.31169965075669</v>
+        <v>-12.3654360570785</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-18.55986171761273</v>
+        <v>-16.706134626142</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-12.53094059405922</v>
+        <v>-10.5027557843493</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-13.18908389163987</v>
+        <v>-11.18491016623435</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-6.344696969696884</v>
+        <v>-4.171993244188975</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.228614106674442</v>
+        <v>2.175739247311824</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-3.458454810495624</v>
+        <v>-1.182951309462673</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-3.242563429571298</v>
+        <v>2.257317369295997</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-6.180717619603271</v>
+        <v>-0.7539026372579158</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.4732637875693015</v>
+        <v>5.130265764587151</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-3.674109748978402</v>
+        <v>1.829296791019054</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-3.399635036496264</v>
+        <v>2.072931276297339</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-3.475467289719539</v>
+        <v>1.91079228200779</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.06123</t>
+          <t>X ≈ 0.06113</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.009268166063613</v>
+        <v>-1.161674347158282</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>11.81384977242875</v>
+        <v>12.87813310285219</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>13.0074096707661</v>
+        <v>11.62343900096068</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>9.662876703955163</v>
+        <v>8.650084421200148</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>11.95866517877616</v>
+        <v>10.75547866205305</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>14.77721031224196</v>
+        <v>10.91241226805108</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.8473668915093526</v>
+        <v>-1.787431648943553</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.062423500611921</v>
+        <v>-4.473304473304474</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.020936318697217</v>
+        <v>-4.345375563620365</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>5.100884847371482</v>
+        <v>2.001430084017436</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>13.26968133163867</v>
+        <v>9.416522241478901</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>12.99093192819068</v>
+        <v>9.139940287007605</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>19.76250670343975</v>
+        <v>15.16790531241393</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>9.015112037519543</v>
+        <v>5.395861727171358</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>18.88328452941251</v>
+        <v>14.23751686909576</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>19.47767145135566</v>
+        <v>14.79882088791548</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>19.34375431437827</v>
+        <v>14.69494047619055</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>21.8704925579255</v>
+        <v>16.94300875198131</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>16.82322604411298</v>
+        <v>12.39556621722234</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>19.64165080144936</v>
+        <v>14.99110504323363</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>16.46752568611492</v>
+        <v>12.04270816090052</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>16.39167972470582</v>
+        <v>11.96754563894523</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>14.03457548981937</v>
+        <v>9.83022774327123</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>11.32716428922766</v>
+        <v>7.287136368029373</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.06385</t>
+          <t>X ≈ 0.06374</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.769409296824556</v>
+        <v>3.214130028646281</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.434632498474627</v>
+        <v>2.96822319294229</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3.560716013546234</v>
+        <v>1.713529091050709</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.2836594300008173</v>
+        <v>-1.581575810460293</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.511971521556156</v>
+        <v>0.8455687521431514</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-7.557472548756621</v>
+        <v>-9.8083084526695</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-13.4576263608521</v>
+        <v>-16.00879587030762</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-13.73583780560524</v>
+        <v>-16.31371631371632</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-16.25845318779311</v>
+        <v>-18.88849010673491</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-11.90316373562447</v>
+        <v>-14.27913619654885</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-14.19320665756511</v>
+        <v>-14.00690118194451</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-11.90785349691054</v>
+        <v>-14.28348313641581</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-18.15922069197179</v>
+        <v>-20.80378065927191</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-10.68799187611076</v>
+        <v>-12.94390661259714</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-11.34613517369117</v>
+        <v>-13.62606099448189</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-8.187645687645691</v>
+        <v>-7.65935157025698</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-10.8856653887258</v>
+        <v>-13.16863738738746</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-5.862300964341848</v>
+        <v>-7.896116087143668</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-8.210512147520085</v>
+        <v>-10.38435656270059</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-5.459563773449425</v>
+        <v>-7.467067414938832</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-3.438007377312893</v>
+        <v>-5.331809213616857</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-6.077955902824556</v>
+        <v>-8.109674438274851</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-3.239378626240018</v>
+        <v>-5.163337250293843</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.7511083153605824</v>
+        <v>-2.622773541880527</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.06648</t>
+          <t>X ≈ 0.06636</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>5.73415288656799</v>
+        <v>5.280902683654062</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>11.64937608821822</v>
+        <v>10.91734878912671</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>7.086357039187185</v>
+        <v>9.662654687235126</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-3.001596980255513</v>
+        <v>0.2467230766621995</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-3.337387452802744</v>
+        <v>-0.02883506343713549</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-12.52542126670541</v>
+        <v>-8.695430869203761</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-10.17236995059576</v>
+        <v>-6.549336410848241</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-13.57558139534883</v>
+        <v>-9.795433324845099</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-10.40909421343413</v>
+        <v>-6.726327944572752</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-11.18200988947062</v>
+        <v>-7.52237943979209</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-7.782950247308698</v>
+        <v>-7.250144425187756</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-4.936699650756694</v>
+        <v>-1.644373438482582</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-2.934861717612812</v>
+        <v>0.181910914654793</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>3.094059405940598</v>
+        <v>5.816029794398325</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-3.81408389163996</v>
+        <v>-0.748477528663372</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-9.469696969696969</v>
+        <v>-9.010702921608328</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.2286141066744847</v>
+        <v>2.650122549019564</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-3.458454810495667</v>
+        <v>-0.4239380267302764</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>3.007436570428702</v>
+        <v>5.672877141592011</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>0.06928238039672863</v>
+        <v>2.946287116062763</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>5.776736212430698</v>
+        <v>8.261195555858507</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>8.825890251021555</v>
+        <v>11.12720950449141</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>5.975364963503736</v>
+        <v>8.42966751918167</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>9.024532710280418</v>
+        <v>11.2087049954805</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.0691</t>
+          <t>X ≈ 0.06897</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.91470844212359</v>
+        <v>-1.542626728110541</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-2.123772059929934</v>
+        <v>-5.788533563814468</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-7.265494812664627</v>
+        <v>-11.04322766570605</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>10.5400696864112</v>
+        <v>8.364370135485672</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>6.500575510160175</v>
+        <v>4.088811995386394</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>6.687541696257554</v>
+        <v>4.245745601384478</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>13.32300041977461</v>
+        <v>11.45066358915176</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>13.04478897502153</v>
+        <v>11.14574314574314</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>9.382572453232527</v>
+        <v>7.273672055427248</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>1.202249369788632</v>
+        <v>-1.522379439792083</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>5.180012715654264</v>
+        <v>2.749855574812244</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>4.901263312206268</v>
+        <v>2.473273620340947</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>14.88921235646126</v>
+        <v>13.35838150289018</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>3.55702236890351</v>
+        <v>1.110147441457123</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>6.602582775026697</v>
+        <v>4.427993059571953</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>7.196969696969688</v>
+        <v>4.989297078391672</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.3443548474151328</v>
+        <v>-3.114583333333272</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>3.254508152467395</v>
+        <v>0.7525325615051202</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.2333041703120458</v>
+        <v>-3.033005211349156</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.04645836034401896</v>
+        <v>-2.818418766290172</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-4.292708232013744</v>
+        <v>-3.385863267670906</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-4.368554193422789</v>
+        <v>-3.461025789626134</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.3903757772370966</v>
+        <v>0.7826086956521792</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>6.94119937694699</v>
+        <v>8.620469701362659</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.07172</t>
+          <t>X ≈ 0.07159</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-7.807513780098638</v>
+        <v>-3.542626728110655</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-12.30895724511515</v>
+        <v>-7.634687409968336</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-9.580309627479444</v>
+        <v>-5.043227665706048</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.959930313588906</v>
+        <v>2.056677827793472</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-6.462387452802787</v>
+        <v>-2.06503415845976</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-2.108754600038679</v>
+        <v>1.938053293692221</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1.285963382737634</v>
+        <v>4.989125127613356</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.007751937984501</v>
+        <v>4.68420468420468</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>13.54923911989927</v>
+        <v>16.35059513235037</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>4.442990110529436</v>
+        <v>7.862235944823354</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.5503830860246381</v>
+        <v>4.288317113273784</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-3.89503298409003</v>
+        <v>0.1655813126486336</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>3.315138282387188</v>
+        <v>6.742996887505562</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-5.239273927392674</v>
+        <v>-1.19754486623529</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-1.730750558306624</v>
+        <v>1.966454598033607</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-9.469696969696969</v>
+        <v>-5.164549075454481</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-9.603614106674385</v>
+        <v>-5.268429487179439</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-13.87512147716223</v>
+        <v>-9.24746743849488</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-13.65923009623791</v>
+        <v>-9.033005211349106</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-13.47238428626994</v>
+        <v>-8.818418766290179</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-14.01493045423597</v>
+        <v>-13.23201711382476</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-14.09077641564507</v>
+        <v>-13.30717963578005</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-5.482968369829685</v>
+        <v>-5.371237458193974</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>2.774532710280376</v>
+        <v>2.158931239824255</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.07434</t>
+          <t>X ≈ 0.07421</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>8.859152886568033</v>
+        <v>6.457373271889402</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-3.975623911781739</v>
+        <v>-7.121866897147754</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>7.086357039187227</v>
+        <v>4.956772334293994</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.1234030197444866</v>
+        <v>4.364370135485728</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-6.462387452802787</v>
+        <v>-2.577854671280321</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-6.27542126670545</v>
+        <v>-2.420921065282279</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-7.047369950595801</v>
+        <v>-3.216003077514998</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>5.174418604651166</v>
+        <v>9.812409812409896</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-13.53409421343422</v>
+        <v>-10.05966127790609</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.807009889470621</v>
+        <v>2.477620560207818</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-14.0329502473087</v>
+        <v>-10.58347775852118</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.811699650756694</v>
+        <v>2.473273620340947</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-15.43486171761281</v>
+        <v>-11.97495183044316</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>3.094059405940513</v>
+        <v>7.776814108123823</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>2.43591610836004</v>
+        <v>7.094659726238667</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>3.030303030302946</v>
+        <v>7.655963745058244</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-3.353614106674527</v>
+        <v>0.8854166666664725</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-3.458454810495624</v>
+        <v>0.7525325615049709</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-9.492563429571383</v>
+        <v>-5.699671878016019</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-9.305717619603271</v>
+        <v>-5.485085432956843</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-9.848263787569216</v>
+        <v>-6.052529934337578</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-9.924109748978488</v>
+        <v>-6.127692456292955</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-15.89963503649635</v>
+        <v>-12.55072463768116</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-15.97546728971962</v>
+        <v>-12.71286363197062</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.07696</t>
+          <t>X ≈ 0.07683</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>14</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.502010029425129</v>
+        <v>3.600230414746541</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>10.31009037393251</v>
+        <v>10.49718072189977</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>8.872071324901519</v>
+        <v>9.242486620008187</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>15.30197444831586</v>
+        <v>8.65008442120002</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>22.10904111862578</v>
+        <v>15.51738342395787</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>15.15315016186597</v>
+        <v>8.531459887098769</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>21.52405862083277</v>
+        <v>14.87923501772319</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>21.24584717607969</v>
+        <v>14.57431457431451</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>14.1444772151373</v>
+        <v>7.559386341141426</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>27.65727582481499</v>
+        <v>21.04904913163648</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>27.93133546697707</v>
+        <v>21.32128414624091</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>27.65258606352901</v>
+        <v>21.04470219176952</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>26.52942399667295</v>
+        <v>19.92981007431874</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>26.30834512022642</v>
+        <v>26.82443315574267</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>25.65020182264575</v>
+        <v>18.99942163100058</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>26.24458874458885</v>
+        <v>19.56072564982034</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>18.96781446475413</v>
+        <v>12.31398809523825</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>11.72011661807571</v>
+        <v>5.038246847219398</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-2.349706286714159</v>
+        <v>-9.033005211349064</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-9.305717619603271</v>
+        <v>-15.96127590914733</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-9.848263787569401</v>
+        <v>-9.385863267670914</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-9.924109748978303</v>
+        <v>-16.60388293248324</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-2.506777893639111</v>
+        <v>-9.21739130434792</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-9.725467289719624</v>
+        <v>-16.52238744149443</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.07958</t>
+          <t>X ≈ 0.07944</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>3.502010029425271</v>
+        <v>8.957373271889402</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>3.167233231075357</v>
+        <v>8.711466436185617</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-12.55650010367002</v>
+        <v>-5.043227665706134</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-13.26945412311255</v>
+        <v>-5.635629864514272</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.6804696900543519</v>
+        <v>6.588811995386394</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.8674358761517311</v>
+        <v>6.745745601384478</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-14.1902270934529</v>
+        <v>-6.549336410848241</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-14.46843853820587</v>
+        <v>-6.854256854256946</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-28.71266564200556</v>
+        <v>-19.22632794457275</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-15.19986703232766</v>
+        <v>-7.522379439792005</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>13.64562118126263</v>
+        <v>17.74985557481224</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.918842507899555</v>
+        <v>4.973273620340947</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-2.042004574755872</v>
+        <v>3.85838150289009</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-16.54879773691655</v>
+        <v>-21.38985255854293</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>11.36448753693157</v>
+        <v>15.4279930595721</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>11.95887445887446</v>
+        <v>15.98929707839167</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>11.82495732189709</v>
+        <v>15.88541666666666</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-2.565597667638485</v>
+        <v>3.252532561504978</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-2.349706286714159</v>
+        <v>3.466994788650837</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-16.44857476246042</v>
+        <v>-8.818418766290179</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-31.27683521614073</v>
+        <v>-34.38586326767091</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-17.06696689183555</v>
+        <v>-9.461025789626198</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-2.506777893639409</v>
+        <v>3.282608695652357</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>11.70310413885181</v>
+        <v>15.62046970136272</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.0822</t>
+          <t>X ≈ 0.08206</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>3.502010029425172</v>
+        <v>13.12403993855606</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>3.167233231075357</v>
+        <v>12.87813310285219</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-12.55650010366981</v>
+        <v>-5.043227665705928</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-13.26945412311266</v>
+        <v>-5.635629864514272</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-13.60524459565993</v>
+        <v>-5.911188004613606</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.8674358761518306</v>
+        <v>10.91241226805113</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.09548719226147995</v>
+        <v>-6.549336410848241</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.1827242524916954</v>
+        <v>-6.85425685425686</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>14.1444772151373</v>
+        <v>9.940338722093905</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.9141527466135813</v>
+        <v>-7.522379439792203</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.6400931044515588</v>
+        <v>-7.250144425187756</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>27.65258606352901</v>
+        <v>25.80660695367429</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>26.5294239966729</v>
+        <v>24.69171483622362</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>26.30834512022631</v>
+        <v>24.44348077479041</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>11.36448753693147</v>
+        <v>23.76132639290535</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-2.326839826839731</v>
+        <v>7.655963745058457</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-2.460756963817403</v>
+        <v>-9.114583333333449</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-2.565597667638485</v>
+        <v>-9.247467438494816</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>11.93600799900003</v>
+        <v>7.633661455317494</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>12.12285380896806</v>
+        <v>7.848247900376478</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>25.86602192671641</v>
+        <v>23.9474700656623</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>11.50446167959303</v>
+        <v>7.205640877040459</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>26.06465067778936</v>
+        <v>24.11594202898552</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>25.98881842456608</v>
+        <v>23.95380303469606</v>
       </c>
     </row>
   </sheetData>
@@ -3180,83 +3180,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; 0.007494</t>
+          <t>X &gt; 0.007499</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3336</v>
+        <v>3360</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.006071612379287217</v>
+        <v>0.01930055536561071</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.01484660638379864</v>
+        <v>0.1144824030690401</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.09639541836416043</v>
+        <v>0.0292361024098966</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.2267161697668385</v>
+        <v>-0.04391388818291375</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1285573484808822</v>
+        <v>0.05211474767996549</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.2527617556738022</v>
+        <v>-0.1000211244888121</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.2325772276610749</v>
+        <v>-0.1087086347155832</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.1656768607426216</v>
+        <v>-0.04146064572605468</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.01223524046022817</v>
+        <v>0.2218202035753976</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.03254234933535116</v>
+        <v>0.2428843420691962</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.1746490360594706</v>
+        <v>0.4136563456394029</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.2417651043209688</v>
+        <v>0.5100470485734476</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.3908777505676468</v>
+        <v>0.6879572964232494</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.4565818207642707</v>
+        <v>0.7837379459081006</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.4740327002882907</v>
+        <v>0.8316736769658917</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>0.548245614035082</v>
+        <v>0.9061616864676836</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.6117613046327648</v>
+        <v>0.9091766904266834</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0.6147049740645159</v>
+        <v>0.8832515157534289</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.6690648254421703</v>
+        <v>1.026430152692441</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.6942823803967286</v>
+        <v>0.9913315309749819</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>0.7087892223138965</v>
+        <v>1.066114133459031</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>0.6810430371210572</v>
+        <v>0.9791883686129452</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>0.7039759913729995</v>
+        <v>1.062287362715551</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>0.7061873865393693</v>
+        <v>1.007374463267475</v>
       </c>
     </row>
     <row r="7">
@@ -3266,2375 +3266,2375 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3246</v>
+        <v>3272</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.1064762270391171</v>
+        <v>0.1447784312217237</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.1553430404825988</v>
+        <v>0.2794688648437003</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.05008523018814515</v>
+        <v>0.1951567861615473</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.002898266232236324</v>
+        <v>0.1966909131285064</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.1991745686367281</v>
+        <v>0.3938864408436942</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.219676772510276</v>
+        <v>0.385563230563811</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.5376744870383234</v>
+        <v>0.6717034188872475</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.7369569247002161</v>
+        <v>0.8708039729937482</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.857580119592555</v>
+        <v>1.016294507511219</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.8693704786275447</v>
+        <v>1.029050870615706</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.9774056900954093</v>
+        <v>1.166902758982715</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>1.054322448690826</v>
+        <v>1.27351722570026</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>1.238841076369383</v>
+        <v>1.486313272612996</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>1.220595032476226</v>
+        <v>1.500153535302282</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>1.256960655211039</v>
+        <v>1.567889432629002</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>1.317027062263691</v>
+        <v>1.660028785708747</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>1.32475970211744</v>
+        <v>1.605148292162241</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>1.238654660599082</v>
+        <v>1.490787595062109</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>1.257974866337655</v>
+        <v>1.60172167299627</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>1.309666995781342</v>
+        <v>1.590616642745225</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>1.432130179805277</v>
+        <v>1.743907724695504</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>1.313574980085633</v>
+        <v>1.59578545044711</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>1.298932872342576</v>
+        <v>1.644203562746583</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>1.211069986928557</v>
+        <v>1.500665300384718</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 0.01274</t>
+          <t>X &gt; 0.01273</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3062</v>
+        <v>3091</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.0914143743720004</v>
+        <v>-0.0423055977316622</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.04512835799772574</v>
+        <v>0.2108239691119707</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.2464283982530731</v>
+        <v>0.4194972700265964</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.3626956868437787</v>
+        <v>0.5842351306641334</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.4022668802059783</v>
+        <v>0.6161431850970018</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.5427605514764124</v>
+        <v>0.6947645785475558</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1.023432257913498</v>
+        <v>1.108321246809417</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.251416655333429</v>
+        <v>1.336924349476639</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.279441698168071</v>
+        <v>1.387001095993888</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>1.240779447330425</v>
+        <v>1.318200270352833</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1.273960321796991</v>
+        <v>1.383876193368948</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>1.242138995957689</v>
+        <v>1.38400517045374</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>1.472476388472444</v>
+        <v>1.642069446152583</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>1.368798989273934</v>
+        <v>1.574513774897888</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>1.479387290385439</v>
+        <v>1.71831564021717</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>1.605221597078284</v>
+        <v>1.87990695254463</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>1.784460184625658</v>
+        <v>2.053912470411014</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>1.764817679726015</v>
+        <v>2.037647188563511</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>1.707306149822244</v>
+        <v>2.01350641655781</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>1.848881206228434</v>
+        <v>2.118576387183161</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>2.044069001990245</v>
+        <v>2.378842614682029</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>1.92314873666129</v>
+        <v>2.194325002485023</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>1.95663332785233</v>
+        <v>2.263850610270545</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>1.966237478405787</v>
+        <v>2.218657989942464</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; 0.01536</t>
+          <t>X &gt; 0.01535</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2794</v>
+        <v>2826</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.002224465224657024</v>
+        <v>0.09022690474302664</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.06937391178178132</v>
+        <v>0.1440507058484499</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.003763788743178509</v>
+        <v>0.2079138868053718</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.1278450950820798</v>
+        <v>0.337665989315667</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.2741927107236961</v>
+        <v>0.43327596726688</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.5880211230527692</v>
+        <v>0.680344757502624</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.5833664421470388</v>
+        <v>0.6085953513747597</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.8594719854340767</v>
+        <v>0.8867705912040833</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.9216729634971585</v>
+        <v>0.9646259449027852</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.8817365492758142</v>
+        <v>0.8931135179543972</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.8917914698270408</v>
+        <v>0.9041352507544786</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.6339525231563528</v>
+        <v>0.6832806675572982</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.8864395301590235</v>
+        <v>0.9635982811770916</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.8651007754127775</v>
+        <v>0.9832080902581879</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>1.049009222880194</v>
+        <v>1.204007168919453</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>1.129874764778407</v>
+        <v>1.328040903374024</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>1.338906421708273</v>
+        <v>1.563143458053887</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>1.398688046647237</v>
+        <v>1.628238776194323</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>1.564957113479792</v>
+        <v>1.828881047923183</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>1.916584024428182</v>
+        <v>2.17098052699604</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>1.89646270510142</v>
+        <v>2.190665541095434</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>1.735403841865661</v>
+        <v>1.960473503160223</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>1.853048326652129</v>
+        <v>2.084341981821261</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>1.835019467617528</v>
+        <v>2.050052150053446</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 0.01798</t>
+          <t>X &gt; 0.01796</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2498</v>
+        <v>2531</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.1473321804990135</v>
+        <v>0.1770287143326286</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.04705248321035782</v>
+        <v>0.1871812814655982</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.2433637878970316</v>
+        <v>0.3642958452657439</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.1482243064799889</v>
+        <v>0.2640173326633075</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.3115497740545834</v>
+        <v>0.3633217993079612</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.6403180019750323</v>
+        <v>0.5815635692150067</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.447659870477807</v>
+        <v>0.3187954572836276</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.6696453349614302</v>
+        <v>0.5466069070309274</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.4556590694946436</v>
+        <v>0.3435856453722579</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.3028627219943516</v>
+        <v>0.1593494403650766</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.3213906527311323</v>
+        <v>0.1791008578311164</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.06579038908394352</v>
+        <v>-0.0355741971973913</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.1216348945832806</v>
+        <v>0.05232328101762818</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.04382017149083595</v>
+        <v>0.02396090072507207</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>0.167268322161398</v>
+        <v>0.2311426658712179</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.6260731819391054</v>
+        <v>0.6978437503097581</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.7955874901319433</v>
+        <v>0.8932968873128431</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.7148678732104443</v>
+        <v>0.8234825023801164</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.8350434421825952</v>
+        <v>0.9827676593133035</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>1.205873107814789</v>
+        <v>1.339372160731514</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>1.047377955733374</v>
+        <v>1.22976419878529</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>1.035890251021598</v>
+        <v>1.139053168131397</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>1.094662682591284</v>
+        <v>1.209148980012365</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>1.043147602193905</v>
+        <v>1.149904707289231</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; 0.0206</t>
+          <t>X &gt; 0.02058</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2222</v>
+        <v>2249</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.08849634346843516</v>
+        <v>0.1545563704809538</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.1351893143129388</v>
+        <v>0.328595454239256</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.2412519877790871</v>
+        <v>0.3312216735009983</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.0890298961768039</v>
+        <v>-0.01641435107222833</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.09242239059765467</v>
+        <v>0.08528465852572253</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.4837550985586887</v>
+        <v>0.3992524386142904</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.364184012682351</v>
+        <v>0.202649467351236</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.3546693883502243</v>
+        <v>0.2318358609749254</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.1722425532474645</v>
+        <v>0.1199618080774272</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.06327948194710586</v>
+        <v>-0.1207002528720693</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.05791666020615338</v>
+        <v>-0.0883407116599102</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.2023176534436644</v>
+        <v>-0.2069563663905853</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.1611268318089643</v>
+        <v>-0.1017954882602652</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.3109585152063588</v>
+        <v>-0.1913133819161033</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.2254465093002054</v>
+        <v>-0.05030632041027872</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.08187253702948283</v>
+        <v>0.3158367328001788</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.2438511243708774</v>
+        <v>0.5042109929077938</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.3454051535977385</v>
+        <v>0.6638407654961966</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.8127800818790831</v>
+        <v>1.171076421303901</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>1.071640870962767</v>
+        <v>1.412384606989896</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>0.8708373360262058</v>
+        <v>1.271330338012923</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>0.8672571574964181</v>
+        <v>1.178689892292951</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>1.034125647264332</v>
+        <v>1.315942028985511</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>1.165621819191266</v>
+        <v>1.403039732487663</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; 0.02322</t>
+          <t>X &gt; 0.0232</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1969</v>
+        <v>1990</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.1160868250450946</v>
+        <v>0.3073484333399747</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.09065922964252593</v>
+        <v>0.1379077880741946</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.08804982603236056</v>
+        <v>-0.04571399091738471</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.1360292823707425</v>
+        <v>0.0857631703116013</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.3845049170809958</v>
+        <v>0.2361489789603084</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.6002106847607251</v>
+        <v>0.3712436093525966</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.7675010660962016</v>
+        <v>0.4511618452553989</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.8939431367705382</v>
+        <v>0.6233104438488226</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.188338765827382</v>
+        <v>0.9295324045544362</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1.477638567787857</v>
+        <v>1.210155490347631</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.650534831092919</v>
+        <v>1.361937451996461</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.574112185358629</v>
+        <v>1.314432461499784</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>1.71549235421319</v>
+        <v>1.528296545368939</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.443831788338173</v>
+        <v>1.360147441457066</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>1.3420870744703</v>
+        <v>1.358458292188317</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>1.632983859842732</v>
+        <v>1.750057839152433</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>1.732418281989524</v>
+        <v>1.876903897512925</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>1.962431265453745</v>
+        <v>2.175378252887832</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>2.564174159081176</v>
+        <v>2.821631380129531</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>2.782472953128611</v>
+        <v>3.017087753268498</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>2.47425142541244</v>
+        <v>2.831898899915643</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>2.632967876592375</v>
+        <v>2.888371800735243</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>2.989958872133094</v>
+        <v>3.26377393924836</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>3.149088322266159</v>
+        <v>3.334037540558697</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; 0.02584</t>
+          <t>X &gt; 0.02581</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1706</v>
+        <v>1722</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.2608937334785821</v>
+        <v>-0.1824888763012922</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.73947230828324</v>
+        <v>-0.6276140235845773</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.2794539293075218</v>
+        <v>-0.4141304834173809</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.5515823859764737</v>
+        <v>-0.7765154309317452</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.09556502289625257</v>
+        <v>-0.477030442796476</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.241235659068991</v>
+        <v>-0.2050882111514625</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.1215955496606327</v>
+        <v>-0.6229842819644702</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.1660255800361554</v>
+        <v>-0.6078550120000941</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.1092430162561158</v>
+        <v>-0.3323187279828943</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.1545622905410653</v>
+        <v>-0.2889500449794014</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.4286219327029883</v>
+        <v>0.01629156097141049</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.7343260651988857</v>
+        <v>0.292084930208226</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.189188545391275</v>
+        <v>0.7694669532366021</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.7927736081615251</v>
+        <v>0.4977846453854298</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.9528652609024135</v>
+        <v>0.7748138688205657</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>1.313470768467845</v>
+        <v>1.255346818125624</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>1.354889692273538</v>
+        <v>1.359953703703702</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>1.600721110018689</v>
+        <v>1.725317738111897</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>2.144863471013494</v>
+        <v>2.322730593981085</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>2.192234399121126</v>
+        <v>2.456943552550399</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>2.154078132805402</v>
+        <v>2.447083368059943</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>2.290301498824753</v>
+        <v>2.581922556282102</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>2.506193903163869</v>
+        <v>2.803514618997127</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>2.642645254242858</v>
+        <v>2.873663661873749</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; 0.02847</t>
+          <t>X &gt; 0.02843</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1511</v>
+        <v>1525</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.4437475748690147</v>
+        <v>-0.2958734813573543</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.46902760571318</v>
+        <v>-1.38593616121706</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.288230419558644</v>
+        <v>-1.276993899472288</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.040731722659743</v>
+        <v>-1.284980513864923</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.1504244653606222</v>
+        <v>-0.4566425500681532</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.2569027481868815</v>
+        <v>-0.6893193336804586</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.3674757707015814</v>
+        <v>-0.8999857614975895</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.3811369509043914</v>
+        <v>-0.97381500890274</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.4719249012648135</v>
+        <v>-1.134650441321774</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.6496024820632158</v>
+        <v>-1.243914898477847</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.1535576891992463</v>
+        <v>-0.4793110918544201</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.5361839471269008</v>
+        <v>-0.002296412232347222</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.5373605046094099</v>
+        <v>0.02852491879630037</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.3162816281628196</v>
+        <v>-0.05097454158272541</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.4517891242330521</v>
+        <v>0.2191157749767072</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>1.112313612313613</v>
+        <v>0.950107006543206</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>1.110671607611266</v>
+        <v>1.081495098039213</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>1.534931432890623</v>
+        <v>1.642002803493291</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>1.949235512227645</v>
+        <v>2.223539291268644</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>2.136081322195672</v>
+        <v>2.543729236329334</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>2.163648853066036</v>
+        <v>2.60627303639199</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>2.153984228519946</v>
+        <v>2.571761095619706</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>2.362277604138988</v>
+        <v>2.880969351389886</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>2.484989361504731</v>
+        <v>2.981125439067632</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; 0.03109</t>
+          <t>X &gt; 0.03104</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1344</v>
+        <v>1352</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.7868812127648042</v>
+        <v>-0.6143690414341734</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.417760410298101</v>
+        <v>-2.397611162643166</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.961527147895175</v>
+        <v>-2.18817642119653</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.594650472083153</v>
+        <v>-1.975307756168732</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.477257341278623</v>
+        <v>-0.9331499372636856</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.9182784095625465</v>
+        <v>-1.508280752934702</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.02058423631005</v>
+        <v>-1.644504785665227</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.4803433001107393</v>
+        <v>-1.103341103341108</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.3644513562912692</v>
+        <v>-1.081166654250175</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.3933194132801461</v>
+        <v>-1.102716930621149</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.5503830860246381</v>
+        <v>-0.1282648363478174</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.7924670159099705</v>
+        <v>0.1514514307744506</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.157400187149094</v>
+        <v>0.5495579734784144</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.564297501178693</v>
+        <v>0.05054479245044519</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>1.24543991788385</v>
+        <v>0.8109091125911547</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>1.765422077922075</v>
+        <v>1.490402457905304</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>1.408290655230324</v>
+        <v>1.283646755162238</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>1.749878522837712</v>
+        <v>1.859543631615772</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>2.412198475190607</v>
+        <v>2.636123296774912</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>2.450234761349115</v>
+        <v>2.822379459873908</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>2.354117164811655</v>
+        <v>2.744314247121984</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>2.650295012926364</v>
+        <v>3.112938707415225</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>3.29679353493222</v>
+        <v>3.726395677900697</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>3.295366043613711</v>
+        <v>3.786150174735489</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 0.03371</t>
+          <t>X &gt; 0.03366</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1188</v>
+        <v>1195</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.3690350328950487</v>
+        <v>-0.2313684499649113</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-2.170418202293959</v>
+        <v>-2.050122967787985</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.304399263333778</v>
+        <v>-2.477002500143129</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.711121791020858</v>
+        <v>-2.158808672461291</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.1032691128537735</v>
+        <v>-0.3648303887195681</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.8882158795000237</v>
+        <v>-1.44961863702612</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.575989479215288</v>
+        <v>-2.244700649258839</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.8440999138673604</v>
+        <v>-1.556243609223742</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.2133871427270577</v>
+        <v>-0.968250065533816</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.107973275512542</v>
+        <v>-0.8059615293443301</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.5503830860246381</v>
+        <v>-0.4036713961421157</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.8608592718022265</v>
+        <v>-0.05164332318064879</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.4952729625218666</v>
+        <v>-0.2875037838928733</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.1058439177251103</v>
+        <v>-0.5703850044663881</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.9628521352960675</v>
+        <v>0.3780346915453734</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>1.557239057239059</v>
+        <v>1.072630411725008</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.9182714152110805</v>
+        <v>0.6018470252988521</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>1.48683138479057</v>
+        <v>1.520479139134444</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>2.376123439115574</v>
+        <v>2.537587938191358</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>2.64714433325868</v>
+        <v>2.970878892572692</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>2.441298501992996</v>
+        <v>2.873550958270506</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>2.7863279614593</v>
+        <v>3.384162494892628</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>3.650028263166952</v>
+        <v>4.213571038748412</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>3.574196009943677</v>
+        <v>4.218796061195349</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 0.03633</t>
+          <t>X &gt; 0.03628</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1023</v>
+        <v>1031</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.1320751836074052</v>
+        <v>0.008236995497846067</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.780501960562269</v>
+        <v>-1.773178477442109</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.312080460812773</v>
+        <v>-1.492363942097604</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.287887302836161</v>
+        <v>-1.796858271424064</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.2336047270603672</v>
+        <v>-0.3449691946328031</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.7524496147015043</v>
+        <v>-1.43563635638904</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.7423846133523497</v>
+        <v>-1.558933339830958</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.05467275909887093</v>
+        <v>-0.8081915951397747</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.073677047562938</v>
+        <v>0.0874916331623723</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.571533610040625</v>
+        <v>0.4987540856642028</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.845593252202548</v>
+        <v>0.9229324978891711</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>2.446609244648975</v>
+        <v>1.472311156433335</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.300964284342221</v>
+        <v>1.570327552986519</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.688878565275886</v>
+        <v>1.090861038371237</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>2.203755795554564</v>
+        <v>1.624904256483205</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>2.993646138807428</v>
+        <v>2.535190798198435</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>2.273218737900336</v>
+        <v>1.910561734364926</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>2.070626323424221</v>
+        <v>2.030364120072335</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>3.068531389588038</v>
+        <v>3.273196339038435</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>3.255377199556065</v>
+        <v>3.548215569306322</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>2.908334452899908</v>
+        <v>3.368743909826662</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>3.712253887385231</v>
+        <v>4.360506703099311</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>3.986728599867284</v>
+        <v>4.701134398852957</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>4.301903189263761</v>
+        <v>5.120954667415084</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 0.03895</t>
+          <t>X &gt; 0.03889</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>867</v>
+        <v>875</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.2141586403079572</v>
+        <v>0.2948450551851138</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.4041953403532119</v>
+        <v>-0.2896622319860214</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.2810016690019239</v>
+        <v>-0.6414217966315547</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.455316703438896</v>
+        <v>-2.136758532685825</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.2916838772549255</v>
+        <v>-1.057914866916086</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.9120994673974465</v>
+        <v>-1.916782615319811</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.992006628796446</v>
+        <v>-2.034663724617992</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.2321557898125022</v>
+        <v>-1.210915996469048</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.2706924070964334</v>
+        <v>-0.8572534524734294</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.7665195222940895</v>
+        <v>-0.4602325471367266</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.040579164456013</v>
+        <v>-0.1234475926085707</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.68455179099648</v>
+        <v>0.5706688638290487</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>2.176153276620177</v>
+        <v>1.22232708112147</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.839734146425023</v>
+        <v>1.042043014669325</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>2.104312878832943</v>
+        <v>1.450720332299284</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>2.583359547027371</v>
+        <v>2.081447249040139</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>1.642060633809983</v>
+        <v>1.249881359149576</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>1.767900437485913</v>
+        <v>1.641928228551819</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>2.329812579655922</v>
+        <v>2.268364651664534</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>2.170637628378266</v>
+        <v>2.324438376566967</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>1.628091460412236</v>
+        <v>1.98556530375766</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>2.474967528991613</v>
+        <v>2.9389742103738</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>2.980122748970786</v>
+        <v>3.525465838509326</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>3.365651510741742</v>
+        <v>4.16332684421986</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 0.04157</t>
+          <t>X &gt; 0.04151</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>748</v>
+        <v>759</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.6982717116681627</v>
+        <v>0.6836411522535144</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.6333779224769671</v>
+        <v>-0.4725387653749351</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.0660493779250757</v>
+        <v>-0.1667647268243826</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.447452595228782</v>
+        <v>-2.05955704266772</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.5800345116263159</v>
+        <v>-1.294803089138959</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.195207362962094</v>
+        <v>-2.30822058847248</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.165017009419287</v>
+        <v>-2.193029518780619</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.1063300584504461</v>
+        <v>-1.197559845154132</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.2025368026086483</v>
+        <v>-0.939591923766514</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.033899201438473</v>
+        <v>-0.2307127731254255</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.307958843600396</v>
+        <v>-0.01416007055933477</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.965038317157742</v>
+        <v>0.6978167012808996</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.446154325167939</v>
+        <v>1.358381502890175</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.35876528829354</v>
+        <v>1.450461577582715</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>2.502761028146132</v>
+        <v>1.764821368877378</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>2.963458110516939</v>
+        <v>2.406619913037346</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>2.428471454822891</v>
+        <v>1.989227441962328</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>2.18994091142951</v>
+        <v>2.068322035189276</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>2.94059165064261</v>
+        <v>2.890578451364938</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>2.726367941894061</v>
+        <v>2.709907979427875</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>2.183821773928031</v>
+        <v>2.274215783712485</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>2.64273517080769</v>
+        <v>2.989567095749287</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>3.585659081150709</v>
+        <v>4.023715415019772</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>3.643516667499625</v>
+        <v>4.388585643391693</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.04419</t>
+          <t>X &gt; 0.04412</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>632</v>
+        <v>644</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.07163313933264703</v>
+        <v>0.4329084400851215</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.4547558350536605</v>
+        <v>0.492812001934773</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.2825595708327953</v>
+        <v>0.1555490927037368</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.063305841015001</v>
+        <v>-1.660094696318552</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.1332735287521558</v>
+        <v>-0.8653164449805786</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.737446583161109</v>
+        <v>-1.167098435312774</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.034711722747659</v>
+        <v>-1.503464851215213</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.3635560788931329</v>
+        <v>-1.196764499516803</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.4802967450796984</v>
+        <v>-1.374645987386202</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.6455217560990008</v>
+        <v>-0.2482599910937751</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.236037094463455</v>
+        <v>0.571941464382796</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>2.064882627724316</v>
+        <v>1.459448735548321</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>2.365771193779587</v>
+        <v>1.666073810582482</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.986464469231741</v>
+        <v>1.510763774276789</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>2.594143956461309</v>
+        <v>2.156388121300402</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>2.55561948599923</v>
+        <v>2.349420725995998</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>1.788790956616701</v>
+        <v>1.721329979360164</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>1.842178100896774</v>
+        <v>2.147881398714368</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>2.374525178023639</v>
+        <v>2.612957521570095</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>1.77023174748534</v>
+        <v>2.051146451101133</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>1.069457731418041</v>
+        <v>1.328422446614795</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>1.942978858616534</v>
+        <v>2.340216446398649</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>2.692137115402382</v>
+        <v>3.049689440993795</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>3.249216254584177</v>
+        <v>3.819227465337867</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.04681</t>
+          <t>X &gt; 0.04674</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.023331991045652</v>
+        <v>1.24941667152774</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.248256685233144</v>
+        <v>1.365173488626759</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.489342113814097</v>
+        <v>1.376302171545312</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.2166866018340414</v>
+        <v>-0.4819228120730443</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.00029911436139</v>
+        <v>0.3275100062363023</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.06786231538414711</v>
+        <v>-0.7813791725757397</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.3309520401479986</v>
+        <v>-0.853133879202673</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.5102395001735474</v>
+        <v>-0.4347270170054998</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.1785923537300462</v>
+        <v>-0.6684617601242806</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.271348319484602</v>
+        <v>0.3438050086708415</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.10510945418384</v>
+        <v>1.445507748725291</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>3.50546452834778</v>
+        <v>2.908845308181242</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>3.688272610745393</v>
+        <v>3.176563321071988</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>3.467193734298803</v>
+        <v>2.858781321238489</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>4.115020585971983</v>
+        <v>3.566679190958865</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>3.590004522840346</v>
+        <v>3.329333641462974</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>2.523251564967353</v>
+        <v>2.423878205128204</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>2.231843696967061</v>
+        <v>2.587394946826166</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>2.447735077891387</v>
+        <v>2.801857173971939</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>1.888312231142997</v>
+        <v>2.099012426370372</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>1.159198898997857</v>
+        <v>1.348081686457526</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>2.016188758484283</v>
+        <v>2.373836595694904</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>2.290663470966336</v>
+        <v>2.617471080973282</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>3.33423420281769</v>
+        <v>3.923221994940697</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.04944</t>
+          <t>X &gt; 0.04936</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>465</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.7677550371056654</v>
+        <v>0.6946614074826201</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.6480320021967145</v>
+        <v>0.6606189785584107</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.14549682413346</v>
+        <v>1.100840130904118</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.4276722490727138</v>
+        <v>-0.55088410180241</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.172021149347749</v>
+        <v>0.8684730123355493</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.4987722816816884</v>
+        <v>0.1779489912149828</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.5870386515547779</v>
+        <v>0.2303246061009148</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.7389347336834291</v>
+        <v>0.3491329762516173</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.0797931381653143</v>
+        <v>-0.370395741182918</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.082775056765939</v>
+        <v>0.7403324246146923</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.786942225809582</v>
+        <v>1.560895914515001</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.798515403006753</v>
+        <v>2.68603957778776</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>3.180729680236652</v>
+        <v>3.19207020225052</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.959650803790062</v>
+        <v>3.075959407269032</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>3.80688385029552</v>
+        <v>4.025423466424265</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>3.541055718475079</v>
+        <v>3.86483355907837</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>2.761977291175022</v>
+        <v>3.251008064516128</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>2.442082823912976</v>
+        <v>2.903070195913664</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>2.012812914514726</v>
+        <v>2.47237113273686</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>1.769551197601025</v>
+        <v>2.256850050914117</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>1.011951266194146</v>
+        <v>1.474351786092534</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>2.656535412311925</v>
+        <v>3.119619371664129</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>2.931010124793978</v>
+        <v>3.363253856942507</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>3.715392925334136</v>
+        <v>4.061329916416476</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.05206</t>
+          <t>X &gt; 0.05197</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.531566679671478</v>
+        <v>1.311742203928233</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.4578736251640265</v>
+        <v>0.5803984750204805</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.7439925071675191</v>
+        <v>1.024733499342496</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.03103848772477846</v>
+        <v>-0.0531055926696169</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.911996783650416</v>
+        <v>1.855802286648526</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.6211304574325283</v>
+        <v>0.556425213034963</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.8897344826154665</v>
+        <v>-0.9668121390035864</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.1827242524916954</v>
+        <v>-0.543577242606375</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.6338479080154116</v>
+        <v>-0.9010852261261491</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.056290603140219</v>
+        <v>0.9727661912758663</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>2.315571920178989</v>
+        <v>2.215874992287965</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3.02204419160784</v>
+        <v>3.057215226180368</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3.130409218347772</v>
+        <v>3.309601015085299</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.648246598058826</v>
+        <v>3.701834483021855</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>4.467935812793534</v>
+        <v>4.643679334081817</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>4.077101059859679</v>
+        <v>4.379960469055064</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>2.957962248005359</v>
+        <v>3.293279074529075</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>3.099426962903387</v>
+        <v>3.406095215067722</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>2.330096668950866</v>
+        <v>2.637756459412515</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>2.024331641480472</v>
+        <v>2.360942413071001</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>1.481785473514442</v>
+        <v>1.793497911690267</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>3.130077443139825</v>
+        <v>3.438237109636702</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>3.158246736902662</v>
+        <v>3.436171349214838</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>4.06763615855624</v>
+        <v>4.256833337726349</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.05468</t>
+          <t>X &gt; 0.05459</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>357</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.541225715699689</v>
+        <v>1.639446101021058</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.1941113067397637</v>
+        <v>-0.00702095877245057</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.048541913136809</v>
+        <v>0.4189572082435333</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.4560360729657731</v>
+        <v>0.9470031887070149</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2.361141958961923</v>
+        <v>2.912341407151104</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.5873238313338049</v>
+        <v>1.10849069942369</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.865297121464103</v>
+        <v>-1.367263581716585</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.4628362973096216</v>
+        <v>0.008488243782352356</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.4213491153949178</v>
+        <v>0.1364171534664607</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.7665195222940895</v>
+        <v>1.30114997197262</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>2.441139388545643</v>
+        <v>2.973945210666585</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>4.123174298823137</v>
+        <v>4.658147569920779</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>5.240908590510436</v>
+        <v>5.784151811013423</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4.73971766924592</v>
+        <v>5.255805704762388</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>5.202022550937066</v>
+        <v>5.694099502149037</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>5.516297428062131</v>
+        <v>5.975291476150772</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>4.822156201448806</v>
+        <v>5.311186974789912</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>4.157091407991764</v>
+        <v>4.618078779992452</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>4.092870744098164</v>
+        <v>4.552428962320299</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>3.999604509248265</v>
+        <v>4.486903362561357</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>4.017282430918087</v>
+        <v>4.479682950816475</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>5.341996693598624</v>
+        <v>5.805080652950828</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>5.056247316444825</v>
+        <v>5.488491048593353</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>6.38097528731118</v>
+        <v>6.72691227839352</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.0573</t>
+          <t>X &gt; 0.0572</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.424726657059836</v>
+        <v>2.950879765395896</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.434212153791989</v>
+        <v>1.40627163099073</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.635537367056081</v>
+        <v>1.774954152475772</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.906189904990391</v>
+        <v>2.156577927693526</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.537612547197213</v>
+        <v>4.153747060321457</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.429496766081485</v>
+        <v>2.037953393592275</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.6539273276449435</v>
+        <v>-0.05582991734174669</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.05146778497903171</v>
+        <v>0.6132756132756043</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.0929549668937355</v>
+        <v>0.4165291982843868</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.6315147006933159</v>
+        <v>0.9191790017663521</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1.233443195314251</v>
+        <v>1.516089341046012</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>2.92190690662035</v>
+        <v>3.187559334626656</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4.093826806977354</v>
+        <v>4.345394489903164</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>4.528485635448803</v>
+        <v>4.746511077820699</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>4.526080042786269</v>
+        <v>4.713707345286302</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>4.464729259811236</v>
+        <v>4.625660714755305</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>3.675074417915724</v>
+        <v>3.872429653679653</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>3.570233714094542</v>
+        <v>3.739545548518052</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>3.130387390100829</v>
+        <v>3.6293324509885</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>2.661495495150824</v>
+        <v>3.194568246696832</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>3.430424737020864</v>
+        <v>3.925825044017394</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>4.338185332988807</v>
+        <v>4.824688496088093</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>5.596266602847919</v>
+        <v>6.042348955392434</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>7.159778611919727</v>
+        <v>7.503586584479599</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.05992</t>
+          <t>X &gt; 0.05982</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.036808564223712</v>
+        <v>2.053041141925505</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.702031765873897</v>
+        <v>2.168145136546542</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.095514548344731</v>
+        <v>2.357494355954607</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.847761994103465</v>
+        <v>3.209135478446022</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>4.343473353058016</v>
+        <v>4.738631489971226</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.332637341353205</v>
+        <v>2.368489283694949</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.4617875585617455</v>
+        <v>0.4903747804874996</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.648777579010144</v>
+        <v>1.629497658378519</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.323964394624483</v>
+        <v>1.396415737737719</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>2.382550550089817</v>
+        <v>2.405418394142927</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>3.389210924852478</v>
+        <v>3.399675069397077</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>4.941963352906306</v>
+        <v>4.928147266550333</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>6.749204216453116</v>
+        <v>6.70134179169883</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>6.528125340006525</v>
+        <v>6.453107730265721</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>6.602582775026697</v>
+        <v>6.492975009030495</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>5.731768231768228</v>
+        <v>5.610235706550512</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>4.132649629589288</v>
+        <v>4.062311973525865</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>4.394109292068478</v>
+        <v>4.290438698689179</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>3.877399940392067</v>
+        <v>3.782879265185137</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>3.697945384059729</v>
+        <v>3.636454879919206</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>3.887999948694429</v>
+        <v>3.791032039188288</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>5.277355452486795</v>
+        <v>5.159912838532641</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>6.650731263869943</v>
+        <v>6.486579814785749</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>8.406400842148507</v>
+        <v>8.129494972120845</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.06254</t>
+          <t>X &gt; 0.06244</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>235</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.529365652525485</v>
+        <v>2.627586037846854</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.06692927970757978</v>
+        <v>0.2540196276748929</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.3310378902510607</v>
+        <v>0.701453185357785</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.745743445276396</v>
+        <v>2.236710561017638</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3.112080632303595</v>
+        <v>3.663280080492775</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.3203234141456619</v>
+        <v>0.8414902822355472</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.3994385600425474</v>
+        <v>0.8974720997900647</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.248886689757548</v>
+        <v>2.720211230849522</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.864841956778633</v>
+        <v>2.422608225640012</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.942990110529379</v>
+        <v>2.47762056020791</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.791517837797684</v>
+        <v>2.324323659918626</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>3.640428008817771</v>
+        <v>4.175401279915413</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>4.644925516429744</v>
+        <v>5.188168736932731</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>6.125974299557612</v>
+        <v>6.64206233507408</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>4.616767172189832</v>
+        <v>5.108844123401802</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>3.509026434558351</v>
+        <v>3.968020482646992</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>1.672981638006405</v>
+        <v>2.162012411347511</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>1.568140934185223</v>
+        <v>2.02912830618591</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>1.784032315109549</v>
+        <v>2.243590533331684</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>1.119814295290347</v>
+        <v>1.607113148603439</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>1.853863872005164</v>
+        <v>2.316264391903552</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>3.480145570170535</v>
+        <v>3.943229529522739</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>5.456747942227054</v>
+        <v>5.888991674375582</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>7.934107178365487</v>
+        <v>8.280044169447827</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.06516</t>
+          <t>X &gt; 0.06505</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.481601866159863</v>
+        <v>2.517979332495457</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.4041953403532119</v>
+        <v>-0.2531800284609318</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.3116021444862511</v>
+        <v>0.5123278898495087</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2.036668325866934</v>
+        <v>2.950228721344317</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>3.231490098217627</v>
+        <v>4.18982209639649</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.88784403941704</v>
+        <v>2.831604187243066</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>3.156711682057306</v>
+        <v>4.056724195212368</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>5.429520645467491</v>
+        <v>6.277056277056268</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>5.471007827382195</v>
+        <v>6.404985186740376</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>4.698092151345705</v>
+        <v>5.608933691521038</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>4.972151793507628</v>
+        <v>5.376118201074874</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>6.734218716590249</v>
+        <v>7.624788771856103</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>9.1824852211627</v>
+        <v>10.04525018975885</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>9.471610426348761</v>
+        <v>10.30206663337626</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>7.793058965502901</v>
+        <v>8.609811241390183</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>5.836425479282624</v>
+        <v>6.140812229906828</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>4.171896097407192</v>
+        <v>5.02683080808081</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>3.046647230320701</v>
+        <v>3.883845692818191</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>3.772742692877685</v>
+        <v>4.60335842501447</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>2.428976257947745</v>
+        <v>3.302793354921945</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>2.906838253247024</v>
+        <v>3.745449863642214</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>5.382012700001191</v>
+        <v>6.195539866939463</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>7.187099657381211</v>
+        <v>7.954325867369356</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>9.662287812321189</v>
+        <v>10.31743939833242</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.06779</t>
+          <t>X &gt; 0.06767</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>164</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.846957764616818</v>
+        <v>1.945178149938187</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-2.756111716659831</v>
+        <v>-2.569021368692518</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-1.755106375446914</v>
+        <v>-1.38469108034019</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>3.019744483159116</v>
+        <v>3.510711598900357</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>4.513222303294775</v>
+        <v>5.064421751483955</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>4.700188489392154</v>
+        <v>5.221355357482039</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>5.757508098184729</v>
+        <v>6.255541637932247</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>9.137833238797512</v>
+        <v>9.609157779889486</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>8.569564323151241</v>
+        <v>9.127330592012619</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>7.79664864711475</v>
+        <v>8.331279096793281</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>7.460952191715698</v>
+        <v>7.99375801383664</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>9.011471080950628</v>
+        <v>9.546444352048269</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>11.54684559946036</v>
+        <v>12.09008881996335</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>10.7160106254528</v>
+        <v>11.23209866096926</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>10.05786732787224</v>
+        <v>10.54994427908421</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>8.822985957132303</v>
+        <v>9.281980005220944</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>5.030532234788978</v>
+        <v>5.519563008130085</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>4.315935433406821</v>
+        <v>4.776922805407509</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>3.922070716770165</v>
+        <v>4.3816289349923</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>2.889404331616241</v>
+        <v>3.376703184929333</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>2.346858163650211</v>
+        <v>2.809258683548599</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>4.710036592485018</v>
+        <v>5.173120551837222</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>7.423535695210973</v>
+        <v>7.855779427359501</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>9.786727832231584</v>
+        <v>10.13266482331392</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.07041</t>
+          <t>X &gt; 0.07028</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1.833605441312557</v>
+        <v>2.572481185558459</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-2.880733400832874</v>
+        <v>-1.989972412735334</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.6691174133675162</v>
+        <v>0.3524557875313619</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1.537636596386818</v>
+        <v>2.637751430449761</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>4.121554153036634</v>
+        <v>5.239891132077041</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>4.308520339134013</v>
+        <v>5.396824738075125</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>4.266498662542929</v>
+        <v>5.321167186274067</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>8.367849261585476</v>
+        <v>9.332793505455371</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>8.40933644350018</v>
+        <v>9.460722415139479</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>9.096274782062224</v>
+        <v>10.10351984078345</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>7.910480409625613</v>
+        <v>8.936905934524475</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>9.821512028075418</v>
+        <v>10.81859736134814</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>10.88813098311712</v>
+        <v>11.86197862519233</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>12.12690612126907</v>
+        <v>13.05259348462253</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>10.73883581638923</v>
+        <v>11.65101464230583</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>9.143441716434424</v>
+        <v>10.05404527983052</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>6.089816550259869</v>
+        <v>7.072467026378895</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>4.525121831840138</v>
+        <v>5.500734000353987</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>4.741013212764464</v>
+        <v>5.71519622749976</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>3.468005008133957</v>
+        <v>4.49093375169543</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>3.655385847467194</v>
+        <v>3.923489250314695</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>6.499247915255175</v>
+        <v>6.726024570086032</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>8.963503649635044</v>
+        <v>9.127932436659371</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>10.3475254110103</v>
+        <v>10.40464236323322</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.07303</t>
+          <t>X &gt; 0.0729</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>113</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>3.881276780373341</v>
+        <v>3.97949716569471</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.8782787790384106</v>
+        <v>-0.6911884310710974</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.22352518078015</v>
+        <v>1.593940475886875</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2.280482665762186</v>
+        <v>2.771449781503428</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>6.369470954276856</v>
+        <v>6.920670402466037</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>5.671481388161844</v>
+        <v>6.192648256251729</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>4.899532704271493</v>
+        <v>5.397566244019011</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>9.93105577279276</v>
+        <v>10.40238031388473</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>7.317675698070289</v>
+        <v>7.875441966931668</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>10.08458303088335</v>
+        <v>10.61921348056188</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>9.473686920832897</v>
+        <v>10.00649274295384</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>12.73476052623445</v>
+        <v>13.26973379733209</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>12.49655421159073</v>
+        <v>13.03979743209371</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>15.81529834399369</v>
+        <v>16.33138637951016</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>13.38724354198836</v>
+        <v>13.87932049320033</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>13.09667471171896</v>
+        <v>13.5556687598076</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>9.422934565891921</v>
+        <v>9.911965339233028</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>8.433138109858348</v>
+        <v>8.894125481859035</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>8.649029490782674</v>
+        <v>9.108587709004809</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>7.065963796325931</v>
+        <v>7.553262649639024</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>7.408373380572293</v>
+        <v>7.870773900470681</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>10.87235042801274</v>
+        <v>11.33543438736495</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>12.03178089270719</v>
+        <v>12.46402462485572</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>11.95594863948391</v>
+        <v>12.30188563056625</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.07565</t>
+          <t>X &gt; 0.07552</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.060183814403082</v>
+        <v>3.600230414746541</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.3673764891013676</v>
+        <v>0.2930990892467591</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.2564601319707336</v>
+        <v>1.079221313885782</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2.636289617682635</v>
+        <v>2.527635441608176</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>8.486066155444632</v>
+        <v>8.374526281100685</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>7.642104506490462</v>
+        <v>7.511051723833461</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>6.870155822600111</v>
+        <v>6.715969711600742</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>10.71565571805323</v>
+        <v>10.49268192125334</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>10.75714289996793</v>
+        <v>10.62061083093744</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>12.04608289403453</v>
+        <v>11.86537566224872</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>13.35107037124801</v>
+        <v>13.15801884011837</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>15.1341766379031</v>
+        <v>14.92225321217768</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>17.10379807620162</v>
+        <v>16.86858558452283</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>17.91364703480659</v>
+        <v>17.64075968635502</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>15.19364806712293</v>
+        <v>14.91778897793936</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>14.75710715401438</v>
+        <v>14.45868483349372</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>11.53040651188226</v>
+        <v>11.29357993197279</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>10.39463797300952</v>
+        <v>10.14028766354588</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>11.64145718898541</v>
+        <v>11.37515805395697</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>9.766447328850333</v>
+        <v>9.548928172485333</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>10.25482899593585</v>
+        <v>10.0018918343699</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>14.30269437473294</v>
+        <v>14.00836196547585</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>16.63902475731808</v>
+        <v>16.29281277728483</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>16.56319250409481</v>
+        <v>16.13067378299537</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.07827</t>
+          <t>X &gt; 0.07813</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>2.985658910664426</v>
+        <v>3.600230414746541</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-2.168394996119133</v>
+        <v>-1.407581182862081</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-1.196775490933256</v>
+        <v>-0.2813229038012821</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.49990904384088</v>
+        <v>1.507227278342867</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>6.188214956835772</v>
+        <v>7.184050090624488</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>6.375181142933151</v>
+        <v>7.340983696622573</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>4.398413181934359</v>
+        <v>5.355425493913664</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>8.939478845615028</v>
+        <v>9.812409812409797</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>10.18578530463816</v>
+        <v>11.13081491257011</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>9.412869628601669</v>
+        <v>10.33476341735077</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>10.89174854787202</v>
+        <v>11.7974746224313</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>13.02263769864089</v>
+        <v>13.90184504891238</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>15.51393346311007</v>
+        <v>16.35838150289018</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>16.49767386377192</v>
+        <v>16.11014744145707</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>13.42989201197449</v>
+        <v>14.23751686909582</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>12.81945965680906</v>
+        <v>13.60834469743929</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>10.27590396561472</v>
+        <v>11.12351190476189</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>10.17106326179353</v>
+        <v>10.99062779960029</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>14.00141247404316</v>
+        <v>14.77651859817465</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>12.98343900690276</v>
+        <v>13.80062885275744</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>13.64571211604515</v>
+        <v>13.23318435137671</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>18.38914326306979</v>
+        <v>19.11040278180237</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>19.86843725266027</v>
+        <v>20.54451345755695</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>20.99742427654544</v>
+        <v>21.57285065374366</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.08089</t>
+          <t>X &gt; 0.08075</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>76</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.938100254989081</v>
+        <v>3.03632064031045</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-2.659834438097569</v>
+        <v>-2.472744090130256</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.1504850660759232</v>
+        <v>0.2199302290308012</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1.768139861849754</v>
+        <v>2.259106977590996</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>6.695507284039316</v>
+        <v>7.246706732228496</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>6.882473470136695</v>
+        <v>7.40364033822658</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>6.110524786246344</v>
+        <v>6.608558325993862</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>11.09547123623011</v>
+        <v>11.56679577732208</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>13.76853736551324</v>
+        <v>14.32630363437462</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>11.67983221579253</v>
+        <v>12.21446266547106</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>10.63810238427025</v>
+        <v>11.17090820639119</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>14.30672140187488</v>
+        <v>14.84169467297252</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>17.13092775607141</v>
+        <v>17.67417097657439</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>19.54142782699323</v>
+        <v>20.0575158625097</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>13.62012663467582</v>
+        <v>14.11220358588779</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>12.89872408293461</v>
+        <v>13.35771813102325</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>10.13322799858871</v>
+        <v>10.62225877192981</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>11.34417676845175</v>
+        <v>11.80516414045243</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>15.5074365704287</v>
+        <v>15.96699478865084</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>15.69428238039673</v>
+        <v>16.18158123370982</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>17.78331515979912</v>
+        <v>18.24571567969751</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>21.65483761944265</v>
+        <v>22.11792157879486</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>21.92931233192471</v>
+        <v>22.36155606407323</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>21.85348007870143</v>
+        <v>22.19941706978377</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.08351</t>
+          <t>X &gt; 0.08337</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>2.880892017002814</v>
+        <v>2.171658986175117</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-3.25098623062236</v>
+        <v>-3.788533563814468</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>1.108096169622009</v>
+        <v>0.6710580485796669</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>3.293692874816948</v>
+        <v>2.935798706914305</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>8.755003851545041</v>
+        <v>8.374526281100685</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>7.49269467532357</v>
+        <v>7.102888458527332</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>6.720745991433219</v>
+        <v>7.736377874866051</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>12.23963599595551</v>
+        <v>13.14574314574314</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>13.73039854018906</v>
+        <v>14.70224348399868</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>12.95748286415257</v>
+        <v>13.90619198877934</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>11.78226714399565</v>
+        <v>12.74985557481224</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>12.95279310286649</v>
+        <v>13.90184504891238</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>16.17745712296691</v>
+        <v>17.07266721717588</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>18.85492897115799</v>
+        <v>19.68157601288564</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>13.8489595866209</v>
+        <v>13.28513591671486</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>14.44334650856389</v>
+        <v>13.84643993553452</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>11.41087864694875</v>
+        <v>12.31398809523809</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>12.75531330544641</v>
+        <v>13.60967541864791</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>15.86975541100842</v>
+        <v>16.68128050293654</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>16.05660122097645</v>
+        <v>16.89586694799553</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>16.96333041532925</v>
+        <v>17.75699387518624</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>22.6845859031955</v>
+        <v>23.39611706751666</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>21.50978525335873</v>
+        <v>22.21118012422361</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>21.43395300013545</v>
+        <v>22.04904112993415</v>
       </c>
     </row>
   </sheetData>
@@ -5824,83 +5824,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; 0.007494</t>
+          <t>X &lt; 0.007499</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-7.264035519229068</v>
+        <v>-6.399769585253459</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-10.49736304221656</v>
+        <v>-9.502819278100183</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-6.138280641972187</v>
+        <v>-5.043227665706048</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-1.054133212139568</v>
+        <v>0.0786558497714438</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-5.737749771643365</v>
+        <v>-4.482616576042183</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.2463178637293737</v>
+        <v>1.388602744241616</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.525630820160977</v>
+        <v>0.5935207320088978</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-3.702392989551726</v>
+        <v>-2.568542568542576</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-12.35655798155008</v>
+        <v>-12.44061365885847</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-13.12947365758657</v>
+        <v>-13.23666515407781</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-20.10179082701884</v>
+        <v>-20.10728728233061</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-23.27909095510452</v>
+        <v>-23.24101209394477</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-30.199354471236</v>
+        <v>-30.07018992568126</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-33.31898407232028</v>
+        <v>-33.17556684425722</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-33.97712736990083</v>
+        <v>-33.85772122614227</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-37.73056653491436</v>
+        <v>-37.5821314930369</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-40.76303439652951</v>
+        <v>-40.54315476190476</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-40.86787510035069</v>
+        <v>-40.67603886706637</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-43.55053444406406</v>
+        <v>-43.31871949706345</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-44.81296399641487</v>
+        <v>-44.53270448057589</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-45.3555101643809</v>
+        <v>-45.10014898195663</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-43.98208076347116</v>
+        <v>-43.74674007534048</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-45.15688141330794</v>
+        <v>-44.93167701863354</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-45.23271366653122</v>
+        <v>-45.093816012923</v>
       </c>
     </row>
     <row r="7">
@@ -5910,2375 +5910,2375 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-5.213174157457125</v>
+        <v>-5.441360905325787</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-7.434743408637125</v>
+        <v>-7.586001918244847</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-5.728108369617807</v>
+        <v>-5.676139058111112</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-5.183200753840417</v>
+        <v>-5.002718472109208</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-9.292576132048069</v>
+        <v>-9.075744966638922</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-9.734540763560751</v>
+        <v>-9.551722753045901</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-16.16686680594167</v>
+        <v>-16.04300729692419</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-20.21866315635513</v>
+        <v>-20.14539609476319</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-22.69289924488067</v>
+        <v>-21.91620136229427</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-22.8368841033071</v>
+        <v>-22.07934146510855</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-25.07854773158543</v>
+        <v>-24.33875202012447</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-26.61515877025355</v>
+        <v>-25.88115675940589</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-30.25404410754992</v>
+        <v>-29.52769444647691</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-29.84619216638645</v>
+        <v>-29.14301711550496</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-30.50433546396701</v>
+        <v>-29.82517149739002</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-31.7967409948542</v>
+        <v>-31.79551304819061</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-31.93065813183167</v>
+        <v>-31.89939345991561</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-30.14870638282267</v>
+        <v>-30.13354338786203</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-30.56174581950841</v>
+        <v>-30.55199255312131</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-31.6327616447605</v>
+        <v>-31.60322889287246</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-34.06210026555672</v>
+        <v>-33.43649617906332</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-31.62222295652557</v>
+        <v>-31.61292452380341</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-31.34774824404352</v>
+        <v>-31.36929003852504</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-29.53678804443661</v>
+        <v>-29.63269485559931</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 0.01274</t>
+          <t>X &lt; 0.01273</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.5796226236360482</v>
+        <v>-0.7402668461046957</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-2.372125369507728</v>
+        <v>-2.756085186233349</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-4.393234797547464</v>
+        <v>-4.600749789599853</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-5.689279195998949</v>
+        <v>-5.783122489883006</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-6.025069668546223</v>
+        <v>-6.058680629982341</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-7.295829429970716</v>
+        <v>-7.08168802693411</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-11.56632038791354</v>
+        <v>-11.12160779727892</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-13.59380296969286</v>
+        <v>-13.19643974511231</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-13.84386097728252</v>
+        <v>-13.06851083542821</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-13.45059589530153</v>
+        <v>-12.38963607696024</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-13.75962663214835</v>
+        <v>-12.70737156383083</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-13.4552856565876</v>
+        <v>-12.3939830168272</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-15.45308329195684</v>
+        <v>-14.39383088649036</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-14.50798141038593</v>
+        <v>-13.46212394497361</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-15.45766989747086</v>
+        <v>-14.43926357759614</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-16.61255411255411</v>
+        <v>-15.94285631393871</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-18.20419719705345</v>
+        <v>-18.11163348082596</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-18.01749271137026</v>
+        <v>-18.24451758598756</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-17.51005614094156</v>
+        <v>-17.14509960662939</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-18.7809362784954</v>
+        <v>-18.70042466599519</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-20.48966320447892</v>
+        <v>-20.44781017032578</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-19.39932840787053</v>
+        <v>-19.34303168933121</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-19.70794407439723</v>
+        <v>-19.3943824547903</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-19.7837763276205</v>
+        <v>-19.55652144907976</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; 0.01536</t>
+          <t>X &lt; 0.01535</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>611</v>
+        <v>604</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.7766899939556922</v>
+        <v>-1.059183019501333</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.7841345500796564</v>
+        <v>-1.139526941297909</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-1.240156872433069</v>
+        <v>-1.400843559745788</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-1.953110891875809</v>
+        <v>-1.827682844646716</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.61623360664894</v>
+        <v>-2.268803898653346</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-4.065928631680862</v>
+        <v>-3.601936517820818</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-4.019546710006558</v>
+        <v>-3.403641046609835</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-5.279754881437213</v>
+        <v>-4.701938973462156</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-5.565599941748367</v>
+        <v>-4.739572977685334</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-5.356518891107285</v>
+        <v>-4.376684075553683</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-5.409791491171212</v>
+        <v>-4.270011974856629</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-4.215545804602847</v>
+        <v>-3.05652770416237</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-5.338707871458965</v>
+        <v>-4.171419821613142</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-5.232454505679698</v>
+        <v>-4.088528055231677</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-6.054263924373181</v>
+        <v>-4.936245351024013</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-6.441873729107769</v>
+        <v>-5.533881729555347</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-7.394121471649896</v>
+        <v>-6.962265452538631</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-7.662628296584003</v>
+        <v>-7.426275385514799</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-8.428733642337257</v>
+        <v>-7.874064813998167</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-10.04221516461146</v>
+        <v>-9.811796249733888</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-9.930096848125764</v>
+        <v>-9.551426181578201</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-9.187612203970218</v>
+        <v>-8.798774133997057</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-9.731468097052812</v>
+        <v>-9.051828390440541</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-9.643634229163155</v>
+        <v>-9.213967384730005</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 0.01798</t>
+          <t>X &lt; 0.01796</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>907</v>
+        <v>899</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.9396343240163176</v>
+        <v>-0.9286111552518648</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.6128896229173932</v>
+        <v>-0.8408138752716425</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.499640755741105</v>
+        <v>-1.316865040567002</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-1.330566109252203</v>
+        <v>-0.9081548923229477</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-1.776610165040935</v>
+        <v>-1.183713032422283</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-2.692179811358109</v>
+        <v>-1.916657068248455</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-2.141085496351003</v>
+        <v>-1.265687912516761</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-2.750057690828434</v>
+        <v>-1.904312471609472</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-2.157302592706451</v>
+        <v>-1.108975330557179</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-1.717428853086943</v>
+        <v>-0.5702103630401467</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.77412996064939</v>
+        <v>-0.5204447588918697</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.060597114924278</v>
+        <v>0.204085633689111</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.191476932607301</v>
+        <v>0.09030586329061663</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.9715414760880634</v>
+        <v>0.2870106227696354</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-1.298924023944259</v>
+        <v>-0.1726743486593634</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-2.578848017106012</v>
+        <v>-1.502360318716221</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-3.043525903807847</v>
+        <v>-2.273648961809428</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-2.817605857904667</v>
+        <v>-2.184063656514951</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-3.152982393187621</v>
+        <v>-2.303305545053277</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-4.178925998875592</v>
+        <v>-3.534770267958699</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-3.729189917668528</v>
+        <v>-2.989867717059127</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-3.69478229583617</v>
+        <v>-2.953795533786376</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-3.861321916319945</v>
+        <v>-2.932630458964056</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-3.716647003060316</v>
+        <v>-2.983534748025498</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; 0.0206</t>
+          <t>X &lt; 0.02058</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.5710405532974008</v>
+        <v>-0.6213735528354007</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.8217130623284561</v>
+        <v>-0.867280388539271</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.082272060896877</v>
+        <v>-0.8518644142242522</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.5336617405582871</v>
+        <v>-0.08948253174543197</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.8694522131055606</v>
+        <v>-0.2803666667643299</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.607633209514496</v>
+        <v>-0.9701731115706522</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.37033042157978</v>
+        <v>-0.664493057757646</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.349150418917851</v>
+        <v>-0.7153914859249326</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.007767338960669</v>
+        <v>-0.333440560999513</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.552794037868594</v>
+        <v>0.1406180199877625</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.5677603738909696</v>
+        <v>0.1588310193507709</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.2914293804864201</v>
+        <v>0.4749671004425622</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.3513874995232129</v>
+        <v>0.3761630439570709</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.06528125340005886</v>
+        <v>0.6359730130065984</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.21623942841088</v>
+        <v>0.4618626616041865</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.8052844591306112</v>
+        <v>-0.2469433957827505</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-1.108263303631333</v>
+        <v>-0.7741938329099654</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-1.297634861214135</v>
+        <v>-1.161099953312892</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-2.180644579190918</v>
+        <v>-1.878051782051955</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-2.670045599315863</v>
+        <v>-2.510205387797377</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-2.282752375904039</v>
+        <v>-2.061561828212824</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-2.274067483551519</v>
+        <v>-2.052050345087672</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-2.591308747400831</v>
+        <v>-2.147111880131057</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-2.836202708147347</v>
+        <v>-2.478598884581395</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; 0.02322</t>
+          <t>X &lt; 0.0232</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1436</v>
+        <v>1440</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.4920581860963225</v>
+        <v>-0.6954045058883764</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.3424059187021982</v>
+        <v>-0.3857557860366896</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.3963419227504872</v>
+        <v>-0.1126721101504913</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.7632751809475522</v>
+        <v>-0.2189631978476001</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.099065653494826</v>
+        <v>-0.4250768935024922</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.396528533141399</v>
+        <v>-0.6848099541710724</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.614843999038662</v>
+        <v>-0.8548919664037982</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.785415190362684</v>
+        <v>-1.090367965367967</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-2.190539119879041</v>
+        <v>-1.379105722350523</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.578507809026796</v>
+        <v>-1.758490550903197</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.821118186239993</v>
+        <v>-1.902922202965527</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.714477428534465</v>
+        <v>-1.76283749077016</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.895772072025601</v>
+        <v>-1.97495183044316</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.521378702543409</v>
+        <v>-1.667630336320713</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-2.37445271557872</v>
+        <v>-1.585895829316875</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-2.784460200894742</v>
+        <v>-2.135702921608328</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-2.918377337872215</v>
+        <v>-2.447916666666671</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-3.232131690718461</v>
+        <v>-2.928022994050494</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-4.06080855491949</v>
+        <v>-3.616338544682492</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-4.361427926009952</v>
+        <v>-4.026752099623508</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-3.929043731858997</v>
+        <v>-3.621974378782021</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-4.144165459284807</v>
+        <v>-3.836025789626198</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-4.635707459894675</v>
+        <v>-4.217391304347814</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-4.85081547913466</v>
+        <v>-4.448974743081727</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; 0.02584</t>
+          <t>X &lt; 0.02581</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1699</v>
+        <v>1708</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.01935178632916035</v>
+        <v>-0.0379538309143399</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.346805994760274</v>
+        <v>0.4754851277743199</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.1566336150183787</v>
+        <v>0.2721928950416128</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.06499180479121947</v>
+        <v>0.7056910004769605</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.3876210976626027</v>
+        <v>0.4046014690705988</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.7263558461446564</v>
+        <v>0.06786379916096053</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.3553769640381859</v>
+        <v>0.443056801556672</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.3080375356997109</v>
+        <v>0.4307051118051604</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.5842697546863249</v>
+        <v>0.2660652678321611</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.621412699775064</v>
+        <v>0.2306925321213029</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.8995290405131513</v>
+        <v>-0.0236962098571496</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.203551936805937</v>
+        <v>-0.241764413597032</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.648204826117215</v>
+        <v>-0.6544915222707388</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.248663598754241</v>
+        <v>-0.317588076389633</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-1.402897749537786</v>
+        <v>-0.5316324524233167</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-1.772869707652312</v>
+        <v>-1.023575946769242</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-1.814078539361098</v>
+        <v>-1.244483859957093</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-2.061395986966218</v>
+        <v>-1.669936718775801</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-2.610210488394827</v>
+        <v>-2.099125749675665</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-2.658658796073851</v>
+        <v>-2.352649310468053</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-2.612969669922236</v>
+        <v>-2.217928803071736</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-2.747639160743105</v>
+        <v>-2.468632577221285</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-2.969234801063742</v>
+        <v>-2.576080596331444</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-3.103925206141042</v>
+        <v>-2.763605240089277</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; 0.02847</t>
+          <t>X &lt; 0.02843</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1894</v>
+        <v>1905</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.1006494852074908</v>
+        <v>0.03813647105302209</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.8124451620015805</v>
+        <v>0.9708806621269588</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.6303130831432711</v>
+        <v>0.8960711307355993</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.3883166775152915</v>
+        <v>0.9612287742291841</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.313774161332347</v>
+        <v>0.2962504448363674</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.2314652227493639</v>
+        <v>0.4302319745500967</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.1363751861978528</v>
+        <v>0.5560647427962238</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.1228574561136355</v>
+        <v>0.6182129936718255</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.05138981091840833</v>
+        <v>0.8510186731514295</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.09715896212875208</v>
+        <v>0.9464197211937488</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.5426564382845598</v>
+        <v>0.3796405774341594</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.8438518817278222</v>
+        <v>0.05062023806512883</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.834021381478351</v>
+        <v>0.08937258836474626</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.6565974516526722</v>
+        <v>0.2082072212158508</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.7580902007882244</v>
+        <v>0.05043668830824544</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-1.289791656703805</v>
+        <v>-0.541903760622489</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-1.28782463299023</v>
+        <v>-0.7506609421429857</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-1.625253125398203</v>
+        <v>-1.250613741588801</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-1.958316854228833</v>
+        <v>-1.560535363420477</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-2.110145663883713</v>
+        <v>-1.922771152236692</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-2.125543703225595</v>
+        <v>-1.86095503484448</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-2.118202575982615</v>
+        <v>-1.936117556799765</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-2.288157463936976</v>
+        <v>-2.08202928965737</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-2.386502136604527</v>
+        <v>-2.26666940624883</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; 0.03109</t>
+          <t>X &lt; 0.03104</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2061</v>
+        <v>2078</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.2793068067219551</v>
+        <v>0.2187532431400001</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.243231307073444</v>
+        <v>1.436778037336062</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.9115133643435485</v>
+        <v>1.311688401440243</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.631459777801247</v>
+        <v>1.226174358134479</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.0891310795464122</v>
+        <v>0.5458451206864439</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.1940352027510599</v>
+        <v>0.8739876763124386</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.267355747190571</v>
+        <v>0.9230326424915063</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.07955347045716366</v>
+        <v>0.5700583788041698</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.1549998011027256</v>
+        <v>0.6499334682095608</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.1292990460971311</v>
+        <v>0.6707969177283388</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.7434131209827513</v>
+        <v>0.07806316731584673</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.8981685364296368</v>
+        <v>-0.05435732631930534</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.125016157767256</v>
+        <v>-0.2562268584745482</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.7386301160294693</v>
+        <v>0.1202387437155963</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-1.175195002751067</v>
+        <v>-0.3216465367759014</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-1.518996148044003</v>
+        <v>-0.7694727438091959</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-1.286399406481024</v>
+        <v>-0.7291916946980592</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-1.508164534733645</v>
+        <v>-1.150398721531943</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-1.941740583491914</v>
+        <v>-1.512582337730713</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-1.969155876261866</v>
+        <v>-1.730480275180135</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-1.902527353460769</v>
+        <v>-1.577117472380188</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-2.095704513883874</v>
+        <v>-1.912948866549279</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-2.520634066564241</v>
+        <v>-2.218834305790814</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-2.520227115047135</v>
+        <v>-2.353543773131996</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 0.03371</t>
+          <t>X &lt; 0.03366</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2217</v>
+        <v>2235</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.01830686298474404</v>
+        <v>-0.04596748534891049</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.8544297554811848</v>
+        <v>0.9797373809270695</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.8922604381138868</v>
+        <v>1.220704567909642</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.5370881718017273</v>
+        <v>1.09942811942863</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.4248203687240775</v>
+        <v>0.1352198490231658</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.1004176594690875</v>
+        <v>0.6743170299559083</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.4727732902278845</v>
+        <v>1.065670288571141</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.0859725679292751</v>
+        <v>0.6971283110693278</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.2500440342226611</v>
+        <v>0.4675952010930189</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.4146970252841555</v>
+        <v>0.3864677451945084</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.6529054042593643</v>
+        <v>0.2118752352233244</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.8162981254089985</v>
+        <v>0.06934153812468224</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.6121507660867778</v>
+        <v>0.2502492419429032</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.4027973520297721</v>
+        <v>0.4488427050853048</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.8547397766354692</v>
+        <v>-0.009897914511988404</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-1.177562138236297</v>
+        <v>-0.3869316973009091</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.8356284951636539</v>
+        <v>-0.2227155942806078</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-1.138954135731794</v>
+        <v>-0.7577444715601729</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-1.616775850813426</v>
+        <v>-1.168840778820119</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-1.764069713254777</v>
+        <v>-1.490447363251754</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-1.650065589371096</v>
+        <v>-1.342967825311661</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-1.834880366373625</v>
+        <v>-1.705102678316408</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-2.300672006739809</v>
+        <v>-2.061756241736013</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-2.260424439020483</v>
+        <v>-2.153579515639528</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 0.03633</t>
+          <t>X &lt; 0.03628</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2382</v>
+        <v>2399</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.1437613515668517</v>
+        <v>-0.162286620271523</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.4789972372606783</v>
+        <v>0.6513004610817958</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.2483054155402726</v>
+        <v>0.5400018901262413</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.201462969786121</v>
+        <v>0.7181907334923707</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.4440617551767971</v>
+        <v>0.0921356347715232</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.02542126670540767</v>
+        <v>0.5217223262390007</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.02361005063744415</v>
+        <v>0.5400606785488478</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.3614446146982928</v>
+        <v>0.2172905667082006</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.7968184520657573</v>
+        <v>-0.08879153175544019</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.003587518852918</v>
+        <v>-0.2606233016314548</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.123242522882805</v>
+        <v>-0.4045347705893363</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.378324546328955</v>
+        <v>-0.5978874283481943</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.307720054428529</v>
+        <v>-0.5891840401809887</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.044736580681473</v>
+        <v>-0.3380423213394366</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-1.260236129197466</v>
+        <v>-0.520820922949838</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-1.603588183086089</v>
+        <v>-0.9166538163232687</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-1.294698242296043</v>
+        <v>-0.7292316895547302</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-1.207617289557604</v>
+        <v>-0.8205011463601082</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-1.637515251942474</v>
+        <v>-1.230258644557658</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-1.71979976545407</v>
+        <v>-1.431818683060882</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-1.567341355703476</v>
+        <v>-1.26762846334119</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-1.912364782535448</v>
+        <v>-1.776727580546641</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-2.033185183370044</v>
+        <v>-1.842391304347821</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-2.168792226747328</v>
+        <v>-2.105666188591428</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 0.03895</t>
+          <t>X &lt; 0.03889</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2538</v>
+        <v>2555</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.2606204623964103</v>
+        <v>-0.2508464398363515</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.1264640837239455</v>
+        <v>-0.008330913775502324</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.1967613664399721</v>
+        <v>0.1224643420912273</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.1673826913629384</v>
+        <v>0.6826228655949365</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.2246088059510072</v>
+        <v>0.311987961051635</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.01564035903717809</v>
+        <v>0.568930613094075</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.01720930576432522</v>
+        <v>0.5767861975078716</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.2386589207991037</v>
+        <v>0.2941806457431468</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.4098286435163843</v>
+        <v>0.2490530636335748</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.572683870661848</v>
+        <v>0.117323569195797</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.6680933284533452</v>
+        <v>0.03785870103342148</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.8852290625213968</v>
+        <v>-0.1605677239341574</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.044414483403322</v>
+        <v>-0.3375934873403779</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.9287035453937804</v>
+        <v>-0.2341276660067919</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-1.014221308208469</v>
+        <v>-0.3301155766139985</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-1.182187150372535</v>
+        <v>-0.5503668528314662</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.8609814937078397</v>
+        <v>-0.3416251465416238</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.9034233639547438</v>
+        <v>-0.5135870164550767</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-1.096967676523718</v>
+        <v>-0.6117469073241466</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-1.044505975228759</v>
+        <v>-0.7097825802800131</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.8557411586830312</v>
+        <v>-0.5117428611032793</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-1.144582189923277</v>
+        <v>-0.9158556683903782</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-1.319583835236017</v>
+        <v>-1.040552493706194</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-1.451235611232626</v>
+        <v>-1.3364774610639</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 0.04157</t>
+          <t>X &lt; 0.04151</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2657</v>
+        <v>2671</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.3747030298186829</v>
+        <v>-0.3384538518065767</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.07491469192362388</v>
+        <v>0.03181679026678097</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.260543632956157</v>
+        <v>-0.04695622648158349</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.09305188040941204</v>
+        <v>0.5374398855789835</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.1469913392003974</v>
+        <v>0.3201552789684854</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.02364415385533647</v>
+        <v>0.5727332833553618</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.02069287662936858</v>
+        <v>0.5081691903466847</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.273579898902895</v>
+        <v>0.2245627198933065</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.3604415188233503</v>
+        <v>0.2243447011671549</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.5878971975949199</v>
+        <v>0.02620053031253633</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.6668453783948465</v>
+        <v>-0.0005181172654786792</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.8492605349830029</v>
+        <v>-0.1649924484183956</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.976465915513856</v>
+        <v>-0.308285163776489</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.9507474931970137</v>
+        <v>-0.2949347708000403</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.9868145743106354</v>
+        <v>-0.3418126205475787</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-1.120728864631303</v>
+        <v>-0.5278927571838139</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.9699804730408133</v>
+        <v>-0.4822963378176439</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.9025967556702383</v>
+        <v>-0.5404420274336488</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-1.115403399518712</v>
+        <v>-0.6623026702430366</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-1.056938964962164</v>
+        <v>-0.6875776447948567</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.9008953665166786</v>
+        <v>-0.4853397074614847</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-1.029788575604947</v>
+        <v>-0.7629337582008375</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-1.297490566970389</v>
+        <v>-0.9838583702160832</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-1.313724722914955</v>
+        <v>-1.16163437950587</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.04419</t>
+          <t>X &lt; 0.04412</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2773</v>
+        <v>2786</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.1882531957217637</v>
+        <v>-0.2378750310759372</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.3441391175062876</v>
+        <v>-0.214552148517825</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.331323705265163</v>
+        <v>-0.127246257053919</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.05785369346710922</v>
+        <v>0.3371884473598357</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.2661123811695489</v>
+        <v>0.1532127109499015</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.1306702813954885</v>
+        <v>0.1870483930809641</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.05812263876779866</v>
+        <v>0.2354827799859862</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.2083350705012208</v>
+        <v>0.1658004523333929</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.1822290771357089</v>
+        <v>0.2783298841624671</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.4323238471311868</v>
+        <v>0.01972016608394256</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.5683055954781153</v>
+        <v>-0.137998241024377</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.7546978554245598</v>
+        <v>-0.3070918400675069</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.8156088440495992</v>
+        <v>-0.3112709514272751</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.7282546436461743</v>
+        <v>-0.2370399465758908</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.8620709513092635</v>
+        <v>-0.3459230995107561</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.8576869013762192</v>
+        <v>-0.3937197614506758</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.6827507973219227</v>
+        <v>-0.3184529141287484</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.6944209853786703</v>
+        <v>-0.4513370192903494</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.8172574540493329</v>
+        <v>-0.4518515030008956</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.6813027834491479</v>
+        <v>-0.3954796981898241</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.5182926060131052</v>
+        <v>-0.1531633752363533</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.7169025417711978</v>
+        <v>-0.4581563491670835</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.8897215541603671</v>
+        <v>-0.5521598727008836</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-1.016487845074828</v>
+        <v>-0.8009229763113694</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.04681</t>
+          <t>X &lt; 0.04674</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2869</v>
+        <v>2885</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.3559231853545128</v>
+        <v>-0.370212935007153</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.4647280280045365</v>
+        <v>-0.3563155576054271</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.5347502272487645</v>
+        <v>-0.3503360162926583</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.3287430515604655</v>
+        <v>0.04265801950368342</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.4720827436615167</v>
+        <v>-0.1100830322379167</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.3003606501484271</v>
+        <v>0.06612556684216742</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.2213131245389306</v>
+        <v>0.05052537215106412</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.3758413606867919</v>
+        <v>-0.02743348750953345</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.3146073895783772</v>
+        <v>0.08556693786155023</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.5127851236017307</v>
+        <v>-0.1028014391002827</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.6698343555668487</v>
+        <v>-0.2802378184772678</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.9287596993509339</v>
+        <v>-0.5222296657192373</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.9556950509461473</v>
+        <v>-0.5302383518313789</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.9134084648478762</v>
+        <v>-0.4325713409711582</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-1.03003246703954</v>
+        <v>-0.5266938999575643</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.9365026700793138</v>
+        <v>-0.484241489577883</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.7371328827523271</v>
+        <v>-0.3805812579269059</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.6823678539738864</v>
+        <v>-0.444285148629838</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.7242962061892584</v>
+        <v>-0.3824861802072945</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.6214154963871223</v>
+        <v>-0.3206686797550375</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.4819685229453441</v>
+        <v>-0.1060848743191158</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.6416297768432528</v>
+        <v>-0.3685422426916602</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.6949312037437423</v>
+        <v>-0.3469824339389476</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.8896359896150585</v>
+        <v>-0.6620259658816536</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.04944</t>
+          <t>X &lt; 0.04936</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2940</v>
+        <v>2965</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.2827640894697652</v>
+        <v>-0.2383664127801737</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.3294389016534893</v>
+        <v>-0.1979295369688359</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.4322177666216263</v>
+        <v>-0.2597432749709014</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.214434818093352</v>
+        <v>0.03931976611031018</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.4637392608460402</v>
+        <v>-0.1839458144893271</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.3592616994302276</v>
+        <v>-0.1090931082929458</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.368303329019831</v>
+        <v>-0.1459750663104273</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.3905340340497858</v>
+        <v>-0.1629320391929809</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.2620975975288857</v>
+        <v>0.01770165515816302</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.4402190973243734</v>
+        <v>-0.1536042042604606</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.5530145886564739</v>
+        <v>-0.2514903202079495</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.7107511412715937</v>
+        <v>-0.3934827726603984</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.7639874377076907</v>
+        <v>-0.4316588739604228</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.7279744923644884</v>
+        <v>-0.377066555851151</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.8575732100529834</v>
+        <v>-0.4872155541561156</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-0.8197648123021253</v>
+        <v>-0.4642695434118238</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-0.6962506862468913</v>
+        <v>-0.4335604531179982</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-0.645318354283809</v>
+        <v>-0.4120584852805322</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.5791508659040616</v>
+        <v>-0.2451264234703743</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.5421306630815295</v>
+        <v>-0.280190406573098</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-0.4191098630025323</v>
+        <v>-0.08667189300783917</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.6786984641381579</v>
+        <v>-0.4114807946818075</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.7240995043644247</v>
+        <v>-0.3839455862089096</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.8479162693114688</v>
+        <v>-0.5599687472038966</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.05206</t>
+          <t>X &lt; 0.05197</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2999</v>
+        <v>3023</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.3648709387132385</v>
+        <v>-0.3035606314318784</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.2847930610701042</v>
+        <v>-0.1701125111828858</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.3474177952498607</v>
+        <v>-0.2225629733730514</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.2802902561746947</v>
+        <v>-0.03984316273678701</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.5313072672494386</v>
+        <v>-0.2970951498226952</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.358947948839976</v>
+        <v>-0.1547814078381791</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.1508182264578224</v>
+        <v>0.02397495653232085</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.2443210305063772</v>
+        <v>-0.03158051938540041</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.1838951424321422</v>
+        <v>0.08211254339295238</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.4068273471539925</v>
+        <v>-0.1674981733013254</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.5784349750643401</v>
+        <v>-0.3052417528024023</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.6721280798500189</v>
+        <v>-0.3838692368019139</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.6798783289084867</v>
+        <v>-0.3770193549125338</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.7485793444748197</v>
+        <v>-0.3943065341285532</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.8553072958952797</v>
+        <v>-0.4825975045982389</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.8065775816025251</v>
+        <v>-0.4491720737033447</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-0.6548449782645918</v>
+        <v>-0.3687087458745921</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-0.6735130467685053</v>
+        <v>-0.4161699805880446</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.5711253470147071</v>
+        <v>-0.2153037582448079</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.5311588450445015</v>
+        <v>-0.2455743658937521</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.4545262792415201</v>
+        <v>-0.09967688300468325</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.6771920548764356</v>
+        <v>-0.3866456243369427</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.6829683698296805</v>
+        <v>-0.3218886588451682</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.8058274097596367</v>
+        <v>-0.497624906642578</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.05468</t>
+          <t>X &lt; 0.05459</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3048</v>
+        <v>3073</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.3357347721750443</v>
+        <v>-0.3126525679038821</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.197122283117281</v>
+        <v>-0.08901821648005637</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.2490942478769611</v>
+        <v>-0.1304933412070142</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.3247716869047963</v>
+        <v>-0.1555134726616956</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.5445524348699493</v>
+        <v>-0.3807869696847632</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.3393482073446705</v>
+        <v>-0.2058881740927205</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.04900127196606974</v>
+        <v>0.05260533672457512</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.2106988888214119</v>
+        <v>-0.1044996512785445</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.2158604556802928</v>
+        <v>-0.05534348861419858</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.3496290926058236</v>
+        <v>-0.1851588372653623</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.5467529261718127</v>
+        <v>-0.3480057343257954</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.7414382128482018</v>
+        <v>-0.5088981786866071</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.8651493933238257</v>
+        <v>-0.6001139575508034</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.8055481807173521</v>
+        <v>-0.5051623217605794</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.8557096685454226</v>
+        <v>-0.5194436698244829</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.8963985403775894</v>
+        <v>-0.5556558589663325</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.8147434029101248</v>
+        <v>-0.5431547619047592</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.7366146009343879</v>
+        <v>-0.4946256067313755</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.7306898625880081</v>
+        <v>-0.3910299027071815</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.7211828882795501</v>
+        <v>-0.4498779798098411</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.7201090841933535</v>
+        <v>-0.3806617072027692</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.8749294211095489</v>
+        <v>-0.5992371717400218</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.843469080445189</v>
+        <v>-0.4991089360979828</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.998433168984711</v>
+        <v>-0.707223106967902</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.0573</t>
+          <t>X &lt; 0.0572</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3100</v>
+        <v>3122</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.3907670621991812</v>
+        <v>-0.4106712432139332</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.3561492160739022</v>
+        <v>-0.2261925968933483</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.3992245051895793</v>
+        <v>-0.2548089574655066</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.4535200571785865</v>
+        <v>-0.2568902082443785</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.6111530828124074</v>
+        <v>-0.4511434328211834</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.4062743776739808</v>
+        <v>-0.2765473922460941</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.1978351414844326</v>
+        <v>-0.0982373347093386</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.2652476341164842</v>
+        <v>-0.1620962424021783</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.2696479855047613</v>
+        <v>-0.07985041827374317</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.3177677571649085</v>
+        <v>-0.1244202561186114</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.3785172245011168</v>
+        <v>-0.1528557489517084</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.5424194451011601</v>
+        <v>-0.283586622160648</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.6506283521354703</v>
+        <v>-0.3588224549776768</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.6921142274999141</v>
+        <v>-0.3649483439835421</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.6880787452906532</v>
+        <v>-0.3257597350622916</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.6859131859131864</v>
+        <v>-0.3206070749629646</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.6077982070928485</v>
+        <v>-0.309853387663793</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.5970575149386335</v>
+        <v>-0.328030098341479</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.5553653619384491</v>
+        <v>-0.2226438426251462</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.510614526819765</v>
+        <v>-0.2451622083887059</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.58303658808493</v>
+        <v>-0.2498632676709107</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.6720143266702081</v>
+        <v>-0.4021269419949505</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.7976518052806156</v>
+        <v>-0.4597864372328644</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.9512737413325283</v>
+        <v>-0.6671664293227408</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.05992</t>
+          <t>X &lt; 0.05982</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3132</v>
+        <v>3153</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.3286442608170717</v>
+        <v>-0.2995536802516483</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.3611660804564778</v>
+        <v>-0.2767225401924236</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.4184003347423655</v>
+        <v>-0.2858237589637653</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.5111147467529804</v>
+        <v>-0.3251980964714036</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.6388393728281727</v>
+        <v>-0.4572157473626532</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.4658974571815975</v>
+        <v>-0.2827942913938273</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.2991959270962354</v>
+        <v>-0.145550921889253</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.4005496291480739</v>
+        <v>-0.2433385835089936</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.3727500761605427</v>
+        <v>-0.1606713789161915</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.4600613834312099</v>
+        <v>-0.2441981957125137</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.5492459547808792</v>
+        <v>-0.3013130922755565</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.682564790705797</v>
+        <v>-0.4019238520129207</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.8329686218444436</v>
+        <v>-0.5189889143032502</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.8126878887761393</v>
+        <v>-0.4643071902217173</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.8154369639099386</v>
+        <v>-0.4322219941914298</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.7435823200154417</v>
+        <v>-0.3583777080683035</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.603932679468322</v>
+        <v>-0.2854694092826975</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.6262368372642726</v>
+        <v>-0.3364196385582474</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.5827770094246603</v>
+        <v>-0.1982997015328181</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.5684727216440848</v>
+        <v>-0.2501577590047859</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.5819161001689821</v>
+        <v>-0.1970166263527844</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-0.7026675026478344</v>
+        <v>-0.3802017008781817</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-0.8242280783093037</v>
+        <v>-0.4348928896363375</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.9770637137298408</v>
+        <v>-0.6418201812887361</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.06254</t>
+          <t>X &lt; 0.06244</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3170</v>
+        <v>3195</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.3367443887216695</v>
+        <v>-0.3108057212740576</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.2162254155411745</v>
+        <v>-0.1049774556391441</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.2585191751656382</v>
+        <v>-0.1302923423229672</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.3899198642680517</v>
+        <v>-0.2079471273447595</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.4887279984283737</v>
+        <v>-0.3106901825849775</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.2842042027154434</v>
+        <v>-0.1364517219893173</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.2855249553023853</v>
+        <v>-0.1670200970250733</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.4203711003080244</v>
+        <v>-0.2986666954278334</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.3924144646115195</v>
+        <v>-0.2154245177814715</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.3936933065560524</v>
+        <v>-0.214806987314681</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.3842697572050255</v>
+        <v>-0.1740845748136977</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.5192735036793863</v>
+        <v>-0.2769602430828115</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.5869365368520434</v>
+        <v>-0.3134837497610974</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.6952487701600276</v>
+        <v>-0.3875124649391921</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.5799693902244201</v>
+        <v>-0.2399220465453453</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.5017926273432849</v>
+        <v>-0.1596258064038309</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.3653390043766791</v>
+        <v>-0.0889743389548272</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.3570694200674112</v>
+        <v>-0.1096979914471419</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.3744531933508313</v>
+        <v>-0.03300521134916323</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.3265115704539383</v>
+        <v>-0.05005365219202673</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.3777311685967177</v>
+        <v>-0.03626977173595236</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.4978802407816758</v>
+        <v>-0.2179854392977632</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.6461660992525751</v>
+        <v>-0.2999945584154062</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.829568236091859</v>
+        <v>-0.5375897665559037</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.06516</t>
+          <t>X &lt; 0.06505</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3209</v>
+        <v>3232</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.2992629550161254</v>
+        <v>-0.2707373271889395</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.1842280591045906</v>
+        <v>-0.07003325650039471</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.2124045707198974</v>
+        <v>-0.1093205030869271</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.3817843447646538</v>
+        <v>-0.2235757439730648</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.4524741938188939</v>
+        <v>-0.2975306684093582</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.3721054935414756</v>
+        <v>-0.24656209092322</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.4447661068263855</v>
+        <v>-0.3474281313776402</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.5813953488372121</v>
+        <v>-0.4811041448972517</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.5843423523919498</v>
+        <v>-0.4282066017947983</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.5329639695202602</v>
+        <v>-0.3751212758980671</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.5514170381218619</v>
+        <v>-0.3318085238010013</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.6571668969535338</v>
+        <v>-0.4367140492028199</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.7997685499109508</v>
+        <v>-0.5472614203290718</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.8163164871939088</v>
+        <v>-0.5308149274510185</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.7104480930072725</v>
+        <v>-0.392741281680685</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.5949689622366066</v>
+        <v>-0.2452708228428904</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.4929175892615092</v>
+        <v>-0.2383869764330555</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.4238513890337217</v>
+        <v>-0.1986718856845613</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.4695391607474022</v>
+        <v>-0.1513246429216082</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.3888175262325859</v>
+        <v>-0.134858815733935</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.414888943235546</v>
+        <v>-0.09683699255499789</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.5656544391060905</v>
+        <v>-0.30827377973133</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.6776724196739252</v>
+        <v>-0.3556529808093174</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.8286146876629061</v>
+        <v>-0.5614609917065891</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.06779</t>
+          <t>X &lt; 0.06767</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3241</v>
+        <v>3266</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.2401118193143148</v>
+        <v>-0.2133473118746565</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.06817677724301774</v>
+        <v>0.04358322450670471</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.140804211579173</v>
+        <v>-0.008241356001143174</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.4074924111049469</v>
+        <v>-0.218709596711463</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.4807923607782456</v>
+        <v>-0.2947496484492191</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.4914384498904383</v>
+        <v>-0.3340351537921364</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.5403104048621827</v>
+        <v>-0.411657458670355</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.7090631270037306</v>
+        <v>-0.5775962814354116</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.6809001102400316</v>
+        <v>-0.4934721079375777</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.6376550507609409</v>
+        <v>-0.4492087080847753</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.6225323001667107</v>
+        <v>-0.4035448521471992</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.6992649750727082</v>
+        <v>-0.449240107541911</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.8207780767764064</v>
+        <v>-0.5396960070274304</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.7778261677290459</v>
+        <v>-0.4649441336345035</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.7410069685630347</v>
+        <v>-0.3964344213440185</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.6823777945661575</v>
+        <v>-0.3362985233187672</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.4903136140636022</v>
+        <v>-0.2083810724106314</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.4537581674404976</v>
+        <v>-0.201012670768776</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.4352621356711097</v>
+        <v>-0.09078570661054641</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.3843000541179151</v>
+        <v>-0.1028224360149466</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.3538124928713984</v>
+        <v>-0.009907317839164875</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.4729842478991557</v>
+        <v>-0.1892999634328092</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.6120039445777721</v>
+        <v>-0.2642232602706898</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.7313296778714289</v>
+        <v>-0.4389301761633106</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.07041</t>
+          <t>X &lt; 0.07028</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3268</v>
+        <v>3291</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.222433257461141</v>
+        <v>-0.2233750684847635</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.08504640418300369</v>
+        <v>-0.0004261083360503903</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.1992920942879977</v>
+        <v>-0.09153684445001176</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.3175945471654842</v>
+        <v>-0.1539022897634439</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.4234461689573337</v>
+        <v>-0.2616411768190474</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.4324510901990166</v>
+        <v>-0.2994342112477426</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.4263653843857185</v>
+        <v>-0.3220087204008379</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.5959833441917084</v>
+        <v>-0.4889710967727297</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.5981362481584753</v>
+        <v>-0.4347368979907813</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.622518725546179</v>
+        <v>-0.4573264897164435</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.5747820059188768</v>
+        <v>-0.3796843767616025</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.6531630653908422</v>
+        <v>-0.4271199612515417</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.6914185947094893</v>
+        <v>-0.4344713135846945</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.742121191984964</v>
+        <v>-0.4530152365193061</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.6805013466292777</v>
+        <v>-0.3598857283067716</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.6174381174381125</v>
+        <v>-0.2959408725025412</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.4891102898805499</v>
+        <v>-0.2304111077420643</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.4231768630307471</v>
+        <v>-0.1937822701600922</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.433596121291437</v>
+        <v>-0.113102298727803</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.3815122406301654</v>
+        <v>-0.1234263535435929</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.3863255423843484</v>
+        <v>-0.03552932717303747</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.5051495043300775</v>
+        <v>-0.2141384528512233</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.6101734274415946</v>
+        <v>-0.2562734428654423</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.66793974993994</v>
+        <v>-0.37011066934528</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.07303</t>
+          <t>X &lt; 0.0729</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3292</v>
+        <v>3317</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.2773478675797776</v>
+        <v>-0.2492135544579028</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.1735720107558336</v>
+        <v>-0.05987228798337441</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.2672499635293377</v>
+        <v>-0.1301060359876516</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.3294955309801466</v>
+        <v>-0.1366787107833787</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.4672198297281795</v>
+        <v>-0.275696397898983</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.444605556735624</v>
+        <v>-0.2819905305495567</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.4139459554310605</v>
+        <v>-0.2805901600983987</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.5843480217091681</v>
+        <v>-0.4486162902004551</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.4954640350246891</v>
+        <v>-0.303758916961705</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.5857455216545304</v>
+        <v>-0.392388446096497</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.5666113668245814</v>
+        <v>-0.3432375182808514</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.6767117572942283</v>
+        <v>-0.4224908735010473</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.6623064648123318</v>
+        <v>-0.3783973432636714</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.7748079471787221</v>
+        <v>-0.4588336225645691</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.6881372088165705</v>
+        <v>-0.3417002657436825</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.6818181818181799</v>
+        <v>-0.3340111922850255</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.5554176835159126</v>
+        <v>-0.269817990373042</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.521068515771546</v>
+        <v>-0.2646206133369517</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.5298700719734839</v>
+        <v>-0.1829149043052212</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.4768341244576391</v>
+        <v>-0.1914991637608168</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.485593074367479</v>
+        <v>-0.138875315863686</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.6041340355600653</v>
+        <v>-0.3167052111387036</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.6456872685036359</v>
+        <v>-0.2963545352097867</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.6428427453696841</v>
+        <v>-0.3502870065058445</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.07565</t>
+          <t>X &lt; 0.07552</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3308</v>
+        <v>3332</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.2334619438132322</v>
+        <v>-0.2192288145487566</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.191840127998006</v>
+        <v>-0.09145544813170403</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.2319067036784972</v>
+        <v>-0.1073493477817991</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.3273181341016667</v>
+        <v>-0.1165367857553221</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.4960514143296919</v>
+        <v>-0.2860014931244947</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.472655181317549</v>
+        <v>-0.2915678314513457</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.4458661911972612</v>
+        <v>-0.2937377246732638</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.5566283267567798</v>
+        <v>-0.4026439510310453</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.558244078014333</v>
+        <v>-0.3474812161592524</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.5916275896512317</v>
+        <v>-0.379522296934951</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.6314898438157712</v>
+        <v>-0.3891578781025515</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.6821815784675351</v>
+        <v>-0.4095014992762742</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.7335209523220598</v>
+        <v>-0.4304309410224718</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.7561515645235346</v>
+        <v>-0.4218693149762132</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.6730679133463227</v>
+        <v>-0.308313435489346</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.6639068611324319</v>
+        <v>-0.2981280713089234</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.5689233072777569</v>
+        <v>-0.2646282569631637</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.5352502238933354</v>
+        <v>-0.2600498231564146</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.5731550383850603</v>
+        <v>-0.2077130327456231</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.5194857355453024</v>
+        <v>-0.2153012602949715</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.5308370282820718</v>
+        <v>-0.1654734625734591</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.6491852776793081</v>
+        <v>-0.3428494248991356</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.71944464665048</v>
+        <v>-0.3515047156889537</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.7170029608199897</v>
+        <v>-0.4059408628629768</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.07827</t>
+          <t>X &lt; 0.07813</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3322</v>
+        <v>3346</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.2178276814439286</v>
+        <v>-0.2033569151097083</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.1478727156095374</v>
+        <v>-0.04744092723490212</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.1937805617699979</v>
+        <v>-0.06847269095106867</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.2618453345343923</v>
+        <v>-0.08007430895871437</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.4013278897976988</v>
+        <v>-0.2202518976299501</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.4071577936515141</v>
+        <v>-0.2548489289365676</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.3537491060315148</v>
+        <v>-0.2305734016302736</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.4651859489737546</v>
+        <v>-0.3402770803127808</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.4965605005183349</v>
+        <v>-0.3145457368964628</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.4730770357535974</v>
+        <v>-0.2902365826492357</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.5115859294676213</v>
+        <v>-0.2986707723148783</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.5631993508166815</v>
+        <v>-0.3200557423749544</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.6190051319542391</v>
+        <v>-0.3455207908244446</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.6424351918985352</v>
+        <v>-0.3082077432866726</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.562432735830896</v>
+        <v>-0.2277446453460286</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.5507780507780495</v>
+        <v>-0.2152348238146473</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.4867621991947146</v>
+        <v>-0.2121079381648272</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.4836951951110109</v>
+        <v>-0.2379208991154584</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.5806307574943474</v>
+        <v>-0.2445838445929667</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.5564692732412766</v>
+        <v>-0.2811053334543558</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.5700682988474952</v>
+        <v>-0.2040179407076437</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.6882493398327867</v>
+        <v>-0.410846578156665</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.7269747897313792</v>
+        <v>-0.3885893921876757</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.7549675907431066</v>
+        <v>-0.4733736937359154</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.08089</t>
+          <t>X &lt; 0.08075</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3329</v>
+        <v>3354</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.2100595239331611</v>
+        <v>-0.1816554518298759</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.1409476957268723</v>
+        <v>-0.0266852225822376</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2196131100664971</v>
+        <v>-0.08026470274309361</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.2890335284788605</v>
+        <v>-0.09324693623922542</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.3990660669007582</v>
+        <v>-0.2041023242104032</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.404492076385722</v>
+        <v>-0.2382401637400804</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.3826957126997641</v>
+        <v>-0.2455689827853504</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.4944902144818712</v>
+        <v>-0.3557405337820825</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.5556253139125999</v>
+        <v>-0.35945350111772</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.503913867933079</v>
+        <v>-0.3074150692457707</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.4819328924313808</v>
+        <v>-0.2557874308307575</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.5639444876318862</v>
+        <v>-0.3074750427606645</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.6219874661158045</v>
+        <v>-0.3355263722955542</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.6757818639006672</v>
+        <v>-0.35834245152747</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.5374212193811232</v>
+        <v>-0.1905023314479166</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.5245366460529723</v>
+        <v>-0.1766755569444385</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.4609282553554976</v>
+        <v>-0.1737919022116472</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.4880650053981697</v>
+        <v>-0.2296102956377908</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.5843450732425666</v>
+        <v>-0.2357441217391667</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.5898460324445551</v>
+        <v>-0.3014443767726078</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.6345783133796203</v>
+        <v>-0.2854760171496125</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.7226687402723115</v>
+        <v>-0.4324203069086749</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.7307161175774297</v>
+        <v>-0.3798354176116092</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.728771585303889</v>
+        <v>-0.4349864703725217</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.08351</t>
+          <t>X &lt; 0.08337</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3336</v>
+        <v>3360</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.2023237433813634</v>
+        <v>-0.1580568197452479</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.1340515472791068</v>
+        <v>-0.003790808048641736</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.2453379265559903</v>
+        <v>-0.08907209043245956</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.3161083032590852</v>
+        <v>-0.1030854858160453</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.4266199416254395</v>
+        <v>-0.2142362437376022</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.4018374861448848</v>
+        <v>-0.2184343867741916</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.3816974185349196</v>
+        <v>-0.2567690433623042</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.4938391519120771</v>
+        <v>-0.3672900296123132</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.5249178481700341</v>
+        <v>-0.3411427593875729</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.5047710835004722</v>
+        <v>-0.3202454741726513</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.4822634751379056</v>
+        <v>-0.2682292161750084</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.5049493520709163</v>
+        <v>-0.2610087046887131</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.5652023211383579</v>
+        <v>-0.290980704170039</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.6193297153983224</v>
+        <v>-0.3141849027565868</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.5125143849135085</v>
+        <v>-0.1478454681810248</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.5283094098883581</v>
+        <v>-0.1627219239836251</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.4651157519032765</v>
+        <v>-0.1897244084744116</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.4924165100767084</v>
+        <v>-0.2456849073006424</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.5581126663267568</v>
+        <v>-0.2217124921812541</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.5632026495433919</v>
+        <v>-0.2869086592747152</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.5790214994590883</v>
+        <v>-0.2422415013908079</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.697027663897515</v>
+        <v>-0.4187890257951423</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.6745076765922491</v>
+        <v>-0.3361059726013167</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.6727094959546349</v>
+        <v>-0.3914350605420438</v>
       </c>
     </row>
   </sheetData>
